--- a/0. capaian omnibus 2026.xlsx
+++ b/0. capaian omnibus 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Downloads\0. Omnibus\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{21C7C395-3CAA-4496-AE3E-59DBB8C13646}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F177ED59-2B15-4AB5-BD4C-9AC854785BB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-109" yWindow="-109" windowWidth="26301" windowHeight="15800" xr2:uid="{ABC9ECFA-347A-408B-B0D0-6F1CCFF80879}"/>
   </bookViews>
@@ -4999,13 +4999,13 @@
         <v>22</v>
       </c>
       <c r="G2" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H2" s="4">
         <v>3</v>
       </c>
       <c r="I2" s="4">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -5115,13 +5115,13 @@
         <v>72</v>
       </c>
       <c r="G6" s="4">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H6" s="4">
         <v>13</v>
       </c>
       <c r="I6" s="4">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
@@ -5173,13 +5173,13 @@
         <v>35</v>
       </c>
       <c r="G8" s="4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H8" s="4">
         <v>5</v>
       </c>
       <c r="I8" s="4">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
@@ -5260,13 +5260,13 @@
         <v>61</v>
       </c>
       <c r="G11" s="4">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H11" s="4">
         <v>15</v>
       </c>
       <c r="I11" s="4">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
@@ -5405,13 +5405,13 @@
         <v>20</v>
       </c>
       <c r="G16" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H16" s="4">
         <v>2</v>
       </c>
       <c r="I16" s="4">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
@@ -5521,13 +5521,13 @@
         <v>132</v>
       </c>
       <c r="G20" s="4">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H20" s="4">
         <v>14</v>
       </c>
       <c r="I20" s="4">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
@@ -5666,13 +5666,13 @@
         <v>21</v>
       </c>
       <c r="G25" s="4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H25" s="4">
         <v>3</v>
       </c>
       <c r="I25" s="4">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
@@ -5898,13 +5898,13 @@
         <v>7</v>
       </c>
       <c r="G33" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H33" s="4">
         <v>1</v>
       </c>
       <c r="I33" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
@@ -6072,13 +6072,13 @@
         <v>43</v>
       </c>
       <c r="G39" s="4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H39" s="4">
         <v>3</v>
       </c>
       <c r="I39" s="4">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
@@ -6333,13 +6333,13 @@
         <v>74</v>
       </c>
       <c r="G48" s="4">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="H48" s="4">
         <v>7</v>
       </c>
       <c r="I48" s="4">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
@@ -6478,13 +6478,13 @@
         <v>111</v>
       </c>
       <c r="G53" s="4">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H53" s="4">
         <v>15</v>
       </c>
       <c r="I53" s="4">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
@@ -6594,13 +6594,13 @@
         <v>102</v>
       </c>
       <c r="G57" s="4">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H57" s="4">
         <v>21</v>
       </c>
       <c r="I57" s="4">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
@@ -6768,13 +6768,13 @@
         <v>106</v>
       </c>
       <c r="G63" s="4">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H63" s="4">
         <v>11</v>
       </c>
       <c r="I63" s="4">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
@@ -6884,13 +6884,13 @@
         <v>50</v>
       </c>
       <c r="G67" s="4">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H67" s="4">
         <v>20</v>
       </c>
       <c r="I67" s="4">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
@@ -7058,13 +7058,13 @@
         <v>15</v>
       </c>
       <c r="G73" s="4">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H73" s="4">
         <v>1</v>
       </c>
       <c r="I73" s="4">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.25">
@@ -7116,13 +7116,13 @@
         <v>6</v>
       </c>
       <c r="G75" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H75" s="4">
         <v>0</v>
       </c>
       <c r="I75" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.25">
@@ -7232,13 +7232,13 @@
         <v>130</v>
       </c>
       <c r="G79" s="4">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="H79" s="4">
         <v>15</v>
       </c>
       <c r="I79" s="4">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.25">
@@ -7261,13 +7261,13 @@
         <v>10</v>
       </c>
       <c r="G80" s="4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H80" s="4">
         <v>3</v>
       </c>
       <c r="I80" s="4">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.25">
@@ -7493,13 +7493,13 @@
         <v>35</v>
       </c>
       <c r="G88" s="4">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H88" s="4">
         <v>8</v>
       </c>
       <c r="I88" s="4">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.25">
@@ -7522,13 +7522,13 @@
         <v>5</v>
       </c>
       <c r="G89" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H89" s="4">
         <v>1</v>
       </c>
       <c r="I89" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.25">
@@ -7609,13 +7609,13 @@
         <v>5</v>
       </c>
       <c r="G92" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H92" s="4">
         <v>1</v>
       </c>
       <c r="I92" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.25">
@@ -7725,13 +7725,13 @@
         <v>36</v>
       </c>
       <c r="G96" s="4">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H96" s="4">
         <v>9</v>
       </c>
       <c r="I96" s="4">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.25">
@@ -7783,13 +7783,13 @@
         <v>76</v>
       </c>
       <c r="G98" s="4">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H98" s="4">
         <v>6</v>
       </c>
       <c r="I98" s="4">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.25">
@@ -8044,13 +8044,13 @@
         <v>46</v>
       </c>
       <c r="G107" s="4">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H107" s="4">
         <v>5</v>
       </c>
       <c r="I107" s="4">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.25">
@@ -8189,13 +8189,13 @@
         <v>110</v>
       </c>
       <c r="G112" s="4">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H112" s="4">
         <v>12</v>
       </c>
       <c r="I112" s="4">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.25">
@@ -8247,13 +8247,13 @@
         <v>54</v>
       </c>
       <c r="G114" s="4">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H114" s="4">
         <v>10</v>
       </c>
       <c r="I114" s="4">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.25">
@@ -8334,13 +8334,13 @@
         <v>45</v>
       </c>
       <c r="G117" s="4">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H117" s="4">
         <v>7</v>
       </c>
       <c r="I117" s="4">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.25">
@@ -8363,13 +8363,13 @@
         <v>41</v>
       </c>
       <c r="G118" s="4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H118" s="4">
         <v>4</v>
       </c>
       <c r="I118" s="4">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.25">
@@ -8450,13 +8450,13 @@
         <v>39</v>
       </c>
       <c r="G121" s="4">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H121" s="4">
         <v>8</v>
       </c>
       <c r="I121" s="4">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.25">
@@ -8508,13 +8508,13 @@
         <v>16</v>
       </c>
       <c r="G123" s="4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H123" s="4">
         <v>0</v>
       </c>
       <c r="I123" s="4">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.25">
@@ -8595,13 +8595,13 @@
         <v>38</v>
       </c>
       <c r="G126" s="4">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H126" s="4">
         <v>9</v>
       </c>
       <c r="I126" s="4">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.25">
@@ -8624,13 +8624,13 @@
         <v>140</v>
       </c>
       <c r="G127" s="4">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="H127" s="4">
         <v>20</v>
       </c>
       <c r="I127" s="4">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.25">
@@ -8682,13 +8682,13 @@
         <v>44</v>
       </c>
       <c r="G129" s="4">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H129" s="4">
         <v>10</v>
       </c>
       <c r="I129" s="4">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.25">
@@ -8943,13 +8943,13 @@
         <v>35</v>
       </c>
       <c r="G138" s="4">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="H138" s="4">
         <v>10</v>
       </c>
       <c r="I138" s="4">
-        <v>22</v>
+        <v>30</v>
       </c>
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.25">
@@ -8972,13 +8972,13 @@
         <v>83</v>
       </c>
       <c r="G139" s="4">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H139" s="4">
         <v>11</v>
       </c>
       <c r="I139" s="4">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.25">
@@ -9117,13 +9117,13 @@
         <v>42</v>
       </c>
       <c r="G144" s="4">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H144" s="4">
         <v>12</v>
       </c>
       <c r="I144" s="4">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.25">
@@ -9407,13 +9407,13 @@
         <v>122</v>
       </c>
       <c r="G154" s="4">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="H154" s="4">
         <v>19</v>
       </c>
       <c r="I154" s="4">
-        <v>86</v>
+        <v>90</v>
       </c>
     </row>
     <row r="155" spans="1:9" x14ac:dyDescent="0.25">
@@ -9436,13 +9436,13 @@
         <v>101</v>
       </c>
       <c r="G155" s="4">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H155" s="4">
         <v>11</v>
       </c>
       <c r="I155" s="4">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="156" spans="1:9" x14ac:dyDescent="0.25">
@@ -9552,13 +9552,13 @@
         <v>46</v>
       </c>
       <c r="G159" s="4">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H159" s="4">
         <v>16</v>
       </c>
       <c r="I159" s="4">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="160" spans="1:9" x14ac:dyDescent="0.25">
@@ -9784,13 +9784,13 @@
         <v>144</v>
       </c>
       <c r="G167" s="4">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H167" s="4">
         <v>21</v>
       </c>
       <c r="I167" s="4">
-        <v>97</v>
+        <v>101</v>
       </c>
     </row>
     <row r="168" spans="1:9" x14ac:dyDescent="0.25">
@@ -9842,13 +9842,13 @@
         <v>76</v>
       </c>
       <c r="G169" s="4">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H169" s="4">
         <v>7</v>
       </c>
       <c r="I169" s="4">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="170" spans="1:9" x14ac:dyDescent="0.25">
@@ -9897,7 +9897,7 @@
         <v>14</v>
       </c>
       <c r="F171" s="4">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G171" s="4">
         <v>2</v>
@@ -9906,7 +9906,7 @@
         <v>12</v>
       </c>
       <c r="I171" s="4">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="172" spans="1:9" x14ac:dyDescent="0.25">
@@ -9955,16 +9955,16 @@
         <v>14</v>
       </c>
       <c r="F173" s="4">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G173" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H173" s="4">
         <v>2</v>
       </c>
       <c r="I173" s="4">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="174" spans="1:9" x14ac:dyDescent="0.25">
@@ -10074,13 +10074,13 @@
         <v>49</v>
       </c>
       <c r="G177" s="4">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H177" s="4">
         <v>6</v>
       </c>
       <c r="I177" s="4">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="178" spans="1:9" x14ac:dyDescent="0.25">
@@ -10248,13 +10248,13 @@
         <v>9</v>
       </c>
       <c r="G183" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H183" s="4">
         <v>2</v>
       </c>
       <c r="I183" s="4">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="184" spans="1:9" x14ac:dyDescent="0.25">
@@ -10277,13 +10277,13 @@
         <v>82</v>
       </c>
       <c r="G184" s="4">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H184" s="4">
         <v>6</v>
       </c>
       <c r="I184" s="4">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="185" spans="1:9" x14ac:dyDescent="0.25">
@@ -10306,13 +10306,13 @@
         <v>71</v>
       </c>
       <c r="G185" s="4">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H185" s="4">
         <v>12</v>
       </c>
       <c r="I185" s="4">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="186" spans="1:9" x14ac:dyDescent="0.25">
@@ -10422,13 +10422,13 @@
         <v>46</v>
       </c>
       <c r="G189" s="4">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H189" s="4">
         <v>8</v>
       </c>
       <c r="I189" s="4">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="190" spans="1:9" x14ac:dyDescent="0.25">
@@ -10451,13 +10451,13 @@
         <v>210</v>
       </c>
       <c r="G190" s="4">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H190" s="4">
         <v>22</v>
       </c>
       <c r="I190" s="4">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="191" spans="1:9" x14ac:dyDescent="0.25">
@@ -10683,13 +10683,13 @@
         <v>4</v>
       </c>
       <c r="G198" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H198" s="4">
         <v>0</v>
       </c>
       <c r="I198" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="199" spans="1:9" x14ac:dyDescent="0.25">
@@ -10712,13 +10712,13 @@
         <v>107</v>
       </c>
       <c r="G199" s="4">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="H199" s="4">
         <v>9</v>
       </c>
       <c r="I199" s="4">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="200" spans="1:9" x14ac:dyDescent="0.25">
@@ -10828,13 +10828,13 @@
         <v>59</v>
       </c>
       <c r="G203" s="4">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H203" s="4">
         <v>10</v>
       </c>
       <c r="I203" s="4">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="204" spans="1:9" x14ac:dyDescent="0.25">
@@ -11060,13 +11060,13 @@
         <v>24</v>
       </c>
       <c r="G211" s="4">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H211" s="4">
         <v>0</v>
       </c>
       <c r="I211" s="4">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="212" spans="1:9" x14ac:dyDescent="0.25">
@@ -11205,13 +11205,13 @@
         <v>119</v>
       </c>
       <c r="G216" s="4">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H216" s="4">
         <v>11</v>
       </c>
       <c r="I216" s="4">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="217" spans="1:9" x14ac:dyDescent="0.25">
@@ -11350,13 +11350,13 @@
         <v>168</v>
       </c>
       <c r="G221" s="4">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="H221" s="4">
         <v>26</v>
       </c>
       <c r="I221" s="4">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
     <row r="222" spans="1:9" x14ac:dyDescent="0.25">
@@ -11466,13 +11466,13 @@
         <v>55</v>
       </c>
       <c r="G225" s="4">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H225" s="4">
         <v>2</v>
       </c>
       <c r="I225" s="4">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="226" spans="1:9" x14ac:dyDescent="0.25">
@@ -11785,13 +11785,13 @@
         <v>62</v>
       </c>
       <c r="G236" s="4">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H236" s="4">
         <v>7</v>
       </c>
       <c r="I236" s="4">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="237" spans="1:9" x14ac:dyDescent="0.25">
@@ -12278,13 +12278,13 @@
         <v>84</v>
       </c>
       <c r="G253" s="4">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H253" s="4">
         <v>11</v>
       </c>
       <c r="I253" s="4">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="254" spans="1:9" x14ac:dyDescent="0.25">
@@ -12394,13 +12394,13 @@
         <v>44</v>
       </c>
       <c r="G257" s="4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H257" s="4">
         <v>7</v>
       </c>
       <c r="I257" s="4">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="258" spans="1:9" x14ac:dyDescent="0.25">
@@ -13148,13 +13148,13 @@
         <v>38</v>
       </c>
       <c r="G283" s="4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H283" s="4">
         <v>7</v>
       </c>
       <c r="I283" s="4">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="284" spans="1:9" x14ac:dyDescent="0.25">
@@ -13438,13 +13438,13 @@
         <v>151</v>
       </c>
       <c r="G293" s="4">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="H293" s="4">
         <v>25</v>
       </c>
       <c r="I293" s="4">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="294" spans="1:9" x14ac:dyDescent="0.25">
@@ -13786,13 +13786,13 @@
         <v>241</v>
       </c>
       <c r="G305" s="4">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="H305" s="4">
         <v>39</v>
       </c>
       <c r="I305" s="4">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="306" spans="1:9" x14ac:dyDescent="0.25">
@@ -14047,13 +14047,13 @@
         <v>137</v>
       </c>
       <c r="G314" s="4">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H314" s="4">
         <v>16</v>
       </c>
       <c r="I314" s="4">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="315" spans="1:9" x14ac:dyDescent="0.25">
@@ -14308,13 +14308,13 @@
         <v>38</v>
       </c>
       <c r="G323" s="4">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H323" s="4">
         <v>13</v>
       </c>
       <c r="I323" s="4">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="324" spans="1:9" x14ac:dyDescent="0.25">
@@ -14337,13 +14337,13 @@
         <v>49</v>
       </c>
       <c r="G324" s="4">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H324" s="4">
         <v>4</v>
       </c>
       <c r="I324" s="4">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="325" spans="1:9" x14ac:dyDescent="0.25">
@@ -14801,13 +14801,13 @@
         <v>198</v>
       </c>
       <c r="G340" s="4">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H340" s="4">
         <v>37</v>
       </c>
       <c r="I340" s="4">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="341" spans="1:9" x14ac:dyDescent="0.25">
@@ -15207,13 +15207,13 @@
         <v>10</v>
       </c>
       <c r="G354" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H354" s="4">
         <v>2</v>
       </c>
       <c r="I354" s="4">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="355" spans="1:9" x14ac:dyDescent="0.25">
@@ -15294,13 +15294,13 @@
         <v>164</v>
       </c>
       <c r="G357" s="4">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H357" s="4">
         <v>20</v>
       </c>
       <c r="I357" s="4">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="358" spans="1:9" x14ac:dyDescent="0.25">
@@ -15526,13 +15526,13 @@
         <v>148</v>
       </c>
       <c r="G365" s="4">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H365" s="4">
         <v>19</v>
       </c>
       <c r="I365" s="4">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="366" spans="1:9" x14ac:dyDescent="0.25">
@@ -15671,13 +15671,13 @@
         <v>40</v>
       </c>
       <c r="G370" s="4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H370" s="4">
         <v>11</v>
       </c>
       <c r="I370" s="4">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="371" spans="1:9" x14ac:dyDescent="0.25">
@@ -16019,13 +16019,13 @@
         <v>168</v>
       </c>
       <c r="G382" s="4">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H382" s="4">
         <v>19</v>
       </c>
       <c r="I382" s="4">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="383" spans="1:9" x14ac:dyDescent="0.25">
@@ -16860,13 +16860,13 @@
         <v>17</v>
       </c>
       <c r="G411" s="4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H411" s="4">
         <v>0</v>
       </c>
       <c r="I411" s="4">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="412" spans="1:9" x14ac:dyDescent="0.25">
@@ -17063,13 +17063,13 @@
         <v>7</v>
       </c>
       <c r="G418" s="4">
+        <v>3</v>
+      </c>
+      <c r="H418" s="4">
+        <v>1</v>
+      </c>
+      <c r="I418" s="4">
         <v>4</v>
-      </c>
-      <c r="H418" s="4">
-        <v>1</v>
-      </c>
-      <c r="I418" s="4">
-        <v>3</v>
       </c>
     </row>
     <row r="419" spans="1:9" x14ac:dyDescent="0.25">
@@ -17440,13 +17440,13 @@
         <v>70</v>
       </c>
       <c r="G431" s="4">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H431" s="4">
         <v>11</v>
       </c>
       <c r="I431" s="4">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="432" spans="1:9" x14ac:dyDescent="0.25">
@@ -17585,13 +17585,13 @@
         <v>3</v>
       </c>
       <c r="G436" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H436" s="4">
         <v>0</v>
       </c>
       <c r="I436" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="437" spans="1:9" x14ac:dyDescent="0.25">
@@ -17643,13 +17643,13 @@
         <v>63</v>
       </c>
       <c r="G438" s="4">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H438" s="4">
         <v>5</v>
       </c>
       <c r="I438" s="4">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="439" spans="1:9" x14ac:dyDescent="0.25">
@@ -18020,13 +18020,13 @@
         <v>16</v>
       </c>
       <c r="G451" s="4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H451" s="4">
         <v>4</v>
       </c>
       <c r="I451" s="4">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="452" spans="1:9" x14ac:dyDescent="0.25">
@@ -18223,13 +18223,13 @@
         <v>51</v>
       </c>
       <c r="G458" s="4">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H458" s="4">
         <v>9</v>
       </c>
       <c r="I458" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="459" spans="1:9" x14ac:dyDescent="0.25">
@@ -18252,13 +18252,13 @@
         <v>33</v>
       </c>
       <c r="G459" s="4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H459" s="4">
         <v>5</v>
       </c>
       <c r="I459" s="4">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="460" spans="1:9" x14ac:dyDescent="0.25">
@@ -18310,13 +18310,13 @@
         <v>72</v>
       </c>
       <c r="G461" s="4">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H461" s="4">
         <v>16</v>
       </c>
       <c r="I461" s="4">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="462" spans="1:9" x14ac:dyDescent="0.25">
@@ -18455,13 +18455,13 @@
         <v>47</v>
       </c>
       <c r="G466" s="4">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H466" s="4">
         <v>8</v>
       </c>
       <c r="I466" s="4">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="467" spans="1:9" x14ac:dyDescent="0.25">
@@ -19238,13 +19238,13 @@
         <v>82</v>
       </c>
       <c r="G493" s="4">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H493" s="4">
         <v>10</v>
       </c>
       <c r="I493" s="4">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="494" spans="1:9" x14ac:dyDescent="0.25">
@@ -19325,13 +19325,13 @@
         <v>84</v>
       </c>
       <c r="G496" s="4">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H496" s="4">
         <v>15</v>
       </c>
       <c r="I496" s="4">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="497" spans="1:9" x14ac:dyDescent="0.25">
@@ -19412,13 +19412,13 @@
         <v>33</v>
       </c>
       <c r="G499" s="4">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H499" s="4">
         <v>4</v>
       </c>
       <c r="I499" s="4">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="500" spans="1:9" x14ac:dyDescent="0.25">
@@ -19818,13 +19818,13 @@
         <v>42</v>
       </c>
       <c r="G513" s="4">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H513" s="4">
         <v>6</v>
       </c>
       <c r="I513" s="4">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="514" spans="1:9" x14ac:dyDescent="0.25">
@@ -20137,13 +20137,13 @@
         <v>38</v>
       </c>
       <c r="G524" s="4">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H524" s="4">
         <v>5</v>
       </c>
       <c r="I524" s="4">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="525" spans="1:9" x14ac:dyDescent="0.25">
@@ -20340,13 +20340,13 @@
         <v>107</v>
       </c>
       <c r="G531" s="4">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H531" s="4">
         <v>15</v>
       </c>
       <c r="I531" s="4">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="532" spans="1:9" x14ac:dyDescent="0.25">
@@ -20688,13 +20688,13 @@
         <v>38</v>
       </c>
       <c r="G543" s="4">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H543" s="4">
         <v>12</v>
       </c>
       <c r="I543" s="4">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="544" spans="1:9" x14ac:dyDescent="0.25">
@@ -21036,13 +21036,13 @@
         <v>252</v>
       </c>
       <c r="G555" s="4">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H555" s="4">
         <v>29</v>
       </c>
       <c r="I555" s="4">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="556" spans="1:9" x14ac:dyDescent="0.25">
@@ -21558,13 +21558,13 @@
         <v>31</v>
       </c>
       <c r="G573" s="4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H573" s="4">
         <v>3</v>
       </c>
       <c r="I573" s="4">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="574" spans="1:9" x14ac:dyDescent="0.25">
@@ -21819,13 +21819,13 @@
         <v>14</v>
       </c>
       <c r="G582" s="4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H582" s="4">
         <v>0</v>
       </c>
       <c r="I582" s="4">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="583" spans="1:9" x14ac:dyDescent="0.25">
@@ -22138,13 +22138,13 @@
         <v>242</v>
       </c>
       <c r="G593" s="4">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H593" s="4">
         <v>27</v>
       </c>
       <c r="I593" s="4">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="594" spans="1:9" x14ac:dyDescent="0.25">
@@ -22486,13 +22486,13 @@
         <v>179</v>
       </c>
       <c r="G605" s="4">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="H605" s="4">
         <v>22</v>
       </c>
       <c r="I605" s="4">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="606" spans="1:9" x14ac:dyDescent="0.25">
@@ -22747,13 +22747,13 @@
         <v>100</v>
       </c>
       <c r="G614" s="4">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H614" s="4">
         <v>9</v>
       </c>
       <c r="I614" s="4">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="615" spans="1:9" x14ac:dyDescent="0.25">
@@ -22921,13 +22921,13 @@
         <v>35</v>
       </c>
       <c r="G620" s="4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H620" s="4">
         <v>7</v>
       </c>
       <c r="I620" s="4">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="621" spans="1:9" x14ac:dyDescent="0.25">
@@ -23327,13 +23327,13 @@
         <v>5</v>
       </c>
       <c r="G634" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H634" s="4">
         <v>0</v>
       </c>
       <c r="I634" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="635" spans="1:9" x14ac:dyDescent="0.25">
@@ -23443,13 +23443,13 @@
         <v>50</v>
       </c>
       <c r="G638" s="4">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H638" s="4">
         <v>7</v>
       </c>
       <c r="I638" s="4">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="639" spans="1:9" x14ac:dyDescent="0.25">
@@ -23704,13 +23704,13 @@
         <v>53</v>
       </c>
       <c r="G647" s="4">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H647" s="4">
         <v>8</v>
       </c>
       <c r="I647" s="4">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="648" spans="1:9" x14ac:dyDescent="0.25">
@@ -23936,13 +23936,13 @@
         <v>92</v>
       </c>
       <c r="G655" s="4">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H655" s="4">
         <v>9</v>
       </c>
       <c r="I655" s="4">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="656" spans="1:9" x14ac:dyDescent="0.25">
@@ -24226,13 +24226,13 @@
         <v>87</v>
       </c>
       <c r="G665" s="4">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H665" s="4">
         <v>15</v>
       </c>
       <c r="I665" s="4">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="666" spans="1:9" x14ac:dyDescent="0.25">
@@ -25067,13 +25067,13 @@
         <v>166</v>
       </c>
       <c r="G694" s="4">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H694" s="4">
         <v>27</v>
       </c>
       <c r="I694" s="4">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="695" spans="1:9" x14ac:dyDescent="0.25">
@@ -25357,13 +25357,13 @@
         <v>53</v>
       </c>
       <c r="G704" s="4">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H704" s="4">
         <v>11</v>
       </c>
       <c r="I704" s="4">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="705" spans="1:9" x14ac:dyDescent="0.25">
@@ -25618,13 +25618,13 @@
         <v>49</v>
       </c>
       <c r="G713" s="4">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H713" s="4">
         <v>9</v>
       </c>
       <c r="I713" s="4">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="714" spans="1:9" x14ac:dyDescent="0.25">
@@ -26024,13 +26024,13 @@
         <v>64</v>
       </c>
       <c r="G727" s="4">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H727" s="4">
         <v>2</v>
       </c>
       <c r="I727" s="4">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="728" spans="1:9" x14ac:dyDescent="0.25">
@@ -26372,13 +26372,13 @@
         <v>79</v>
       </c>
       <c r="G739" s="4">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H739" s="4">
         <v>12</v>
       </c>
       <c r="I739" s="4">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="740" spans="1:9" x14ac:dyDescent="0.25">
@@ -26401,13 +26401,13 @@
         <v>129</v>
       </c>
       <c r="G740" s="4">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H740" s="4">
         <v>22</v>
       </c>
       <c r="I740" s="4">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="741" spans="1:9" x14ac:dyDescent="0.25">
@@ -27271,13 +27271,13 @@
         <v>43</v>
       </c>
       <c r="G770" s="4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H770" s="4">
         <v>7</v>
       </c>
       <c r="I770" s="4">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="771" spans="1:9" x14ac:dyDescent="0.25">
@@ -27677,13 +27677,13 @@
         <v>249</v>
       </c>
       <c r="G784" s="4">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H784" s="4">
         <v>48</v>
       </c>
       <c r="I784" s="4">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="785" spans="1:9" x14ac:dyDescent="0.25">
@@ -28112,13 +28112,13 @@
         <v>74</v>
       </c>
       <c r="G799" s="4">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H799" s="4">
         <v>15</v>
       </c>
       <c r="I799" s="4">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="800" spans="1:9" x14ac:dyDescent="0.25">
@@ -28518,13 +28518,13 @@
         <v>46</v>
       </c>
       <c r="G813" s="4">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H813" s="4">
         <v>10</v>
       </c>
       <c r="I813" s="4">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="814" spans="1:9" x14ac:dyDescent="0.25">
@@ -28576,13 +28576,13 @@
         <v>144</v>
       </c>
       <c r="G815" s="4">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H815" s="4">
         <v>20</v>
       </c>
       <c r="I815" s="4">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="816" spans="1:9" x14ac:dyDescent="0.25">
@@ -28721,13 +28721,13 @@
         <v>1</v>
       </c>
       <c r="G820" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H820" s="4">
         <v>0</v>
       </c>
       <c r="I820" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="821" spans="1:9" x14ac:dyDescent="0.25">
@@ -28953,13 +28953,13 @@
         <v>111</v>
       </c>
       <c r="G828" s="4">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H828" s="4">
         <v>22</v>
       </c>
       <c r="I828" s="4">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="829" spans="1:9" x14ac:dyDescent="0.25">
@@ -29185,13 +29185,13 @@
         <v>53</v>
       </c>
       <c r="G836" s="4">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H836" s="4">
         <v>7</v>
       </c>
       <c r="I836" s="4">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="837" spans="1:9" x14ac:dyDescent="0.25">
@@ -29388,13 +29388,13 @@
         <v>81</v>
       </c>
       <c r="G843" s="4">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H843" s="4">
         <v>13</v>
       </c>
       <c r="I843" s="4">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="844" spans="1:9" x14ac:dyDescent="0.25">
@@ -29475,13 +29475,13 @@
         <v>143</v>
       </c>
       <c r="G846" s="4">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H846" s="4">
         <v>16</v>
       </c>
       <c r="I846" s="4">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="847" spans="1:9" x14ac:dyDescent="0.25">
@@ -29591,13 +29591,13 @@
         <v>65</v>
       </c>
       <c r="G850" s="4">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H850" s="4">
         <v>11</v>
       </c>
       <c r="I850" s="4">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="851" spans="1:9" x14ac:dyDescent="0.25">
@@ -29736,13 +29736,13 @@
         <v>26</v>
       </c>
       <c r="G855" s="4">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H855" s="4">
         <v>0</v>
       </c>
       <c r="I855" s="4">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="856" spans="1:9" x14ac:dyDescent="0.25">
@@ -29794,13 +29794,13 @@
         <v>107</v>
       </c>
       <c r="G857" s="4">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H857" s="4">
         <v>14</v>
       </c>
       <c r="I857" s="4">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="858" spans="1:9" x14ac:dyDescent="0.25">
@@ -30200,13 +30200,13 @@
         <v>23</v>
       </c>
       <c r="G871" s="4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H871" s="4">
         <v>6</v>
       </c>
       <c r="I871" s="4">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="872" spans="1:9" x14ac:dyDescent="0.25">
@@ -30345,13 +30345,13 @@
         <v>4</v>
       </c>
       <c r="G876" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H876" s="4">
         <v>0</v>
       </c>
       <c r="I876" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="877" spans="1:9" x14ac:dyDescent="0.25">
@@ -30461,13 +30461,13 @@
         <v>12</v>
       </c>
       <c r="G880" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H880" s="4">
         <v>1</v>
       </c>
       <c r="I880" s="4">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="881" spans="1:9" x14ac:dyDescent="0.25">
@@ -30809,13 +30809,13 @@
         <v>9</v>
       </c>
       <c r="G892" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H892" s="4">
         <v>1</v>
       </c>
       <c r="I892" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="893" spans="1:9" x14ac:dyDescent="0.25">
@@ -30954,13 +30954,13 @@
         <v>24</v>
       </c>
       <c r="G897" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H897" s="4">
         <v>5</v>
       </c>
       <c r="I897" s="4">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="898" spans="1:9" x14ac:dyDescent="0.25">
@@ -31186,13 +31186,13 @@
         <v>26</v>
       </c>
       <c r="G905" s="4">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H905" s="4">
         <v>1</v>
       </c>
       <c r="I905" s="4">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="906" spans="1:9" x14ac:dyDescent="0.25">
@@ -31215,13 +31215,13 @@
         <v>4</v>
       </c>
       <c r="G906" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H906" s="4">
         <v>0</v>
       </c>
       <c r="I906" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="907" spans="1:9" x14ac:dyDescent="0.25">
@@ -31476,13 +31476,13 @@
         <v>61</v>
       </c>
       <c r="G915" s="4">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H915" s="4">
         <v>5</v>
       </c>
       <c r="I915" s="4">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="916" spans="1:9" x14ac:dyDescent="0.25">
@@ -32201,13 +32201,13 @@
         <v>57</v>
       </c>
       <c r="G940" s="4">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H940" s="4">
         <v>11</v>
       </c>
       <c r="I940" s="4">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="941" spans="1:9" x14ac:dyDescent="0.25">
@@ -33535,13 +33535,13 @@
         <v>13</v>
       </c>
       <c r="G986" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H986" s="4">
         <v>3</v>
       </c>
       <c r="I986" s="4">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="987" spans="1:9" x14ac:dyDescent="0.25">
@@ -33738,13 +33738,13 @@
         <v>22</v>
       </c>
       <c r="G993" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H993" s="4">
         <v>5</v>
       </c>
       <c r="I993" s="4">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="994" spans="1:9" x14ac:dyDescent="0.25">
@@ -34173,13 +34173,13 @@
         <v>4</v>
       </c>
       <c r="G1008" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H1008" s="4">
         <v>0</v>
       </c>
       <c r="I1008" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1009" spans="1:9" x14ac:dyDescent="0.25">
@@ -34202,13 +34202,13 @@
         <v>23</v>
       </c>
       <c r="G1009" s="4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H1009" s="4">
         <v>4</v>
       </c>
       <c r="I1009" s="4">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="1010" spans="1:9" x14ac:dyDescent="0.25">
@@ -34608,13 +34608,13 @@
         <v>1</v>
       </c>
       <c r="G1023" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1023" s="4">
         <v>0</v>
       </c>
       <c r="I1023" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1024" spans="1:9" x14ac:dyDescent="0.25">
@@ -34811,13 +34811,13 @@
         <v>79</v>
       </c>
       <c r="G1030" s="4">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H1030" s="4">
         <v>13</v>
       </c>
       <c r="I1030" s="4">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="1031" spans="1:9" x14ac:dyDescent="0.25">
@@ -34927,13 +34927,13 @@
         <v>46</v>
       </c>
       <c r="G1034" s="4">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H1034" s="4">
         <v>5</v>
       </c>
       <c r="I1034" s="4">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="1035" spans="1:9" x14ac:dyDescent="0.25">
@@ -35478,13 +35478,13 @@
         <v>179</v>
       </c>
       <c r="G1053" s="4">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="H1053" s="4">
         <v>21</v>
       </c>
       <c r="I1053" s="4">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="1054" spans="1:9" x14ac:dyDescent="0.25">
@@ -35565,13 +35565,13 @@
         <v>124</v>
       </c>
       <c r="G1056" s="4">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H1056" s="4">
         <v>21</v>
       </c>
       <c r="I1056" s="4">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="1057" spans="1:9" x14ac:dyDescent="0.25">
@@ -36232,13 +36232,13 @@
         <v>50</v>
       </c>
       <c r="G1079" s="4">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H1079" s="4">
         <v>10</v>
       </c>
       <c r="I1079" s="4">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="1080" spans="1:9" x14ac:dyDescent="0.25">
@@ -36290,13 +36290,13 @@
         <v>47</v>
       </c>
       <c r="G1081" s="4">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H1081" s="4">
         <v>8</v>
       </c>
       <c r="I1081" s="4">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="1082" spans="1:9" x14ac:dyDescent="0.25">
@@ -37276,13 +37276,13 @@
         <v>55</v>
       </c>
       <c r="G1115" s="4">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H1115" s="4">
         <v>6</v>
       </c>
       <c r="I1115" s="4">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="1116" spans="1:9" x14ac:dyDescent="0.25">
@@ -37682,13 +37682,13 @@
         <v>84</v>
       </c>
       <c r="G1129" s="4">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H1129" s="4">
         <v>10</v>
       </c>
       <c r="I1129" s="4">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="1130" spans="1:9" x14ac:dyDescent="0.25">
@@ -37885,13 +37885,13 @@
         <v>18</v>
       </c>
       <c r="G1136" s="4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H1136" s="4">
         <v>0</v>
       </c>
       <c r="I1136" s="4">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1137" spans="1:9" x14ac:dyDescent="0.25">
@@ -38436,13 +38436,13 @@
         <v>65</v>
       </c>
       <c r="G1155" s="4">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H1155" s="4">
         <v>7</v>
       </c>
       <c r="I1155" s="4">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="1156" spans="1:9" x14ac:dyDescent="0.25">
@@ -38900,13 +38900,13 @@
         <v>167</v>
       </c>
       <c r="G1171" s="4">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H1171" s="4">
         <v>17</v>
       </c>
       <c r="I1171" s="4">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="1172" spans="1:9" x14ac:dyDescent="0.25">
@@ -39393,13 +39393,13 @@
         <v>60</v>
       </c>
       <c r="G1188" s="4">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H1188" s="4">
         <v>7</v>
       </c>
       <c r="I1188" s="4">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="1189" spans="1:9" x14ac:dyDescent="0.25">
@@ -39509,13 +39509,13 @@
         <v>97</v>
       </c>
       <c r="G1192" s="4">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H1192" s="4">
         <v>10</v>
       </c>
       <c r="I1192" s="4">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="1193" spans="1:9" x14ac:dyDescent="0.25">
@@ -40205,13 +40205,13 @@
         <v>120</v>
       </c>
       <c r="G1216" s="4">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H1216" s="4">
         <v>15</v>
       </c>
       <c r="I1216" s="4">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="1217" spans="1:9" x14ac:dyDescent="0.25">
@@ -40524,13 +40524,13 @@
         <v>215</v>
       </c>
       <c r="G1227" s="4">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H1227" s="4">
         <v>23</v>
       </c>
       <c r="I1227" s="4">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="1228" spans="1:9" x14ac:dyDescent="0.25">
@@ -41075,13 +41075,13 @@
         <v>19</v>
       </c>
       <c r="G1246" s="4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H1246" s="4">
         <v>2</v>
       </c>
       <c r="I1246" s="4">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1247" spans="1:9" x14ac:dyDescent="0.25">
@@ -41742,13 +41742,13 @@
         <v>15</v>
       </c>
       <c r="G1269" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H1269" s="4">
         <v>2</v>
       </c>
       <c r="I1269" s="4">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1270" spans="1:9" x14ac:dyDescent="0.25">
@@ -41858,13 +41858,13 @@
         <v>15</v>
       </c>
       <c r="G1273" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1273" s="4">
         <v>3</v>
       </c>
       <c r="I1273" s="4">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1274" spans="1:9" x14ac:dyDescent="0.25">
@@ -55198,13 +55198,13 @@
         <v>200</v>
       </c>
       <c r="G1733" s="4">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H1733" s="4">
         <v>21</v>
       </c>
       <c r="I1733" s="4">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="1734" spans="1:9" x14ac:dyDescent="0.25">

--- a/0. capaian omnibus 2026.xlsx
+++ b/0. capaian omnibus 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Downloads\0. Omnibus\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F177ED59-2B15-4AB5-BD4C-9AC854785BB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93877A21-4CC7-4DD6-98F6-DC5339F067DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-109" yWindow="-109" windowWidth="26301" windowHeight="15800" xr2:uid="{ABC9ECFA-347A-408B-B0D0-6F1CCFF80879}"/>
   </bookViews>

--- a/0. capaian omnibus 2026.xlsx
+++ b/0. capaian omnibus 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Downloads\0. Omnibus\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93877A21-4CC7-4DD6-98F6-DC5339F067DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E3C05A8-1524-4F15-A397-B805597689C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-109" yWindow="-109" windowWidth="26301" windowHeight="15800" xr2:uid="{ABC9ECFA-347A-408B-B0D0-6F1CCFF80879}"/>
   </bookViews>
@@ -12159,7 +12159,7 @@
         <v>21</v>
       </c>
       <c r="F249" s="4">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G249" s="4">
         <v>9</v>
@@ -12168,7 +12168,7 @@
         <v>12</v>
       </c>
       <c r="I249" s="4">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="250" spans="1:9" x14ac:dyDescent="0.25">
@@ -12246,7 +12246,7 @@
         <v>21</v>
       </c>
       <c r="F252" s="4">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G252" s="4">
         <v>2</v>
@@ -12255,7 +12255,7 @@
         <v>1</v>
       </c>
       <c r="I252" s="4">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="253" spans="1:9" x14ac:dyDescent="0.25">
@@ -13116,16 +13116,16 @@
         <v>24</v>
       </c>
       <c r="F282" s="4">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="G282" s="4">
         <v>9</v>
       </c>
       <c r="H282" s="4">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I282" s="4">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="283" spans="1:9" x14ac:dyDescent="0.25">
@@ -13203,16 +13203,16 @@
         <v>24</v>
       </c>
       <c r="F285" s="4">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="G285" s="4">
         <v>4</v>
       </c>
       <c r="H285" s="4">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I285" s="4">
-        <v>24</v>
+        <v>31</v>
       </c>
     </row>
     <row r="286" spans="1:9" x14ac:dyDescent="0.25">
@@ -13348,7 +13348,7 @@
         <v>25</v>
       </c>
       <c r="F290" s="4">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G290" s="4">
         <v>4</v>
@@ -13357,7 +13357,7 @@
         <v>1</v>
       </c>
       <c r="I290" s="4">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="291" spans="1:9" x14ac:dyDescent="0.25">
@@ -13464,7 +13464,7 @@
         <v>25</v>
       </c>
       <c r="F294" s="4">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="G294" s="4">
         <v>0</v>
@@ -13473,7 +13473,7 @@
         <v>6</v>
       </c>
       <c r="I294" s="4">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="295" spans="1:9" x14ac:dyDescent="0.25">
@@ -13580,7 +13580,7 @@
         <v>25</v>
       </c>
       <c r="F298" s="4">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G298" s="4">
         <v>2</v>
@@ -13589,7 +13589,7 @@
         <v>0</v>
       </c>
       <c r="I298" s="4">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="299" spans="1:9" x14ac:dyDescent="0.25">
@@ -15610,7 +15610,7 @@
         <v>31</v>
       </c>
       <c r="F368" s="4">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="G368" s="4">
         <v>3</v>
@@ -15619,7 +15619,7 @@
         <v>4</v>
       </c>
       <c r="I368" s="4">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="369" spans="1:9" x14ac:dyDescent="0.25">
@@ -15639,7 +15639,7 @@
         <v>31</v>
       </c>
       <c r="F369" s="4">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="G369" s="4">
         <v>10</v>
@@ -15648,7 +15648,7 @@
         <v>8</v>
       </c>
       <c r="I369" s="4">
-        <v>23</v>
+        <v>30</v>
       </c>
     </row>
     <row r="370" spans="1:9" x14ac:dyDescent="0.25">
@@ -15900,7 +15900,7 @@
         <v>32</v>
       </c>
       <c r="F378" s="4">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="G378" s="4">
         <v>9</v>
@@ -15909,7 +15909,7 @@
         <v>6</v>
       </c>
       <c r="I378" s="4">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="379" spans="1:9" x14ac:dyDescent="0.25">
@@ -15958,7 +15958,7 @@
         <v>32</v>
       </c>
       <c r="F380" s="4">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G380" s="4">
         <v>2</v>
@@ -15967,7 +15967,7 @@
         <v>2</v>
       </c>
       <c r="I380" s="4">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="381" spans="1:9" x14ac:dyDescent="0.25">
@@ -16045,7 +16045,7 @@
         <v>32</v>
       </c>
       <c r="F383" s="4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G383" s="4">
         <v>1</v>
@@ -16054,7 +16054,7 @@
         <v>0</v>
       </c>
       <c r="I383" s="4">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="384" spans="1:9" x14ac:dyDescent="0.25">
@@ -16219,7 +16219,7 @@
         <v>32</v>
       </c>
       <c r="F389" s="4">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G389" s="4">
         <v>0</v>
@@ -16228,7 +16228,7 @@
         <v>2</v>
       </c>
       <c r="I389" s="4">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="390" spans="1:9" x14ac:dyDescent="0.25">
@@ -16509,7 +16509,7 @@
         <v>33</v>
       </c>
       <c r="F399" s="4">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G399" s="4">
         <v>3</v>
@@ -16518,7 +16518,7 @@
         <v>1</v>
       </c>
       <c r="I399" s="4">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="400" spans="1:9" x14ac:dyDescent="0.25">
@@ -16596,7 +16596,7 @@
         <v>33</v>
       </c>
       <c r="F402" s="4">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="G402" s="4">
         <v>10</v>
@@ -16605,7 +16605,7 @@
         <v>14</v>
       </c>
       <c r="I402" s="4">
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
     <row r="403" spans="1:9" x14ac:dyDescent="0.25">
@@ -16799,7 +16799,7 @@
         <v>34</v>
       </c>
       <c r="F409" s="4">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G409" s="4">
         <v>10</v>
@@ -16808,7 +16808,7 @@
         <v>1</v>
       </c>
       <c r="I409" s="4">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="410" spans="1:9" x14ac:dyDescent="0.25">
@@ -16857,7 +16857,7 @@
         <v>34</v>
       </c>
       <c r="F411" s="4">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G411" s="4">
         <v>8</v>
@@ -16866,7 +16866,7 @@
         <v>0</v>
       </c>
       <c r="I411" s="4">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="412" spans="1:9" x14ac:dyDescent="0.25">
@@ -16944,7 +16944,7 @@
         <v>34</v>
       </c>
       <c r="F414" s="4">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G414" s="4">
         <v>1</v>
@@ -16953,7 +16953,7 @@
         <v>1</v>
       </c>
       <c r="I414" s="4">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="415" spans="1:9" x14ac:dyDescent="0.25">
@@ -16973,7 +16973,7 @@
         <v>34</v>
       </c>
       <c r="F415" s="4">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="G415" s="4">
         <v>7</v>
@@ -16982,7 +16982,7 @@
         <v>6</v>
       </c>
       <c r="I415" s="4">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="416" spans="1:9" x14ac:dyDescent="0.25">
@@ -17031,7 +17031,7 @@
         <v>34</v>
       </c>
       <c r="F417" s="4">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G417" s="4">
         <v>6</v>
@@ -17040,7 +17040,7 @@
         <v>7</v>
       </c>
       <c r="I417" s="4">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="418" spans="1:9" x14ac:dyDescent="0.25">
@@ -17089,7 +17089,7 @@
         <v>34</v>
       </c>
       <c r="F419" s="4">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="G419" s="4">
         <v>6</v>
@@ -17098,7 +17098,7 @@
         <v>1</v>
       </c>
       <c r="I419" s="4">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="420" spans="1:9" x14ac:dyDescent="0.25">
@@ -17321,16 +17321,16 @@
         <v>35</v>
       </c>
       <c r="F427" s="4">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="G427" s="4">
         <v>10</v>
       </c>
       <c r="H427" s="4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I427" s="4">
-        <v>19</v>
+        <v>12</v>
       </c>
     </row>
     <row r="428" spans="1:9" x14ac:dyDescent="0.25">
@@ -17350,16 +17350,16 @@
         <v>35</v>
       </c>
       <c r="F428" s="4">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="G428" s="4">
         <v>7</v>
       </c>
       <c r="H428" s="4">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="I428" s="4">
-        <v>25</v>
+        <v>32</v>
       </c>
     </row>
     <row r="429" spans="1:9" x14ac:dyDescent="0.25">
@@ -19670,7 +19670,7 @@
         <v>42</v>
       </c>
       <c r="F508" s="4">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G508" s="4">
         <v>10</v>
@@ -19679,7 +19679,7 @@
         <v>12</v>
       </c>
       <c r="I508" s="4">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
     <row r="509" spans="1:9" x14ac:dyDescent="0.25">
@@ -19786,16 +19786,16 @@
         <v>42</v>
       </c>
       <c r="F512" s="4">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="G512" s="4">
         <v>6</v>
       </c>
       <c r="H512" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I512" s="4">
-        <v>18</v>
+        <v>13</v>
       </c>
     </row>
     <row r="513" spans="1:9" x14ac:dyDescent="0.25">
@@ -19815,16 +19815,16 @@
         <v>42</v>
       </c>
       <c r="F513" s="4">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G513" s="4">
         <v>14</v>
       </c>
       <c r="H513" s="4">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I513" s="4">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="514" spans="1:9" x14ac:dyDescent="0.25">
@@ -20685,7 +20685,7 @@
         <v>45</v>
       </c>
       <c r="F543" s="4">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="G543" s="4">
         <v>12</v>
@@ -20694,7 +20694,7 @@
         <v>12</v>
       </c>
       <c r="I543" s="4">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="544" spans="1:9" x14ac:dyDescent="0.25">
@@ -20714,7 +20714,7 @@
         <v>45</v>
       </c>
       <c r="F544" s="4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G544" s="4">
         <v>2</v>
@@ -20723,7 +20723,7 @@
         <v>3</v>
       </c>
       <c r="I544" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="545" spans="1:9" x14ac:dyDescent="0.25">
@@ -20772,7 +20772,7 @@
         <v>45</v>
       </c>
       <c r="F546" s="4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G546" s="4">
         <v>0</v>
@@ -20781,7 +20781,7 @@
         <v>1</v>
       </c>
       <c r="I546" s="4">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="547" spans="1:9" x14ac:dyDescent="0.25">
@@ -20859,7 +20859,7 @@
         <v>45</v>
       </c>
       <c r="F549" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G549" s="4">
         <v>2</v>
@@ -20868,7 +20868,7 @@
         <v>1</v>
       </c>
       <c r="I549" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="550" spans="1:9" x14ac:dyDescent="0.25">
@@ -23295,7 +23295,7 @@
         <v>52</v>
       </c>
       <c r="F633" s="4">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G633" s="4">
         <v>4</v>
@@ -23304,7 +23304,7 @@
         <v>2</v>
       </c>
       <c r="I633" s="4">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="634" spans="1:9" x14ac:dyDescent="0.25">
@@ -23469,16 +23469,16 @@
         <v>52</v>
       </c>
       <c r="F639" s="4">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G639" s="4">
         <v>3</v>
       </c>
       <c r="H639" s="4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I639" s="4">
-        <v>27</v>
+        <v>32</v>
       </c>
     </row>
     <row r="640" spans="1:9" x14ac:dyDescent="0.25">
@@ -23527,16 +23527,16 @@
         <v>52</v>
       </c>
       <c r="F641" s="4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G641" s="4">
         <v>3</v>
       </c>
       <c r="H641" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I641" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="642" spans="1:9" x14ac:dyDescent="0.25">
@@ -25992,16 +25992,16 @@
         <v>60</v>
       </c>
       <c r="F726" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G726" s="4">
         <v>1</v>
       </c>
       <c r="H726" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I726" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="727" spans="1:9" x14ac:dyDescent="0.25">
@@ -26050,7 +26050,7 @@
         <v>60</v>
       </c>
       <c r="F728" s="4">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="G728" s="4">
         <v>8</v>
@@ -26059,7 +26059,7 @@
         <v>1</v>
       </c>
       <c r="I728" s="4">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="729" spans="1:9" x14ac:dyDescent="0.25">
@@ -26108,16 +26108,16 @@
         <v>60</v>
       </c>
       <c r="F730" s="4">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="G730" s="4">
         <v>6</v>
       </c>
       <c r="H730" s="4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I730" s="4">
-        <v>23</v>
+        <v>30</v>
       </c>
     </row>
     <row r="731" spans="1:9" x14ac:dyDescent="0.25">
@@ -26224,7 +26224,7 @@
         <v>60</v>
       </c>
       <c r="F734" s="4">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G734" s="4">
         <v>5</v>
@@ -26233,7 +26233,7 @@
         <v>2</v>
       </c>
       <c r="I734" s="4">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="735" spans="1:9" x14ac:dyDescent="0.25">
@@ -31183,16 +31183,16 @@
         <v>78</v>
       </c>
       <c r="F905" s="4">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G905" s="4">
         <v>12</v>
       </c>
       <c r="H905" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I905" s="4">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="906" spans="1:9" x14ac:dyDescent="0.25">
@@ -31241,16 +31241,16 @@
         <v>78</v>
       </c>
       <c r="F907" s="4">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G907" s="4">
         <v>12</v>
       </c>
       <c r="H907" s="4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I907" s="4">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="908" spans="1:9" x14ac:dyDescent="0.25">
@@ -31270,16 +31270,16 @@
         <v>78</v>
       </c>
       <c r="F908" s="4">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="G908" s="4">
         <v>7</v>
       </c>
       <c r="H908" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I908" s="4">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="909" spans="1:9" x14ac:dyDescent="0.25">
@@ -31328,16 +31328,16 @@
         <v>78</v>
       </c>
       <c r="F910" s="4">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G910" s="4">
         <v>6</v>
       </c>
       <c r="H910" s="4">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I910" s="4">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="911" spans="1:9" x14ac:dyDescent="0.25">
@@ -32430,7 +32430,7 @@
         <v>81</v>
       </c>
       <c r="F948" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G948" s="4">
         <v>0</v>
@@ -32439,7 +32439,7 @@
         <v>0</v>
       </c>
       <c r="I948" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="949" spans="1:9" x14ac:dyDescent="0.25">
@@ -32488,16 +32488,16 @@
         <v>81</v>
       </c>
       <c r="F950" s="4">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="G950" s="4">
         <v>7</v>
       </c>
       <c r="H950" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I950" s="4">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="951" spans="1:9" x14ac:dyDescent="0.25">
@@ -32662,16 +32662,16 @@
         <v>81</v>
       </c>
       <c r="F956" s="4">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="G956" s="4">
         <v>10</v>
       </c>
       <c r="H956" s="4">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I956" s="4">
-        <v>23</v>
+        <v>30</v>
       </c>
     </row>
     <row r="957" spans="1:9" x14ac:dyDescent="0.25">
@@ -32691,7 +32691,7 @@
         <v>81</v>
       </c>
       <c r="F957" s="4">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G957" s="4">
         <v>5</v>
@@ -32700,7 +32700,7 @@
         <v>1</v>
       </c>
       <c r="I957" s="4">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="958" spans="1:9" x14ac:dyDescent="0.25">

--- a/0. capaian omnibus 2026.xlsx
+++ b/0. capaian omnibus 2026.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Downloads\0. Omnibus\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\0. codex\0. Omnibus\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E3C05A8-1524-4F15-A397-B805597689C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADBE3B23-509A-4025-AB8D-77BB2D305D6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-109" yWindow="-109" windowWidth="26301" windowHeight="15800" xr2:uid="{ABC9ECFA-347A-408B-B0D0-6F1CCFF80879}"/>
   </bookViews>
@@ -5431,16 +5431,16 @@
         <v>2</v>
       </c>
       <c r="F17" s="4">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G17" s="4">
         <v>10</v>
       </c>
       <c r="H17" s="4">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I17" s="4">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
@@ -9549,16 +9549,16 @@
         <v>13</v>
       </c>
       <c r="F159" s="4">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G159" s="4">
         <v>11</v>
       </c>
       <c r="H159" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I159" s="4">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="160" spans="1:9" x14ac:dyDescent="0.25">
@@ -10477,16 +10477,16 @@
         <v>16</v>
       </c>
       <c r="F191" s="4">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G191" s="4">
         <v>4</v>
       </c>
       <c r="H191" s="4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I191" s="4">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="192" spans="1:9" x14ac:dyDescent="0.25">
@@ -11144,16 +11144,16 @@
         <v>18</v>
       </c>
       <c r="F214" s="4">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G214" s="4">
         <v>8</v>
       </c>
       <c r="H214" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I214" s="4">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="215" spans="1:9" x14ac:dyDescent="0.25">
@@ -11695,16 +11695,16 @@
         <v>19</v>
       </c>
       <c r="F233" s="4">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G233" s="4">
         <v>2</v>
       </c>
       <c r="H233" s="4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I233" s="4">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="234" spans="1:9" x14ac:dyDescent="0.25">
@@ -12159,16 +12159,16 @@
         <v>21</v>
       </c>
       <c r="F249" s="4">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G249" s="4">
         <v>9</v>
       </c>
       <c r="H249" s="4">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I249" s="4">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="250" spans="1:9" x14ac:dyDescent="0.25">
@@ -13464,16 +13464,16 @@
         <v>25</v>
       </c>
       <c r="F294" s="4">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G294" s="4">
         <v>0</v>
       </c>
       <c r="H294" s="4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I294" s="4">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="295" spans="1:9" x14ac:dyDescent="0.25">
@@ -13522,16 +13522,16 @@
         <v>25</v>
       </c>
       <c r="F296" s="4">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G296" s="4">
         <v>7</v>
       </c>
       <c r="H296" s="4">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I296" s="4">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="297" spans="1:9" x14ac:dyDescent="0.25">
@@ -15639,16 +15639,16 @@
         <v>31</v>
       </c>
       <c r="F369" s="4">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G369" s="4">
         <v>10</v>
       </c>
       <c r="H369" s="4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I369" s="4">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="370" spans="1:9" x14ac:dyDescent="0.25">
@@ -15900,16 +15900,16 @@
         <v>32</v>
       </c>
       <c r="F378" s="4">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G378" s="4">
         <v>9</v>
       </c>
       <c r="H378" s="4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I378" s="4">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="379" spans="1:9" x14ac:dyDescent="0.25">
@@ -16277,16 +16277,16 @@
         <v>33</v>
       </c>
       <c r="F391" s="4">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G391" s="4">
         <v>4</v>
       </c>
       <c r="H391" s="4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I391" s="4">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="392" spans="1:9" x14ac:dyDescent="0.25">
@@ -16799,16 +16799,16 @@
         <v>34</v>
       </c>
       <c r="F409" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G409" s="4">
         <v>10</v>
       </c>
       <c r="H409" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I409" s="4">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="410" spans="1:9" x14ac:dyDescent="0.25">
@@ -16973,16 +16973,16 @@
         <v>34</v>
       </c>
       <c r="F415" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G415" s="4">
         <v>7</v>
       </c>
       <c r="H415" s="4">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I415" s="4">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="416" spans="1:9" x14ac:dyDescent="0.25">
@@ -17031,16 +17031,16 @@
         <v>34</v>
       </c>
       <c r="F417" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G417" s="4">
         <v>6</v>
       </c>
       <c r="H417" s="4">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I417" s="4">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="418" spans="1:9" x14ac:dyDescent="0.25">
@@ -17350,16 +17350,16 @@
         <v>35</v>
       </c>
       <c r="F428" s="4">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G428" s="4">
         <v>7</v>
       </c>
       <c r="H428" s="4">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I428" s="4">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="429" spans="1:9" x14ac:dyDescent="0.25">
@@ -17698,16 +17698,16 @@
         <v>36</v>
       </c>
       <c r="F440" s="4">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G440" s="4">
         <v>20</v>
       </c>
       <c r="H440" s="4">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I440" s="4">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="441" spans="1:9" x14ac:dyDescent="0.25">
@@ -18220,16 +18220,16 @@
         <v>37</v>
       </c>
       <c r="F458" s="4">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G458" s="4">
         <v>12</v>
       </c>
       <c r="H458" s="4">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I458" s="4">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="459" spans="1:9" x14ac:dyDescent="0.25">
@@ -18423,16 +18423,16 @@
         <v>38</v>
       </c>
       <c r="F465" s="4">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G465" s="4">
         <v>13</v>
       </c>
       <c r="H465" s="4">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I465" s="4">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="466" spans="1:9" x14ac:dyDescent="0.25">
@@ -18539,16 +18539,16 @@
         <v>38</v>
       </c>
       <c r="F469" s="4">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G469" s="4">
         <v>8</v>
       </c>
       <c r="H469" s="4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I469" s="4">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="470" spans="1:9" x14ac:dyDescent="0.25">
@@ -18626,16 +18626,16 @@
         <v>39</v>
       </c>
       <c r="F472" s="4">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G472" s="4">
         <v>7</v>
       </c>
       <c r="H472" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I472" s="4">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="473" spans="1:9" x14ac:dyDescent="0.25">
@@ -19090,16 +19090,16 @@
         <v>40</v>
       </c>
       <c r="F488" s="4">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G488" s="4">
         <v>5</v>
       </c>
       <c r="H488" s="4">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I488" s="4">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="489" spans="1:9" x14ac:dyDescent="0.25">
@@ -19409,16 +19409,16 @@
         <v>41</v>
       </c>
       <c r="F499" s="4">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G499" s="4">
         <v>12</v>
       </c>
       <c r="H499" s="4">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I499" s="4">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="500" spans="1:9" x14ac:dyDescent="0.25">
@@ -19670,16 +19670,16 @@
         <v>42</v>
       </c>
       <c r="F508" s="4">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G508" s="4">
         <v>10</v>
       </c>
       <c r="H508" s="4">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I508" s="4">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="509" spans="1:9" x14ac:dyDescent="0.25">
@@ -19815,16 +19815,16 @@
         <v>42</v>
       </c>
       <c r="F513" s="4">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G513" s="4">
         <v>14</v>
       </c>
       <c r="H513" s="4">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I513" s="4">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="514" spans="1:9" x14ac:dyDescent="0.25">
@@ -19960,16 +19960,16 @@
         <v>43</v>
       </c>
       <c r="F518" s="4">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G518" s="4">
         <v>7</v>
       </c>
       <c r="H518" s="4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I518" s="4">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="519" spans="1:9" x14ac:dyDescent="0.25">
@@ -20134,16 +20134,16 @@
         <v>43</v>
       </c>
       <c r="F524" s="4">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G524" s="4">
         <v>10</v>
       </c>
       <c r="H524" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I524" s="4">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="525" spans="1:9" x14ac:dyDescent="0.25">
@@ -20685,16 +20685,16 @@
         <v>45</v>
       </c>
       <c r="F543" s="4">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="G543" s="4">
         <v>12</v>
       </c>
       <c r="H543" s="4">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I543" s="4">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="544" spans="1:9" x14ac:dyDescent="0.25">
@@ -20743,16 +20743,16 @@
         <v>45</v>
       </c>
       <c r="F545" s="4">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G545" s="4">
         <v>43</v>
       </c>
       <c r="H545" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I545" s="4">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="546" spans="1:9" x14ac:dyDescent="0.25">
@@ -21004,16 +21004,16 @@
         <v>46</v>
       </c>
       <c r="F554" s="4">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G554" s="4">
         <v>3</v>
       </c>
       <c r="H554" s="4">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I554" s="4">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="555" spans="1:9" x14ac:dyDescent="0.25">
@@ -21642,16 +21642,16 @@
         <v>47</v>
       </c>
       <c r="F576" s="4">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G576" s="4">
         <v>17</v>
       </c>
       <c r="H576" s="4">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I576" s="4">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="577" spans="1:9" x14ac:dyDescent="0.25">
@@ -21758,16 +21758,16 @@
         <v>48</v>
       </c>
       <c r="F580" s="4">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="G580" s="4">
         <v>15</v>
       </c>
       <c r="H580" s="4">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I580" s="4">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="581" spans="1:9" x14ac:dyDescent="0.25">
@@ -22164,16 +22164,16 @@
         <v>49</v>
       </c>
       <c r="F594" s="4">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G594" s="4">
         <v>0</v>
       </c>
       <c r="H594" s="4">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I594" s="4">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="595" spans="1:9" x14ac:dyDescent="0.25">
@@ -22193,16 +22193,16 @@
         <v>49</v>
       </c>
       <c r="F595" s="4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G595" s="4">
         <v>0</v>
       </c>
       <c r="H595" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I595" s="4">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="596" spans="1:9" x14ac:dyDescent="0.25">
@@ -22541,16 +22541,16 @@
         <v>50</v>
       </c>
       <c r="F607" s="4">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G607" s="4">
         <v>10</v>
       </c>
       <c r="H607" s="4">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I607" s="4">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="608" spans="1:9" x14ac:dyDescent="0.25">
@@ -23469,16 +23469,16 @@
         <v>52</v>
       </c>
       <c r="F639" s="4">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G639" s="4">
         <v>3</v>
       </c>
       <c r="H639" s="4">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I639" s="4">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="640" spans="1:9" x14ac:dyDescent="0.25">
@@ -24107,16 +24107,16 @@
         <v>54</v>
       </c>
       <c r="F661" s="4">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G661" s="4">
         <v>12</v>
       </c>
       <c r="H661" s="4">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I661" s="4">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="662" spans="1:9" x14ac:dyDescent="0.25">
@@ -24658,16 +24658,16 @@
         <v>56</v>
       </c>
       <c r="F680" s="4">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G680" s="4">
         <v>6</v>
       </c>
       <c r="H680" s="4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I680" s="4">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="681" spans="1:9" x14ac:dyDescent="0.25">
@@ -24716,16 +24716,16 @@
         <v>56</v>
       </c>
       <c r="F682" s="4">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G682" s="4">
         <v>15</v>
       </c>
       <c r="H682" s="4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I682" s="4">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="683" spans="1:9" x14ac:dyDescent="0.25">
@@ -24948,16 +24948,16 @@
         <v>57</v>
       </c>
       <c r="F690" s="4">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G690" s="4">
         <v>1</v>
       </c>
       <c r="H690" s="4">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I690" s="4">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="691" spans="1:9" x14ac:dyDescent="0.25">
@@ -25035,16 +25035,16 @@
         <v>57</v>
       </c>
       <c r="F693" s="4">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G693" s="4">
         <v>5</v>
       </c>
       <c r="H693" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I693" s="4">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="694" spans="1:9" x14ac:dyDescent="0.25">
@@ -25615,16 +25615,16 @@
         <v>59</v>
       </c>
       <c r="F713" s="4">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G713" s="4">
         <v>14</v>
       </c>
       <c r="H713" s="4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I713" s="4">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="714" spans="1:9" x14ac:dyDescent="0.25">
@@ -25760,16 +25760,16 @@
         <v>59</v>
       </c>
       <c r="F718" s="4">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G718" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H718" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I718" s="4">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="719" spans="1:9" x14ac:dyDescent="0.25">
@@ -26108,16 +26108,16 @@
         <v>60</v>
       </c>
       <c r="F730" s="4">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G730" s="4">
         <v>6</v>
       </c>
       <c r="H730" s="4">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I730" s="4">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="731" spans="1:9" x14ac:dyDescent="0.25">
@@ -26282,16 +26282,16 @@
         <v>61</v>
       </c>
       <c r="F736" s="4">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G736" s="4">
         <v>15</v>
       </c>
       <c r="H736" s="4">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I736" s="4">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="737" spans="1:9" x14ac:dyDescent="0.25">
@@ -26572,16 +26572,16 @@
         <v>62</v>
       </c>
       <c r="F746" s="4">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G746" s="4">
         <v>9</v>
       </c>
       <c r="H746" s="4">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I746" s="4">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="747" spans="1:9" x14ac:dyDescent="0.25">
@@ -26659,16 +26659,16 @@
         <v>62</v>
       </c>
       <c r="F749" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G749" s="4">
         <v>2</v>
       </c>
       <c r="H749" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I749" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="750" spans="1:9" x14ac:dyDescent="0.25">
@@ -27007,16 +27007,16 @@
         <v>63</v>
       </c>
       <c r="F761" s="4">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G761" s="4">
         <v>3</v>
       </c>
       <c r="H761" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I761" s="4">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="762" spans="1:9" x14ac:dyDescent="0.25">
@@ -27065,16 +27065,16 @@
         <v>63</v>
       </c>
       <c r="F763" s="4">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G763" s="4">
         <v>6</v>
       </c>
       <c r="H763" s="4">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I763" s="4">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="764" spans="1:9" x14ac:dyDescent="0.25">
@@ -27268,16 +27268,16 @@
         <v>64</v>
       </c>
       <c r="F770" s="4">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G770" s="4">
         <v>9</v>
       </c>
       <c r="H770" s="4">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I770" s="4">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="771" spans="1:9" x14ac:dyDescent="0.25">
@@ -27645,16 +27645,16 @@
         <v>65</v>
       </c>
       <c r="F783" s="4">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G783" s="4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H783" s="4">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I783" s="4">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="784" spans="1:9" x14ac:dyDescent="0.25">
@@ -27790,16 +27790,16 @@
         <v>66</v>
       </c>
       <c r="F788" s="4">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G788" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H788" s="4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I788" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="789" spans="1:9" x14ac:dyDescent="0.25">
@@ -28225,16 +28225,16 @@
         <v>67</v>
       </c>
       <c r="F803" s="4">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G803" s="4">
+        <v>11</v>
+      </c>
+      <c r="H803" s="4">
         <v>10</v>
       </c>
-      <c r="H803" s="4">
-        <v>8</v>
-      </c>
       <c r="I803" s="4">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="804" spans="1:9" x14ac:dyDescent="0.25">
@@ -28602,16 +28602,16 @@
         <v>68</v>
       </c>
       <c r="F816" s="4">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G816" s="4">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H816" s="4">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I816" s="4">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="817" spans="1:9" x14ac:dyDescent="0.25">
@@ -28834,16 +28834,16 @@
         <v>68</v>
       </c>
       <c r="F824" s="4">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G824" s="4">
         <v>8</v>
       </c>
       <c r="H824" s="4">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I824" s="4">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="825" spans="1:9" x14ac:dyDescent="0.25">
@@ -29240,16 +29240,16 @@
         <v>70</v>
       </c>
       <c r="F838" s="4">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="G838" s="4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H838" s="4">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I838" s="4">
-        <v>38</v>
+        <v>43</v>
       </c>
     </row>
     <row r="839" spans="1:9" x14ac:dyDescent="0.25">
@@ -29385,16 +29385,16 @@
         <v>71</v>
       </c>
       <c r="F843" s="4">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G843" s="4">
         <v>23</v>
       </c>
       <c r="H843" s="4">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I843" s="4">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="844" spans="1:9" x14ac:dyDescent="0.25">
@@ -29414,16 +29414,16 @@
         <v>71</v>
       </c>
       <c r="F844" s="4">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G844" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H844" s="4">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I844" s="4">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="845" spans="1:9" x14ac:dyDescent="0.25">
@@ -29617,16 +29617,16 @@
         <v>72</v>
       </c>
       <c r="F851" s="4">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G851" s="4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H851" s="4">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I851" s="4">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="852" spans="1:9" x14ac:dyDescent="0.25">
@@ -29849,16 +29849,16 @@
         <v>73</v>
       </c>
       <c r="F859" s="4">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G859" s="4">
         <v>10</v>
       </c>
       <c r="H859" s="4">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I859" s="4">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="860" spans="1:9" x14ac:dyDescent="0.25">
@@ -29907,13 +29907,13 @@
         <v>73</v>
       </c>
       <c r="F861" s="4">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G861" s="4">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H861" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I861" s="4">
         <v>16</v>
@@ -29994,16 +29994,16 @@
         <v>74</v>
       </c>
       <c r="F864" s="4">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G864" s="4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H864" s="4">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I864" s="4">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="865" spans="1:9" x14ac:dyDescent="0.25">
@@ -30197,16 +30197,16 @@
         <v>75</v>
       </c>
       <c r="F871" s="4">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="G871" s="4">
         <v>5</v>
       </c>
       <c r="H871" s="4">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I871" s="4">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="872" spans="1:9" x14ac:dyDescent="0.25">
@@ -30574,16 +30574,16 @@
         <v>76</v>
       </c>
       <c r="F884" s="4">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G884" s="4">
         <v>3</v>
       </c>
       <c r="H884" s="4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I884" s="4">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="885" spans="1:9" x14ac:dyDescent="0.25">
@@ -30980,16 +30980,16 @@
         <v>77</v>
       </c>
       <c r="F898" s="4">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G898" s="4">
         <v>13</v>
       </c>
       <c r="H898" s="4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I898" s="4">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="899" spans="1:9" x14ac:dyDescent="0.25">
@@ -31241,16 +31241,16 @@
         <v>78</v>
       </c>
       <c r="F907" s="4">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="G907" s="4">
         <v>12</v>
       </c>
       <c r="H907" s="4">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="I907" s="4">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="908" spans="1:9" x14ac:dyDescent="0.25">
@@ -31734,16 +31734,16 @@
         <v>79</v>
       </c>
       <c r="F924" s="4">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G924" s="4">
         <v>4</v>
       </c>
       <c r="H924" s="4">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I924" s="4">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="925" spans="1:9" x14ac:dyDescent="0.25">
@@ -31821,16 +31821,16 @@
         <v>79</v>
       </c>
       <c r="F927" s="4">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G927" s="4">
         <v>12</v>
       </c>
       <c r="H927" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I927" s="4">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="928" spans="1:9" x14ac:dyDescent="0.25">
@@ -32198,16 +32198,16 @@
         <v>80</v>
       </c>
       <c r="F940" s="4">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G940" s="4">
         <v>19</v>
       </c>
       <c r="H940" s="4">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="I940" s="4">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="941" spans="1:9" x14ac:dyDescent="0.25">
@@ -32546,16 +32546,16 @@
         <v>81</v>
       </c>
       <c r="F952" s="4">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G952" s="4">
         <v>37</v>
       </c>
       <c r="H952" s="4">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I952" s="4">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="953" spans="1:9" x14ac:dyDescent="0.25">
@@ -32662,16 +32662,16 @@
         <v>81</v>
       </c>
       <c r="F956" s="4">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G956" s="4">
         <v>10</v>
       </c>
       <c r="H956" s="4">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I956" s="4">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="957" spans="1:9" x14ac:dyDescent="0.25">
@@ -32778,16 +32778,16 @@
         <v>82</v>
       </c>
       <c r="F960" s="4">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G960" s="4">
         <v>15</v>
       </c>
       <c r="H960" s="4">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I960" s="4">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="961" spans="1:9" x14ac:dyDescent="0.25">
@@ -33271,16 +33271,16 @@
         <v>82</v>
       </c>
       <c r="F977" s="4">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G977" s="4">
         <v>9</v>
       </c>
       <c r="H977" s="4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I977" s="4">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="978" spans="1:9" x14ac:dyDescent="0.25">
@@ -33387,16 +33387,16 @@
         <v>83</v>
       </c>
       <c r="F981" s="4">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G981" s="4">
         <v>22</v>
       </c>
       <c r="H981" s="4">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I981" s="4">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="982" spans="1:9" x14ac:dyDescent="0.25">
@@ -33416,16 +33416,16 @@
         <v>83</v>
       </c>
       <c r="F982" s="4">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G982" s="4">
         <v>9</v>
       </c>
       <c r="H982" s="4">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I982" s="4">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="983" spans="1:9" x14ac:dyDescent="0.25">
@@ -33793,16 +33793,16 @@
         <v>84</v>
       </c>
       <c r="F995" s="4">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G995" s="4">
         <v>22</v>
       </c>
       <c r="H995" s="4">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I995" s="4">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="996" spans="1:9" x14ac:dyDescent="0.25">
@@ -33822,16 +33822,16 @@
         <v>84</v>
       </c>
       <c r="F996" s="4">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G996" s="4">
         <v>8</v>
       </c>
       <c r="H996" s="4">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I996" s="4">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="997" spans="1:9" x14ac:dyDescent="0.25">
@@ -34199,16 +34199,16 @@
         <v>85</v>
       </c>
       <c r="F1009" s="4">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G1009" s="4">
         <v>5</v>
       </c>
       <c r="H1009" s="4">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I1009" s="4">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1010" spans="1:9" x14ac:dyDescent="0.25">
@@ -34373,16 +34373,16 @@
         <v>85</v>
       </c>
       <c r="F1015" s="4">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G1015" s="4">
         <v>9</v>
       </c>
       <c r="H1015" s="4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I1015" s="4">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="1016" spans="1:9" x14ac:dyDescent="0.25">
@@ -34924,16 +34924,16 @@
         <v>86</v>
       </c>
       <c r="F1034" s="4">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G1034" s="4">
         <v>14</v>
       </c>
       <c r="H1034" s="4">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I1034" s="4">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="1035" spans="1:9" x14ac:dyDescent="0.25">
@@ -35214,16 +35214,16 @@
         <v>87</v>
       </c>
       <c r="F1044" s="4">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G1044" s="4">
         <v>2</v>
       </c>
       <c r="H1044" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I1044" s="4">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1045" spans="1:9" x14ac:dyDescent="0.25">
@@ -35446,16 +35446,16 @@
         <v>87</v>
       </c>
       <c r="F1052" s="4">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G1052" s="4">
         <v>13</v>
       </c>
       <c r="H1052" s="4">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I1052" s="4">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="1053" spans="1:9" x14ac:dyDescent="0.25">
@@ -35678,16 +35678,16 @@
         <v>88</v>
       </c>
       <c r="F1060" s="4">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G1060" s="4">
         <v>11</v>
       </c>
       <c r="H1060" s="4">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I1060" s="4">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="1061" spans="1:9" x14ac:dyDescent="0.25">
@@ -35968,16 +35968,16 @@
         <v>89</v>
       </c>
       <c r="F1070" s="4">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G1070" s="4">
         <v>4</v>
       </c>
       <c r="H1070" s="4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I1070" s="4">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1071" spans="1:9" x14ac:dyDescent="0.25">
@@ -36229,16 +36229,16 @@
         <v>90</v>
       </c>
       <c r="F1079" s="4">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G1079" s="4">
         <v>16</v>
       </c>
       <c r="H1079" s="4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I1079" s="4">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1080" spans="1:9" x14ac:dyDescent="0.25">
@@ -36287,16 +36287,16 @@
         <v>90</v>
       </c>
       <c r="F1081" s="4">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G1081" s="4">
         <v>18</v>
       </c>
       <c r="H1081" s="4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I1081" s="4">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="1082" spans="1:9" x14ac:dyDescent="0.25">
@@ -36345,16 +36345,16 @@
         <v>91</v>
       </c>
       <c r="F1083" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G1083" s="4">
         <v>6</v>
       </c>
       <c r="H1083" s="4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I1083" s="4">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="1084" spans="1:9" x14ac:dyDescent="0.25">
@@ -36461,16 +36461,16 @@
         <v>91</v>
       </c>
       <c r="F1087" s="4">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G1087" s="4">
         <v>15</v>
       </c>
       <c r="H1087" s="4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I1087" s="4">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="1088" spans="1:9" x14ac:dyDescent="0.25">
@@ -36896,16 +36896,16 @@
         <v>92</v>
       </c>
       <c r="F1102" s="4">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G1102" s="4">
         <v>5</v>
       </c>
       <c r="H1102" s="4">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I1102" s="4">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="1103" spans="1:9" x14ac:dyDescent="0.25">
@@ -37679,16 +37679,16 @@
         <v>94</v>
       </c>
       <c r="F1129" s="4">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G1129" s="4">
         <v>22</v>
       </c>
       <c r="H1129" s="4">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I1129" s="4">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="1130" spans="1:9" x14ac:dyDescent="0.25">
@@ -38085,16 +38085,16 @@
         <v>95</v>
       </c>
       <c r="F1143" s="4">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G1143" s="4">
         <v>10</v>
       </c>
       <c r="H1143" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I1143" s="4">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="1144" spans="1:9" x14ac:dyDescent="0.25">
@@ -38201,16 +38201,16 @@
         <v>95</v>
       </c>
       <c r="F1147" s="4">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G1147" s="4">
         <v>13</v>
       </c>
       <c r="H1147" s="4">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I1147" s="4">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="1148" spans="1:9" x14ac:dyDescent="0.25">
@@ -38636,16 +38636,16 @@
         <v>96</v>
       </c>
       <c r="F1162" s="4">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G1162" s="4">
         <v>7</v>
       </c>
       <c r="H1162" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I1162" s="4">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="1163" spans="1:9" x14ac:dyDescent="0.25">
@@ -39042,16 +39042,16 @@
         <v>97</v>
       </c>
       <c r="F1176" s="4">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G1176" s="4">
         <v>6</v>
       </c>
       <c r="H1176" s="4">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I1176" s="4">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="1177" spans="1:9" x14ac:dyDescent="0.25">
@@ -39303,16 +39303,16 @@
         <v>98</v>
       </c>
       <c r="F1185" s="4">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G1185" s="4">
         <v>7</v>
       </c>
       <c r="H1185" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I1185" s="4">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="1186" spans="1:9" x14ac:dyDescent="0.25">
@@ -39361,16 +39361,16 @@
         <v>98</v>
       </c>
       <c r="F1187" s="4">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G1187" s="4">
         <v>6</v>
       </c>
       <c r="H1187" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I1187" s="4">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="1188" spans="1:9" x14ac:dyDescent="0.25">
@@ -39622,16 +39622,16 @@
         <v>99</v>
       </c>
       <c r="F1196" s="4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G1196" s="4">
         <v>1</v>
       </c>
       <c r="H1196" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I1196" s="4">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1197" spans="1:9" x14ac:dyDescent="0.25">
@@ -39738,16 +39738,16 @@
         <v>99</v>
       </c>
       <c r="F1200" s="4">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G1200" s="4">
         <v>5</v>
       </c>
       <c r="H1200" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I1200" s="4">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1201" spans="1:9" x14ac:dyDescent="0.25">
@@ -40086,16 +40086,16 @@
         <v>101</v>
       </c>
       <c r="F1212" s="4">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="G1212" s="4">
         <v>30</v>
       </c>
       <c r="H1212" s="4">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I1212" s="4">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="1213" spans="1:9" x14ac:dyDescent="0.25">
@@ -40115,16 +40115,16 @@
         <v>101</v>
       </c>
       <c r="F1213" s="4">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G1213" s="4">
         <v>0</v>
       </c>
       <c r="H1213" s="4">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I1213" s="4">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1214" spans="1:9" x14ac:dyDescent="0.25">
@@ -40202,16 +40202,16 @@
         <v>101</v>
       </c>
       <c r="F1216" s="4">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="G1216" s="4">
         <v>33</v>
       </c>
       <c r="H1216" s="4">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="I1216" s="4">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="1217" spans="1:9" x14ac:dyDescent="0.25">
@@ -40521,16 +40521,16 @@
         <v>103</v>
       </c>
       <c r="F1227" s="4">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="G1227" s="4">
         <v>65</v>
       </c>
       <c r="H1227" s="4">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I1227" s="4">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="1228" spans="1:9" x14ac:dyDescent="0.25">
@@ -40550,16 +40550,16 @@
         <v>103</v>
       </c>
       <c r="F1228" s="4">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G1228" s="4">
         <v>6</v>
       </c>
       <c r="H1228" s="4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I1228" s="4">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="1229" spans="1:9" x14ac:dyDescent="0.25">
@@ -40666,16 +40666,16 @@
         <v>104</v>
       </c>
       <c r="F1232" s="4">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G1232" s="4">
         <v>5</v>
       </c>
       <c r="H1232" s="4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I1232" s="4">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="1233" spans="1:9" x14ac:dyDescent="0.25">
@@ -40811,16 +40811,16 @@
         <v>105</v>
       </c>
       <c r="F1237" s="4">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G1237" s="4">
         <v>34</v>
       </c>
       <c r="H1237" s="4">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I1237" s="4">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="1238" spans="1:9" x14ac:dyDescent="0.25">
@@ -41130,16 +41130,16 @@
         <v>106</v>
       </c>
       <c r="F1248" s="4">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G1248" s="4">
         <v>6</v>
       </c>
       <c r="H1248" s="4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I1248" s="4">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="1249" spans="1:9" x14ac:dyDescent="0.25">
@@ -41159,16 +41159,16 @@
         <v>106</v>
       </c>
       <c r="F1249" s="4">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G1249" s="4">
         <v>42</v>
       </c>
       <c r="H1249" s="4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I1249" s="4">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="1250" spans="1:9" x14ac:dyDescent="0.25">
@@ -41188,16 +41188,16 @@
         <v>106</v>
       </c>
       <c r="F1250" s="4">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G1250" s="4">
         <v>5</v>
       </c>
       <c r="H1250" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I1250" s="4">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1251" spans="1:9" x14ac:dyDescent="0.25">
@@ -41333,16 +41333,16 @@
         <v>106</v>
       </c>
       <c r="F1255" s="4">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G1255" s="4">
         <v>5</v>
       </c>
       <c r="H1255" s="4">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I1255" s="4">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1256" spans="1:9" x14ac:dyDescent="0.25">
@@ -41623,16 +41623,16 @@
         <v>107</v>
       </c>
       <c r="F1265" s="4">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G1265" s="4">
         <v>11</v>
       </c>
       <c r="H1265" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I1265" s="4">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="1266" spans="1:9" x14ac:dyDescent="0.25">
@@ -41652,16 +41652,16 @@
         <v>107</v>
       </c>
       <c r="F1266" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G1266" s="4">
         <v>3</v>
       </c>
       <c r="H1266" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I1266" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1267" spans="1:9" x14ac:dyDescent="0.25">
@@ -41739,16 +41739,16 @@
         <v>107</v>
       </c>
       <c r="F1269" s="4">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G1269" s="4">
         <v>4</v>
       </c>
       <c r="H1269" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I1269" s="4">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1270" spans="1:9" x14ac:dyDescent="0.25">
@@ -41942,16 +41942,16 @@
         <v>107</v>
       </c>
       <c r="F1276" s="4">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G1276" s="4">
         <v>8</v>
       </c>
       <c r="H1276" s="4">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I1276" s="4">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="1277" spans="1:9" x14ac:dyDescent="0.25">
@@ -42145,16 +42145,16 @@
         <v>108</v>
       </c>
       <c r="F1283" s="4">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G1283" s="4">
         <v>6</v>
       </c>
       <c r="H1283" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I1283" s="4">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1284" spans="1:9" x14ac:dyDescent="0.25">
@@ -42348,16 +42348,16 @@
         <v>108</v>
       </c>
       <c r="F1290" s="4">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G1290" s="4">
         <v>20</v>
       </c>
       <c r="H1290" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I1290" s="4">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="1291" spans="1:9" x14ac:dyDescent="0.25">
@@ -42493,16 +42493,16 @@
         <v>109</v>
       </c>
       <c r="F1295" s="4">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G1295" s="4">
         <v>17</v>
       </c>
       <c r="H1295" s="4">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I1295" s="4">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1296" spans="1:9" x14ac:dyDescent="0.25">
@@ -42638,16 +42638,16 @@
         <v>109</v>
       </c>
       <c r="F1300" s="4">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="G1300" s="4">
         <v>46</v>
       </c>
       <c r="H1300" s="4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I1300" s="4">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="1301" spans="1:9" x14ac:dyDescent="0.25">
@@ -42783,16 +42783,16 @@
         <v>109</v>
       </c>
       <c r="F1305" s="4">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G1305" s="4">
         <v>23</v>
       </c>
       <c r="H1305" s="4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I1305" s="4">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1306" spans="1:9" x14ac:dyDescent="0.25">
@@ -42899,16 +42899,16 @@
         <v>110</v>
       </c>
       <c r="F1309" s="4">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="G1309" s="4">
         <v>40</v>
       </c>
       <c r="H1309" s="4">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="I1309" s="4">
-        <v>70</v>
+        <v>75</v>
       </c>
     </row>
     <row r="1310" spans="1:9" x14ac:dyDescent="0.25">
@@ -42957,16 +42957,16 @@
         <v>110</v>
       </c>
       <c r="F1311" s="4">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G1311" s="4">
         <v>10</v>
       </c>
       <c r="H1311" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I1311" s="4">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1312" spans="1:9" x14ac:dyDescent="0.25">
@@ -43015,16 +43015,16 @@
         <v>110</v>
       </c>
       <c r="F1313" s="4">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G1313" s="4">
         <v>13</v>
       </c>
       <c r="H1313" s="4">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I1313" s="4">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="1314" spans="1:9" x14ac:dyDescent="0.25">
@@ -43073,16 +43073,16 @@
         <v>111</v>
       </c>
       <c r="F1315" s="4">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G1315" s="4">
         <v>4</v>
       </c>
       <c r="H1315" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I1315" s="4">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1316" spans="1:9" x14ac:dyDescent="0.25">
@@ -43102,16 +43102,16 @@
         <v>111</v>
       </c>
       <c r="F1316" s="4">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="G1316" s="4">
         <v>28</v>
       </c>
       <c r="H1316" s="4">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="I1316" s="4">
-        <v>54</v>
+        <v>59</v>
       </c>
     </row>
     <row r="1317" spans="1:9" x14ac:dyDescent="0.25">
@@ -43189,16 +43189,16 @@
         <v>111</v>
       </c>
       <c r="F1319" s="4">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G1319" s="4">
         <v>15</v>
       </c>
       <c r="H1319" s="4">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I1319" s="4">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1320" spans="1:9" x14ac:dyDescent="0.25">
@@ -43421,16 +43421,16 @@
         <v>112</v>
       </c>
       <c r="F1327" s="4">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G1327" s="4">
         <v>17</v>
       </c>
       <c r="H1327" s="4">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I1327" s="4">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="1328" spans="1:9" x14ac:dyDescent="0.25">
@@ -43566,16 +43566,16 @@
         <v>113</v>
       </c>
       <c r="F1332" s="4">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G1332" s="4">
         <v>10</v>
       </c>
       <c r="H1332" s="4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I1332" s="4">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="1333" spans="1:9" x14ac:dyDescent="0.25">
@@ -43624,16 +43624,16 @@
         <v>113</v>
       </c>
       <c r="F1334" s="4">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G1334" s="4">
         <v>14</v>
       </c>
       <c r="H1334" s="4">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I1334" s="4">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="1335" spans="1:9" x14ac:dyDescent="0.25">
@@ -43653,16 +43653,16 @@
         <v>113</v>
       </c>
       <c r="F1335" s="4">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="G1335" s="4">
         <v>50</v>
       </c>
       <c r="H1335" s="4">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="I1335" s="4">
-        <v>74</v>
+        <v>81</v>
       </c>
     </row>
     <row r="1336" spans="1:9" x14ac:dyDescent="0.25">
@@ -43711,16 +43711,16 @@
         <v>114</v>
       </c>
       <c r="F1337" s="4">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G1337" s="4">
         <v>10</v>
       </c>
       <c r="H1337" s="4">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I1337" s="4">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="1338" spans="1:9" x14ac:dyDescent="0.25">
@@ -43827,16 +43827,16 @@
         <v>114</v>
       </c>
       <c r="F1341" s="4">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="G1341" s="4">
         <v>23</v>
       </c>
       <c r="H1341" s="4">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="I1341" s="4">
-        <v>34</v>
+        <v>42</v>
       </c>
     </row>
     <row r="1342" spans="1:9" x14ac:dyDescent="0.25">
@@ -44030,16 +44030,16 @@
         <v>115</v>
       </c>
       <c r="F1348" s="4">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G1348" s="4">
         <v>17</v>
       </c>
       <c r="H1348" s="4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I1348" s="4">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="1349" spans="1:9" x14ac:dyDescent="0.25">
@@ -44059,16 +44059,16 @@
         <v>115</v>
       </c>
       <c r="F1349" s="4">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G1349" s="4">
         <v>4</v>
       </c>
       <c r="H1349" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I1349" s="4">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1350" spans="1:9" x14ac:dyDescent="0.25">
@@ -44175,16 +44175,16 @@
         <v>115</v>
       </c>
       <c r="F1353" s="4">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G1353" s="4">
         <v>4</v>
       </c>
       <c r="H1353" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I1353" s="4">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="1354" spans="1:9" x14ac:dyDescent="0.25">
@@ -44320,16 +44320,16 @@
         <v>116</v>
       </c>
       <c r="F1358" s="4">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G1358" s="4">
         <v>26</v>
       </c>
       <c r="H1358" s="4">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I1358" s="4">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="1359" spans="1:9" x14ac:dyDescent="0.25">
@@ -44494,16 +44494,16 @@
         <v>116</v>
       </c>
       <c r="F1364" s="4">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G1364" s="4">
         <v>20</v>
       </c>
       <c r="H1364" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I1364" s="4">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="1365" spans="1:9" x14ac:dyDescent="0.25">
@@ -44755,16 +44755,16 @@
         <v>117</v>
       </c>
       <c r="F1373" s="4">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G1373" s="4">
         <v>14</v>
       </c>
       <c r="H1373" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I1373" s="4">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="1374" spans="1:9" x14ac:dyDescent="0.25">
@@ -44813,16 +44813,16 @@
         <v>117</v>
       </c>
       <c r="F1375" s="4">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="G1375" s="4">
         <v>22</v>
       </c>
       <c r="H1375" s="4">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I1375" s="4">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="1376" spans="1:9" x14ac:dyDescent="0.25">
@@ -45161,16 +45161,16 @@
         <v>118</v>
       </c>
       <c r="F1387" s="4">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G1387" s="4">
         <v>5</v>
       </c>
       <c r="H1387" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I1387" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="1388" spans="1:9" x14ac:dyDescent="0.25">
@@ -45248,16 +45248,16 @@
         <v>118</v>
       </c>
       <c r="F1390" s="4">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G1390" s="4">
         <v>38</v>
       </c>
       <c r="H1390" s="4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I1390" s="4">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="1391" spans="1:9" x14ac:dyDescent="0.25">
@@ -45277,16 +45277,16 @@
         <v>118</v>
       </c>
       <c r="F1391" s="4">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G1391" s="4">
         <v>8</v>
       </c>
       <c r="H1391" s="4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I1391" s="4">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="1392" spans="1:9" x14ac:dyDescent="0.25">
@@ -45335,16 +45335,16 @@
         <v>119</v>
       </c>
       <c r="F1393" s="4">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G1393" s="4">
         <v>16</v>
       </c>
       <c r="H1393" s="4">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I1393" s="4">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="1394" spans="1:9" x14ac:dyDescent="0.25">
@@ -45451,16 +45451,16 @@
         <v>119</v>
       </c>
       <c r="F1397" s="4">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G1397" s="4">
         <v>17</v>
       </c>
       <c r="H1397" s="4">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I1397" s="4">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="1398" spans="1:9" x14ac:dyDescent="0.25">
@@ -45683,16 +45683,16 @@
         <v>120</v>
       </c>
       <c r="F1405" s="4">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G1405" s="4">
         <v>17</v>
       </c>
       <c r="H1405" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I1405" s="4">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="1406" spans="1:9" x14ac:dyDescent="0.25">
@@ -45857,16 +45857,16 @@
         <v>120</v>
       </c>
       <c r="F1411" s="4">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G1411" s="4">
         <v>12</v>
       </c>
       <c r="H1411" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I1411" s="4">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1412" spans="1:9" x14ac:dyDescent="0.25">
@@ -45973,16 +45973,16 @@
         <v>120</v>
       </c>
       <c r="F1415" s="4">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G1415" s="4">
         <v>3</v>
       </c>
       <c r="H1415" s="4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I1415" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="1416" spans="1:9" x14ac:dyDescent="0.25">
@@ -46089,16 +46089,16 @@
         <v>121</v>
       </c>
       <c r="F1419" s="4">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G1419" s="4">
         <v>41</v>
       </c>
       <c r="H1419" s="4">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I1419" s="4">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="1420" spans="1:9" x14ac:dyDescent="0.25">
@@ -46147,16 +46147,16 @@
         <v>121</v>
       </c>
       <c r="F1421" s="4">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G1421" s="4">
         <v>6</v>
       </c>
       <c r="H1421" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I1421" s="4">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="1422" spans="1:9" x14ac:dyDescent="0.25">
@@ -46466,16 +46466,16 @@
         <v>122</v>
       </c>
       <c r="F1432" s="4">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="G1432" s="4">
         <v>26</v>
       </c>
       <c r="H1432" s="4">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I1432" s="4">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="1433" spans="1:9" x14ac:dyDescent="0.25">
@@ -46611,16 +46611,16 @@
         <v>122</v>
       </c>
       <c r="F1437" s="4">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G1437" s="4">
         <v>7</v>
       </c>
       <c r="H1437" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I1437" s="4">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1438" spans="1:9" x14ac:dyDescent="0.25">
@@ -46669,16 +46669,16 @@
         <v>122</v>
       </c>
       <c r="F1439" s="4">
+        <v>6</v>
+      </c>
+      <c r="G1439" s="4">
+        <v>1</v>
+      </c>
+      <c r="H1439" s="4">
+        <v>3</v>
+      </c>
+      <c r="I1439" s="4">
         <v>5</v>
-      </c>
-      <c r="G1439" s="4">
-        <v>1</v>
-      </c>
-      <c r="H1439" s="4">
-        <v>2</v>
-      </c>
-      <c r="I1439" s="4">
-        <v>4</v>
       </c>
     </row>
     <row r="1440" spans="1:9" x14ac:dyDescent="0.25">
@@ -47104,16 +47104,16 @@
         <v>123</v>
       </c>
       <c r="F1454" s="4">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="G1454" s="4">
         <v>24</v>
       </c>
       <c r="H1454" s="4">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I1454" s="4">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="1455" spans="1:9" x14ac:dyDescent="0.25">
@@ -47336,16 +47336,16 @@
         <v>124</v>
       </c>
       <c r="F1462" s="4">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G1462" s="4">
         <v>11</v>
       </c>
       <c r="H1462" s="4">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I1462" s="4">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="1463" spans="1:9" x14ac:dyDescent="0.25">
@@ -47365,16 +47365,16 @@
         <v>124</v>
       </c>
       <c r="F1463" s="4">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G1463" s="4">
         <v>30</v>
       </c>
       <c r="H1463" s="4">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I1463" s="4">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="1464" spans="1:9" x14ac:dyDescent="0.25">
@@ -47394,16 +47394,16 @@
         <v>124</v>
       </c>
       <c r="F1464" s="4">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="G1464" s="4">
         <v>25</v>
       </c>
       <c r="H1464" s="4">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I1464" s="4">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="1465" spans="1:9" x14ac:dyDescent="0.25">
@@ -47510,16 +47510,16 @@
         <v>125</v>
       </c>
       <c r="F1468" s="4">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G1468" s="4">
         <v>12</v>
       </c>
       <c r="H1468" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I1468" s="4">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1469" spans="1:9" x14ac:dyDescent="0.25">
@@ -47539,16 +47539,16 @@
         <v>125</v>
       </c>
       <c r="F1469" s="4">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G1469" s="4">
         <v>20</v>
       </c>
       <c r="H1469" s="4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I1469" s="4">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="1470" spans="1:9" x14ac:dyDescent="0.25">
@@ -47568,16 +47568,16 @@
         <v>125</v>
       </c>
       <c r="F1470" s="4">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G1470" s="4">
         <v>32</v>
       </c>
       <c r="H1470" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I1470" s="4">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="1471" spans="1:9" x14ac:dyDescent="0.25">
@@ -47597,16 +47597,16 @@
         <v>125</v>
       </c>
       <c r="F1471" s="4">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="G1471" s="4">
         <v>15</v>
       </c>
       <c r="H1471" s="4">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I1471" s="4">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="1472" spans="1:9" x14ac:dyDescent="0.25">
@@ -47800,16 +47800,16 @@
         <v>126</v>
       </c>
       <c r="F1478" s="4">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="G1478" s="4">
         <v>30</v>
       </c>
       <c r="H1478" s="4">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="I1478" s="4">
-        <v>76</v>
+        <v>80</v>
       </c>
     </row>
     <row r="1479" spans="1:9" x14ac:dyDescent="0.25">
@@ -47829,16 +47829,16 @@
         <v>126</v>
       </c>
       <c r="F1479" s="4">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G1479" s="4">
         <v>23</v>
       </c>
       <c r="H1479" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I1479" s="4">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="1480" spans="1:9" x14ac:dyDescent="0.25">
@@ -47858,16 +47858,16 @@
         <v>126</v>
       </c>
       <c r="F1480" s="4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G1480" s="4">
         <v>5</v>
       </c>
       <c r="H1480" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I1480" s="4">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1481" spans="1:9" x14ac:dyDescent="0.25">
@@ -48119,16 +48119,16 @@
         <v>126</v>
       </c>
       <c r="F1489" s="4">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G1489" s="4">
         <v>6</v>
       </c>
       <c r="H1489" s="4">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I1489" s="4">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="1490" spans="1:9" x14ac:dyDescent="0.25">
@@ -48177,16 +48177,16 @@
         <v>126</v>
       </c>
       <c r="F1491" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G1491" s="4">
         <v>3</v>
       </c>
       <c r="H1491" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1491" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1492" spans="1:9" x14ac:dyDescent="0.25">
@@ -48235,16 +48235,16 @@
         <v>127</v>
       </c>
       <c r="F1493" s="4">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G1493" s="4">
         <v>11</v>
       </c>
       <c r="H1493" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I1493" s="4">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="1494" spans="1:9" x14ac:dyDescent="0.25">
@@ -48380,16 +48380,16 @@
         <v>127</v>
       </c>
       <c r="F1498" s="4">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G1498" s="4">
         <v>18</v>
       </c>
       <c r="H1498" s="4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I1498" s="4">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="1499" spans="1:9" x14ac:dyDescent="0.25">
@@ -48467,16 +48467,16 @@
         <v>127</v>
       </c>
       <c r="F1501" s="4">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G1501" s="4">
         <v>13</v>
       </c>
       <c r="H1501" s="4">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I1501" s="4">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="1502" spans="1:9" x14ac:dyDescent="0.25">
@@ -48496,16 +48496,16 @@
         <v>127</v>
       </c>
       <c r="F1502" s="4">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G1502" s="4">
         <v>9</v>
       </c>
       <c r="H1502" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I1502" s="4">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="1503" spans="1:9" x14ac:dyDescent="0.25">
@@ -48554,16 +48554,16 @@
         <v>128</v>
       </c>
       <c r="F1504" s="4">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G1504" s="4">
         <v>21</v>
       </c>
       <c r="H1504" s="4">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I1504" s="4">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="1505" spans="1:9" x14ac:dyDescent="0.25">
@@ -48583,16 +48583,16 @@
         <v>128</v>
       </c>
       <c r="F1505" s="4">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G1505" s="4">
         <v>3</v>
       </c>
       <c r="H1505" s="4">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I1505" s="4">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1506" spans="1:9" x14ac:dyDescent="0.25">
@@ -48612,16 +48612,16 @@
         <v>128</v>
       </c>
       <c r="F1506" s="4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G1506" s="4">
         <v>3</v>
       </c>
       <c r="H1506" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I1506" s="4">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1507" spans="1:9" x14ac:dyDescent="0.25">
@@ -48815,16 +48815,16 @@
         <v>128</v>
       </c>
       <c r="F1513" s="4">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G1513" s="4">
         <v>6</v>
       </c>
       <c r="H1513" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I1513" s="4">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="1514" spans="1:9" x14ac:dyDescent="0.25">
@@ -48844,16 +48844,16 @@
         <v>128</v>
       </c>
       <c r="F1514" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1514" s="4">
         <v>0</v>
       </c>
       <c r="H1514" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1514" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1515" spans="1:9" x14ac:dyDescent="0.25">
@@ -48873,16 +48873,16 @@
         <v>128</v>
       </c>
       <c r="F1515" s="4">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="G1515" s="4">
         <v>22</v>
       </c>
       <c r="H1515" s="4">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I1515" s="4">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="1516" spans="1:9" x14ac:dyDescent="0.25">
@@ -48931,16 +48931,16 @@
         <v>129</v>
       </c>
       <c r="F1517" s="4">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G1517" s="4">
         <v>17</v>
       </c>
       <c r="H1517" s="4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I1517" s="4">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="1518" spans="1:9" x14ac:dyDescent="0.25">
@@ -48960,16 +48960,16 @@
         <v>129</v>
       </c>
       <c r="F1518" s="4">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G1518" s="4">
         <v>3</v>
       </c>
       <c r="H1518" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I1518" s="4">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1519" spans="1:9" x14ac:dyDescent="0.25">
@@ -49105,16 +49105,16 @@
         <v>129</v>
       </c>
       <c r="F1523" s="4">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G1523" s="4">
         <v>33</v>
       </c>
       <c r="H1523" s="4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I1523" s="4">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="1524" spans="1:9" x14ac:dyDescent="0.25">
@@ -49192,16 +49192,16 @@
         <v>130</v>
       </c>
       <c r="F1526" s="4">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G1526" s="4">
         <v>23</v>
       </c>
       <c r="H1526" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I1526" s="4">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="1527" spans="1:9" x14ac:dyDescent="0.25">
@@ -49250,16 +49250,16 @@
         <v>130</v>
       </c>
       <c r="F1528" s="4">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G1528" s="4">
         <v>12</v>
       </c>
       <c r="H1528" s="4">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I1528" s="4">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1529" spans="1:9" x14ac:dyDescent="0.25">
@@ -49279,16 +49279,16 @@
         <v>130</v>
       </c>
       <c r="F1529" s="4">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="G1529" s="4">
         <v>7</v>
       </c>
       <c r="H1529" s="4">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I1529" s="4">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="1530" spans="1:9" x14ac:dyDescent="0.25">
@@ -49395,16 +49395,16 @@
         <v>131</v>
       </c>
       <c r="F1533" s="4">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G1533" s="4">
         <v>18</v>
       </c>
       <c r="H1533" s="4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I1533" s="4">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="1534" spans="1:9" x14ac:dyDescent="0.25">
@@ -49453,16 +49453,16 @@
         <v>131</v>
       </c>
       <c r="F1535" s="4">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="G1535" s="4">
         <v>23</v>
       </c>
       <c r="H1535" s="4">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I1535" s="4">
-        <v>43</v>
+        <v>47</v>
       </c>
     </row>
     <row r="1536" spans="1:9" x14ac:dyDescent="0.25">
@@ -49482,16 +49482,16 @@
         <v>131</v>
       </c>
       <c r="F1536" s="4">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G1536" s="4">
         <v>24</v>
       </c>
       <c r="H1536" s="4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I1536" s="4">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="1537" spans="1:9" x14ac:dyDescent="0.25">
@@ -49743,16 +49743,16 @@
         <v>131</v>
       </c>
       <c r="F1545" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1545" s="4">
         <v>0</v>
       </c>
       <c r="H1545" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I1545" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1546" spans="1:9" x14ac:dyDescent="0.25">
@@ -49801,16 +49801,16 @@
         <v>132</v>
       </c>
       <c r="F1547" s="4">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="G1547" s="4">
         <v>19</v>
       </c>
       <c r="H1547" s="4">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I1547" s="4">
-        <v>43</v>
+        <v>48</v>
       </c>
     </row>
     <row r="1548" spans="1:9" x14ac:dyDescent="0.25">
@@ -49859,16 +49859,16 @@
         <v>132</v>
       </c>
       <c r="F1549" s="4">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G1549" s="4">
         <v>18</v>
       </c>
       <c r="H1549" s="4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I1549" s="4">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="1550" spans="1:9" x14ac:dyDescent="0.25">
@@ -49888,16 +49888,16 @@
         <v>132</v>
       </c>
       <c r="F1550" s="4">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G1550" s="4">
         <v>5</v>
       </c>
       <c r="H1550" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1550" s="4">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1551" spans="1:9" x14ac:dyDescent="0.25">
@@ -49917,16 +49917,16 @@
         <v>132</v>
       </c>
       <c r="F1551" s="4">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G1551" s="4">
         <v>17</v>
       </c>
       <c r="H1551" s="4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I1551" s="4">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="1552" spans="1:9" x14ac:dyDescent="0.25">
@@ -49946,16 +49946,16 @@
         <v>132</v>
       </c>
       <c r="F1552" s="4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G1552" s="4">
         <v>3</v>
       </c>
       <c r="H1552" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I1552" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1553" spans="1:9" x14ac:dyDescent="0.25">
@@ -50091,16 +50091,16 @@
         <v>133</v>
       </c>
       <c r="F1557" s="4">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="G1557" s="4">
         <v>58</v>
       </c>
       <c r="H1557" s="4">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="I1557" s="4">
-        <v>127</v>
+        <v>132</v>
       </c>
     </row>
     <row r="1558" spans="1:9" x14ac:dyDescent="0.25">
@@ -50381,16 +50381,16 @@
         <v>134</v>
       </c>
       <c r="F1567" s="4">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G1567" s="4">
         <v>17</v>
       </c>
       <c r="H1567" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I1567" s="4">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="1568" spans="1:9" x14ac:dyDescent="0.25">
@@ -50468,16 +50468,16 @@
         <v>134</v>
       </c>
       <c r="F1570" s="4">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G1570" s="4">
         <v>9</v>
       </c>
       <c r="H1570" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I1570" s="4">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="1571" spans="1:9" x14ac:dyDescent="0.25">
@@ -50555,16 +50555,16 @@
         <v>134</v>
       </c>
       <c r="F1573" s="4">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G1573" s="4">
         <v>8</v>
       </c>
       <c r="H1573" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1573" s="4">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1574" spans="1:9" x14ac:dyDescent="0.25">
@@ -50758,16 +50758,16 @@
         <v>135</v>
       </c>
       <c r="F1580" s="4">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G1580" s="4">
         <v>32</v>
       </c>
       <c r="H1580" s="4">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I1580" s="4">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="1581" spans="1:9" x14ac:dyDescent="0.25">
@@ -50816,16 +50816,16 @@
         <v>135</v>
       </c>
       <c r="F1582" s="4">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G1582" s="4">
         <v>14</v>
       </c>
       <c r="H1582" s="4">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I1582" s="4">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="1583" spans="1:9" x14ac:dyDescent="0.25">
@@ -50845,16 +50845,16 @@
         <v>135</v>
       </c>
       <c r="F1583" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G1583" s="4">
         <v>9</v>
       </c>
       <c r="H1583" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1583" s="4">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1584" spans="1:9" x14ac:dyDescent="0.25">
@@ -50903,16 +50903,16 @@
         <v>135</v>
       </c>
       <c r="F1585" s="4">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G1585" s="4">
         <v>16</v>
       </c>
       <c r="H1585" s="4">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I1585" s="4">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1586" spans="1:9" x14ac:dyDescent="0.25">
@@ -51251,16 +51251,16 @@
         <v>136</v>
       </c>
       <c r="F1597" s="4">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="G1597" s="4">
         <v>18</v>
       </c>
       <c r="H1597" s="4">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I1597" s="4">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="1598" spans="1:9" x14ac:dyDescent="0.25">
@@ -51280,16 +51280,16 @@
         <v>136</v>
       </c>
       <c r="F1598" s="4">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="G1598" s="4">
         <v>16</v>
       </c>
       <c r="H1598" s="4">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="I1598" s="4">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1599" spans="1:9" x14ac:dyDescent="0.25">
@@ -51309,16 +51309,16 @@
         <v>136</v>
       </c>
       <c r="F1599" s="4">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G1599" s="4">
         <v>12</v>
       </c>
       <c r="H1599" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I1599" s="4">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1600" spans="1:9" x14ac:dyDescent="0.25">
@@ -51570,16 +51570,16 @@
         <v>136</v>
       </c>
       <c r="F1608" s="4">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G1608" s="4">
         <v>3</v>
       </c>
       <c r="H1608" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1608" s="4">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1609" spans="1:9" x14ac:dyDescent="0.25">
@@ -51686,16 +51686,16 @@
         <v>137</v>
       </c>
       <c r="F1612" s="4">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="G1612" s="4">
         <v>37</v>
       </c>
       <c r="H1612" s="4">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="I1612" s="4">
-        <v>79</v>
+        <v>84</v>
       </c>
     </row>
     <row r="1613" spans="1:9" x14ac:dyDescent="0.25">
@@ -51744,16 +51744,16 @@
         <v>137</v>
       </c>
       <c r="F1614" s="4">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G1614" s="4">
         <v>9</v>
       </c>
       <c r="H1614" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I1614" s="4">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="1615" spans="1:9" x14ac:dyDescent="0.25">
@@ -51831,16 +51831,16 @@
         <v>137</v>
       </c>
       <c r="F1617" s="4">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="G1617" s="4">
         <v>9</v>
       </c>
       <c r="H1617" s="4">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="I1617" s="4">
-        <v>33</v>
+        <v>39</v>
       </c>
     </row>
     <row r="1618" spans="1:9" x14ac:dyDescent="0.25">
@@ -51918,16 +51918,16 @@
         <v>138</v>
       </c>
       <c r="F1620" s="4">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="G1620" s="4">
         <v>30</v>
       </c>
       <c r="H1620" s="4">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I1620" s="4">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="1621" spans="1:9" x14ac:dyDescent="0.25">
@@ -52005,16 +52005,16 @@
         <v>138</v>
       </c>
       <c r="F1623" s="4">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G1623" s="4">
         <v>7</v>
       </c>
       <c r="H1623" s="4">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I1623" s="4">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="1624" spans="1:9" x14ac:dyDescent="0.25">
@@ -52092,16 +52092,16 @@
         <v>138</v>
       </c>
       <c r="F1626" s="4">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G1626" s="4">
         <v>3</v>
       </c>
       <c r="H1626" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I1626" s="4">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1627" spans="1:9" x14ac:dyDescent="0.25">
@@ -52237,16 +52237,16 @@
         <v>139</v>
       </c>
       <c r="F1631" s="4">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="G1631" s="4">
         <v>31</v>
       </c>
       <c r="H1631" s="4">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="I1631" s="4">
-        <v>70</v>
+        <v>74</v>
       </c>
     </row>
     <row r="1632" spans="1:9" x14ac:dyDescent="0.25">
@@ -52295,16 +52295,16 @@
         <v>139</v>
       </c>
       <c r="F1633" s="4">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="G1633" s="4">
         <v>33</v>
       </c>
       <c r="H1633" s="4">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="I1633" s="4">
-        <v>40</v>
+        <v>52</v>
       </c>
     </row>
     <row r="1634" spans="1:9" x14ac:dyDescent="0.25">
@@ -52382,16 +52382,16 @@
         <v>139</v>
       </c>
       <c r="F1636" s="4">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="G1636" s="4">
         <v>9</v>
       </c>
       <c r="H1636" s="4">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I1636" s="4">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="1637" spans="1:9" x14ac:dyDescent="0.25">
@@ -52585,16 +52585,16 @@
         <v>140</v>
       </c>
       <c r="F1643" s="4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G1643" s="4">
         <v>4</v>
       </c>
       <c r="H1643" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1643" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1644" spans="1:9" x14ac:dyDescent="0.25">
@@ -52614,16 +52614,16 @@
         <v>140</v>
       </c>
       <c r="F1644" s="4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G1644" s="4">
         <v>2</v>
       </c>
       <c r="H1644" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I1644" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1645" spans="1:9" x14ac:dyDescent="0.25">
@@ -52672,16 +52672,16 @@
         <v>140</v>
       </c>
       <c r="F1646" s="4">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="G1646" s="4">
         <v>3</v>
       </c>
       <c r="H1646" s="4">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="I1646" s="4">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="1647" spans="1:9" x14ac:dyDescent="0.25">
@@ -52701,16 +52701,16 @@
         <v>140</v>
       </c>
       <c r="F1647" s="4">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="G1647" s="4">
         <v>12</v>
       </c>
       <c r="H1647" s="4">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="I1647" s="4">
-        <v>14</v>
+        <v>30</v>
       </c>
     </row>
     <row r="1648" spans="1:9" x14ac:dyDescent="0.25">
@@ -52788,16 +52788,16 @@
         <v>141</v>
       </c>
       <c r="F1650" s="4">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="G1650" s="4">
         <v>33</v>
       </c>
       <c r="H1650" s="4">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="I1650" s="4">
-        <v>37</v>
+        <v>49</v>
       </c>
     </row>
     <row r="1651" spans="1:9" x14ac:dyDescent="0.25">
@@ -52817,16 +52817,16 @@
         <v>141</v>
       </c>
       <c r="F1651" s="4">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="G1651" s="4">
         <v>3</v>
       </c>
       <c r="H1651" s="4">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I1651" s="4">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="1652" spans="1:9" x14ac:dyDescent="0.25">
@@ -52846,16 +52846,16 @@
         <v>141</v>
       </c>
       <c r="F1652" s="4">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="G1652" s="4">
         <v>39</v>
       </c>
       <c r="H1652" s="4">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="I1652" s="4">
-        <v>99</v>
+        <v>106</v>
       </c>
     </row>
     <row r="1653" spans="1:9" x14ac:dyDescent="0.25">
@@ -53078,16 +53078,16 @@
         <v>142</v>
       </c>
       <c r="F1660" s="4">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G1660" s="4">
         <v>6</v>
       </c>
       <c r="H1660" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I1660" s="4">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="1661" spans="1:9" x14ac:dyDescent="0.25">
@@ -53107,16 +53107,16 @@
         <v>142</v>
       </c>
       <c r="F1661" s="4">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="G1661" s="4">
         <v>29</v>
       </c>
       <c r="H1661" s="4">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="I1661" s="4">
-        <v>68</v>
+        <v>75</v>
       </c>
     </row>
     <row r="1662" spans="1:9" x14ac:dyDescent="0.25">
@@ -53194,16 +53194,16 @@
         <v>142</v>
       </c>
       <c r="F1664" s="4">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="G1664" s="4">
         <v>22</v>
       </c>
       <c r="H1664" s="4">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="I1664" s="4">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="1665" spans="1:9" x14ac:dyDescent="0.25">
@@ -53223,16 +53223,16 @@
         <v>142</v>
       </c>
       <c r="F1665" s="4">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="G1665" s="4">
         <v>23</v>
       </c>
       <c r="H1665" s="4">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I1665" s="4">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="1666" spans="1:9" x14ac:dyDescent="0.25">
@@ -53397,16 +53397,16 @@
         <v>143</v>
       </c>
       <c r="F1671" s="4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G1671" s="4">
         <v>2</v>
       </c>
       <c r="H1671" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I1671" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1672" spans="1:9" x14ac:dyDescent="0.25">
@@ -53542,16 +53542,16 @@
         <v>143</v>
       </c>
       <c r="F1676" s="4">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="G1676" s="4">
         <v>40</v>
       </c>
       <c r="H1676" s="4">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="I1676" s="4">
-        <v>40</v>
+        <v>56</v>
       </c>
     </row>
     <row r="1677" spans="1:9" x14ac:dyDescent="0.25">
@@ -53571,16 +53571,16 @@
         <v>143</v>
       </c>
       <c r="F1677" s="4">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G1677" s="4">
         <v>17</v>
       </c>
       <c r="H1677" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I1677" s="4">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="1678" spans="1:9" x14ac:dyDescent="0.25">
@@ -53600,16 +53600,16 @@
         <v>143</v>
       </c>
       <c r="F1678" s="4">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G1678" s="4">
         <v>4</v>
       </c>
       <c r="H1678" s="4">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="I1678" s="4">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="1679" spans="1:9" x14ac:dyDescent="0.25">
@@ -53803,16 +53803,16 @@
         <v>144</v>
       </c>
       <c r="F1685" s="4">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G1685" s="4">
         <v>15</v>
       </c>
       <c r="H1685" s="4">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I1685" s="4">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="1686" spans="1:9" x14ac:dyDescent="0.25">
@@ -53832,16 +53832,16 @@
         <v>144</v>
       </c>
       <c r="F1686" s="4">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G1686" s="4">
         <v>7</v>
       </c>
       <c r="H1686" s="4">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I1686" s="4">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="1687" spans="1:9" x14ac:dyDescent="0.25">
@@ -53919,16 +53919,16 @@
         <v>144</v>
       </c>
       <c r="F1689" s="4">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="G1689" s="4">
         <v>44</v>
       </c>
       <c r="H1689" s="4">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="I1689" s="4">
-        <v>69</v>
+        <v>83</v>
       </c>
     </row>
     <row r="1690" spans="1:9" x14ac:dyDescent="0.25">
@@ -53948,16 +53948,16 @@
         <v>144</v>
       </c>
       <c r="F1690" s="4">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G1690" s="4">
         <v>6</v>
       </c>
       <c r="H1690" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I1690" s="4">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1691" spans="1:9" x14ac:dyDescent="0.25">
@@ -54064,16 +54064,16 @@
         <v>145</v>
       </c>
       <c r="F1694" s="4">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="G1694" s="4">
         <v>50</v>
       </c>
       <c r="H1694" s="4">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="I1694" s="4">
-        <v>77</v>
+        <v>87</v>
       </c>
     </row>
     <row r="1695" spans="1:9" x14ac:dyDescent="0.25">
@@ -54093,16 +54093,16 @@
         <v>145</v>
       </c>
       <c r="F1695" s="4">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G1695" s="4">
         <v>25</v>
       </c>
       <c r="H1695" s="4">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="I1695" s="4">
-        <v>41</v>
+        <v>47</v>
       </c>
     </row>
     <row r="1696" spans="1:9" x14ac:dyDescent="0.25">
@@ -54122,16 +54122,16 @@
         <v>145</v>
       </c>
       <c r="F1696" s="4">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="G1696" s="4">
         <v>13</v>
       </c>
       <c r="H1696" s="4">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="I1696" s="4">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="1697" spans="1:9" x14ac:dyDescent="0.25">
@@ -54383,16 +54383,16 @@
         <v>146</v>
       </c>
       <c r="F1705" s="4">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="G1705" s="4">
         <v>48</v>
       </c>
       <c r="H1705" s="4">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="I1705" s="4">
-        <v>105</v>
+        <v>119</v>
       </c>
     </row>
     <row r="1706" spans="1:9" x14ac:dyDescent="0.25">
@@ -54412,16 +54412,16 @@
         <v>146</v>
       </c>
       <c r="F1706" s="4">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="G1706" s="4">
         <v>32</v>
       </c>
       <c r="H1706" s="4">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="I1706" s="4">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="1707" spans="1:9" x14ac:dyDescent="0.25">
@@ -54470,16 +54470,16 @@
         <v>147</v>
       </c>
       <c r="F1708" s="4">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G1708" s="4">
         <v>6</v>
       </c>
       <c r="H1708" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I1708" s="4">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1709" spans="1:9" x14ac:dyDescent="0.25">
@@ -54499,16 +54499,16 @@
         <v>147</v>
       </c>
       <c r="F1709" s="4">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="G1709" s="4">
         <v>43</v>
       </c>
       <c r="H1709" s="4">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="I1709" s="4">
-        <v>41</v>
+        <v>55</v>
       </c>
     </row>
     <row r="1710" spans="1:9" x14ac:dyDescent="0.25">
@@ -54528,16 +54528,16 @@
         <v>147</v>
       </c>
       <c r="F1710" s="4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G1710" s="4">
         <v>3</v>
       </c>
       <c r="H1710" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1710" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1711" spans="1:9" x14ac:dyDescent="0.25">
@@ -54586,16 +54586,16 @@
         <v>147</v>
       </c>
       <c r="F1712" s="4">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G1712" s="4">
         <v>13</v>
       </c>
       <c r="H1712" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I1712" s="4">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="1713" spans="1:9" x14ac:dyDescent="0.25">
@@ -54673,16 +54673,16 @@
         <v>147</v>
       </c>
       <c r="F1715" s="4">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="G1715" s="4">
         <v>13</v>
       </c>
       <c r="H1715" s="4">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I1715" s="4">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="1716" spans="1:9" x14ac:dyDescent="0.25">
@@ -54731,16 +54731,16 @@
         <v>148</v>
       </c>
       <c r="F1717" s="4">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="G1717" s="4">
         <v>45</v>
       </c>
       <c r="H1717" s="4">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="I1717" s="4">
-        <v>59</v>
+        <v>67</v>
       </c>
     </row>
     <row r="1718" spans="1:9" x14ac:dyDescent="0.25">
@@ -54760,16 +54760,16 @@
         <v>148</v>
       </c>
       <c r="F1718" s="4">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="G1718" s="4">
         <v>38</v>
       </c>
       <c r="H1718" s="4">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="I1718" s="4">
-        <v>63</v>
+        <v>73</v>
       </c>
     </row>
     <row r="1719" spans="1:9" x14ac:dyDescent="0.25">
@@ -54789,16 +54789,16 @@
         <v>148</v>
       </c>
       <c r="F1719" s="4">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="G1719" s="4">
         <v>4</v>
       </c>
       <c r="H1719" s="4">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="I1719" s="4">
-        <v>25</v>
+        <v>32</v>
       </c>
     </row>
     <row r="1720" spans="1:9" x14ac:dyDescent="0.25">
@@ -54847,16 +54847,16 @@
         <v>149</v>
       </c>
       <c r="F1721" s="4">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="G1721" s="4">
         <v>37</v>
       </c>
       <c r="H1721" s="4">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="I1721" s="4">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="1722" spans="1:9" x14ac:dyDescent="0.25">
@@ -54876,16 +54876,16 @@
         <v>149</v>
       </c>
       <c r="F1722" s="4">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="G1722" s="4">
         <v>17</v>
       </c>
       <c r="H1722" s="4">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="I1722" s="4">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="1723" spans="1:9" x14ac:dyDescent="0.25">
@@ -54934,16 +54934,16 @@
         <v>149</v>
       </c>
       <c r="F1724" s="4">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="G1724" s="4">
         <v>26</v>
       </c>
       <c r="H1724" s="4">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="I1724" s="4">
-        <v>24</v>
+        <v>40</v>
       </c>
     </row>
     <row r="1725" spans="1:9" x14ac:dyDescent="0.25">
@@ -54992,16 +54992,16 @@
         <v>150</v>
       </c>
       <c r="F1726" s="4">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="G1726" s="4">
         <v>11</v>
       </c>
       <c r="H1726" s="4">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="I1726" s="4">
-        <v>32</v>
+        <v>39</v>
       </c>
     </row>
     <row r="1727" spans="1:9" x14ac:dyDescent="0.25">
@@ -55021,16 +55021,16 @@
         <v>150</v>
       </c>
       <c r="F1727" s="4">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G1727" s="4">
         <v>3</v>
       </c>
       <c r="H1727" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I1727" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1728" spans="1:9" x14ac:dyDescent="0.25">
@@ -55050,16 +55050,16 @@
         <v>150</v>
       </c>
       <c r="F1728" s="4">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G1728" s="4">
         <v>21</v>
       </c>
       <c r="H1728" s="4">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I1728" s="4">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="1729" spans="1:9" x14ac:dyDescent="0.25">
@@ -55079,16 +55079,16 @@
         <v>150</v>
       </c>
       <c r="F1729" s="4">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G1729" s="4">
         <v>6</v>
       </c>
       <c r="H1729" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I1729" s="4">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1730" spans="1:9" x14ac:dyDescent="0.25">
@@ -55108,16 +55108,16 @@
         <v>150</v>
       </c>
       <c r="F1730" s="4">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G1730" s="4">
         <v>14</v>
       </c>
       <c r="H1730" s="4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I1730" s="4">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1731" spans="1:9" x14ac:dyDescent="0.25">

--- a/0. capaian omnibus 2026.xlsx
+++ b/0. capaian omnibus 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\0. codex\0. Omnibus\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9E52D96-81A9-4AF2-9D21-51CC00E5E3E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76D6C95E-4E9C-4AA1-8637-5B0A1FB6603A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-109" yWindow="-109" windowWidth="26301" windowHeight="15800" xr2:uid="{ABC9ECFA-347A-408B-B0D0-6F1CCFF80879}"/>
   </bookViews>
@@ -5112,16 +5112,16 @@
         <v>1</v>
       </c>
       <c r="F6" s="4">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G6" s="4">
         <v>22</v>
       </c>
       <c r="H6" s="4">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I6" s="4">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
@@ -5866,16 +5866,16 @@
         <v>3</v>
       </c>
       <c r="F32" s="4">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G32" s="4">
         <v>9</v>
       </c>
       <c r="H32" s="4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I32" s="4">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
@@ -6272,16 +6272,16 @@
         <v>4</v>
       </c>
       <c r="F46" s="4">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G46" s="4">
         <v>2</v>
       </c>
       <c r="H46" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I46" s="4">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
@@ -6475,16 +6475,16 @@
         <v>5</v>
       </c>
       <c r="F53" s="4">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G53" s="4">
         <v>32</v>
       </c>
       <c r="H53" s="4">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I53" s="4">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
@@ -6765,16 +6765,16 @@
         <v>6</v>
       </c>
       <c r="F63" s="4">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G63" s="4">
         <v>31</v>
       </c>
       <c r="H63" s="4">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I63" s="4">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
@@ -6881,16 +6881,16 @@
         <v>6</v>
       </c>
       <c r="F67" s="4">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G67" s="4">
         <v>8</v>
       </c>
       <c r="H67" s="4">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I67" s="4">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
@@ -7490,16 +7490,16 @@
         <v>8</v>
       </c>
       <c r="F88" s="4">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G88" s="4">
         <v>11</v>
       </c>
       <c r="H88" s="4">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I88" s="4">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.25">
@@ -7722,16 +7722,16 @@
         <v>8</v>
       </c>
       <c r="F96" s="4">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G96" s="4">
         <v>6</v>
       </c>
       <c r="H96" s="4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I96" s="4">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.25">
@@ -8331,16 +8331,16 @@
         <v>10</v>
       </c>
       <c r="F117" s="4">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G117" s="4">
         <v>24</v>
       </c>
       <c r="H117" s="4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I117" s="4">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.25">
@@ -8360,16 +8360,16 @@
         <v>10</v>
       </c>
       <c r="F118" s="4">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G118" s="4">
         <v>5</v>
       </c>
       <c r="H118" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I118" s="4">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.25">
@@ -8592,16 +8592,16 @@
         <v>11</v>
       </c>
       <c r="F126" s="4">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G126" s="4">
         <v>8</v>
       </c>
       <c r="H126" s="4">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I126" s="4">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.25">
@@ -8911,16 +8911,16 @@
         <v>12</v>
       </c>
       <c r="F137" s="4">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G137" s="4">
         <v>39</v>
       </c>
       <c r="H137" s="4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I137" s="4">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.25">
@@ -9114,16 +9114,16 @@
         <v>12</v>
       </c>
       <c r="F144" s="4">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G144" s="4">
         <v>12</v>
       </c>
       <c r="H144" s="4">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I144" s="4">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.25">
@@ -9549,16 +9549,16 @@
         <v>13</v>
       </c>
       <c r="F159" s="4">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G159" s="4">
         <v>11</v>
       </c>
       <c r="H159" s="4">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="I159" s="4">
-        <v>47</v>
+        <v>51</v>
       </c>
     </row>
     <row r="160" spans="1:9" x14ac:dyDescent="0.25">
@@ -9781,16 +9781,16 @@
         <v>14</v>
       </c>
       <c r="F167" s="4">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G167" s="4">
         <v>43</v>
       </c>
       <c r="H167" s="4">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I167" s="4">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="168" spans="1:9" x14ac:dyDescent="0.25">
@@ -9839,16 +9839,16 @@
         <v>14</v>
       </c>
       <c r="F169" s="4">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G169" s="4">
         <v>18</v>
       </c>
       <c r="H169" s="4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I169" s="4">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="170" spans="1:9" x14ac:dyDescent="0.25">
@@ -9897,16 +9897,16 @@
         <v>14</v>
       </c>
       <c r="F171" s="4">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G171" s="4">
         <v>2</v>
       </c>
       <c r="H171" s="4">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I171" s="4">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="172" spans="1:9" x14ac:dyDescent="0.25">
@@ -10071,16 +10071,16 @@
         <v>15</v>
       </c>
       <c r="F177" s="4">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G177" s="4">
         <v>10</v>
       </c>
       <c r="H177" s="4">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I177" s="4">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="178" spans="1:9" x14ac:dyDescent="0.25">
@@ -10274,16 +10274,16 @@
         <v>15</v>
       </c>
       <c r="F184" s="4">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G184" s="4">
         <v>26</v>
       </c>
       <c r="H184" s="4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I184" s="4">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="185" spans="1:9" x14ac:dyDescent="0.25">
@@ -10419,16 +10419,16 @@
         <v>16</v>
       </c>
       <c r="F189" s="4">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G189" s="4">
         <v>10</v>
       </c>
       <c r="H189" s="4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I189" s="4">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="190" spans="1:9" x14ac:dyDescent="0.25">
@@ -10448,16 +10448,16 @@
         <v>16</v>
       </c>
       <c r="F190" s="4">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="G190" s="4">
         <v>72</v>
       </c>
       <c r="H190" s="4">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I190" s="4">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="191" spans="1:9" x14ac:dyDescent="0.25">
@@ -10477,16 +10477,16 @@
         <v>16</v>
       </c>
       <c r="F191" s="4">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G191" s="4">
         <v>5</v>
       </c>
       <c r="H191" s="4">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I191" s="4">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="192" spans="1:9" x14ac:dyDescent="0.25">
@@ -10622,16 +10622,16 @@
         <v>17</v>
       </c>
       <c r="F196" s="4">
+        <v>4</v>
+      </c>
+      <c r="G196" s="4">
+        <v>1</v>
+      </c>
+      <c r="H196" s="4">
+        <v>2</v>
+      </c>
+      <c r="I196" s="4">
         <v>3</v>
-      </c>
-      <c r="G196" s="4">
-        <v>1</v>
-      </c>
-      <c r="H196" s="4">
-        <v>1</v>
-      </c>
-      <c r="I196" s="4">
-        <v>2</v>
       </c>
     </row>
     <row r="197" spans="1:9" x14ac:dyDescent="0.25">
@@ -10796,16 +10796,16 @@
         <v>17</v>
       </c>
       <c r="F202" s="4">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G202" s="4">
         <v>5</v>
       </c>
       <c r="H202" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I202" s="4">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="203" spans="1:9" x14ac:dyDescent="0.25">
@@ -11144,16 +11144,16 @@
         <v>18</v>
       </c>
       <c r="F214" s="4">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="G214" s="4">
         <v>8</v>
       </c>
       <c r="H214" s="4">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I214" s="4">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="215" spans="1:9" x14ac:dyDescent="0.25">
@@ -11695,16 +11695,16 @@
         <v>19</v>
       </c>
       <c r="F233" s="4">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G233" s="4">
         <v>2</v>
       </c>
       <c r="H233" s="4">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I233" s="4">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="234" spans="1:9" x14ac:dyDescent="0.25">
@@ -11782,16 +11782,16 @@
         <v>20</v>
       </c>
       <c r="F236" s="4">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G236" s="4">
         <v>20</v>
       </c>
       <c r="H236" s="4">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I236" s="4">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="237" spans="1:9" x14ac:dyDescent="0.25">
@@ -12101,16 +12101,16 @@
         <v>21</v>
       </c>
       <c r="F247" s="4">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G247" s="4">
         <v>22</v>
       </c>
       <c r="H247" s="4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I247" s="4">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="248" spans="1:9" x14ac:dyDescent="0.25">
@@ -12159,16 +12159,16 @@
         <v>21</v>
       </c>
       <c r="F249" s="4">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G249" s="4">
         <v>9</v>
       </c>
       <c r="H249" s="4">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I249" s="4">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="250" spans="1:9" x14ac:dyDescent="0.25">
@@ -12275,16 +12275,16 @@
         <v>21</v>
       </c>
       <c r="F253" s="4">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G253" s="4">
         <v>23</v>
       </c>
       <c r="H253" s="4">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I253" s="4">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="254" spans="1:9" x14ac:dyDescent="0.25">
@@ -12449,16 +12449,16 @@
         <v>22</v>
       </c>
       <c r="F259" s="4">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G259" s="4">
         <v>18</v>
       </c>
       <c r="H259" s="4">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I259" s="4">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="260" spans="1:9" x14ac:dyDescent="0.25">
@@ -12826,16 +12826,16 @@
         <v>23</v>
       </c>
       <c r="F272" s="4">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G272" s="4">
         <v>33</v>
       </c>
       <c r="H272" s="4">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I272" s="4">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="273" spans="1:9" x14ac:dyDescent="0.25">
@@ -12971,16 +12971,16 @@
         <v>24</v>
       </c>
       <c r="F277" s="4">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="G277" s="4">
         <v>40</v>
       </c>
       <c r="H277" s="4">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I277" s="4">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="278" spans="1:9" x14ac:dyDescent="0.25">
@@ -13522,16 +13522,16 @@
         <v>25</v>
       </c>
       <c r="F296" s="4">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G296" s="4">
         <v>7</v>
       </c>
       <c r="H296" s="4">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I296" s="4">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="297" spans="1:9" x14ac:dyDescent="0.25">
@@ -13638,16 +13638,16 @@
         <v>26</v>
       </c>
       <c r="F300" s="4">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G300" s="4">
         <v>3</v>
       </c>
       <c r="H300" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I300" s="4">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="301" spans="1:9" x14ac:dyDescent="0.25">
@@ -13783,16 +13783,16 @@
         <v>26</v>
       </c>
       <c r="F305" s="4">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="G305" s="4">
         <v>62</v>
       </c>
       <c r="H305" s="4">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I305" s="4">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="306" spans="1:9" x14ac:dyDescent="0.25">
@@ -13812,16 +13812,16 @@
         <v>26</v>
       </c>
       <c r="F306" s="4">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G306" s="4">
         <v>4</v>
       </c>
       <c r="H306" s="4">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I306" s="4">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="307" spans="1:9" x14ac:dyDescent="0.25">
@@ -13986,16 +13986,16 @@
         <v>27</v>
       </c>
       <c r="F312" s="4">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G312" s="4">
         <v>1</v>
       </c>
       <c r="H312" s="4">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I312" s="4">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="313" spans="1:9" x14ac:dyDescent="0.25">
@@ -14044,16 +14044,16 @@
         <v>27</v>
       </c>
       <c r="F314" s="4">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="G314" s="4">
         <v>44</v>
       </c>
       <c r="H314" s="4">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I314" s="4">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="315" spans="1:9" x14ac:dyDescent="0.25">
@@ -14160,16 +14160,16 @@
         <v>27</v>
       </c>
       <c r="F318" s="4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G318" s="4">
         <v>4</v>
       </c>
       <c r="H318" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I318" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="319" spans="1:9" x14ac:dyDescent="0.25">
@@ -14305,16 +14305,16 @@
         <v>28</v>
       </c>
       <c r="F323" s="4">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G323" s="4">
         <v>4</v>
       </c>
       <c r="H323" s="4">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I323" s="4">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="324" spans="1:9" x14ac:dyDescent="0.25">
@@ -14508,16 +14508,16 @@
         <v>28</v>
       </c>
       <c r="F330" s="4">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G330" s="4">
         <v>4</v>
       </c>
       <c r="H330" s="4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I330" s="4">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="331" spans="1:9" x14ac:dyDescent="0.25">
@@ -14769,16 +14769,16 @@
         <v>29</v>
       </c>
       <c r="F339" s="4">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G339" s="4">
         <v>12</v>
       </c>
       <c r="H339" s="4">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I339" s="4">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="340" spans="1:9" x14ac:dyDescent="0.25">
@@ -14798,16 +14798,16 @@
         <v>29</v>
       </c>
       <c r="F340" s="4">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="G340" s="4">
         <v>66</v>
       </c>
       <c r="H340" s="4">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I340" s="4">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="341" spans="1:9" x14ac:dyDescent="0.25">
@@ -15291,16 +15291,16 @@
         <v>30</v>
       </c>
       <c r="F357" s="4">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="G357" s="4">
         <v>44</v>
       </c>
       <c r="H357" s="4">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I357" s="4">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="358" spans="1:9" x14ac:dyDescent="0.25">
@@ -15610,16 +15610,16 @@
         <v>31</v>
       </c>
       <c r="F368" s="4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G368" s="4">
         <v>3</v>
       </c>
       <c r="H368" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I368" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="369" spans="1:9" x14ac:dyDescent="0.25">
@@ -15639,16 +15639,16 @@
         <v>31</v>
       </c>
       <c r="F369" s="4">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G369" s="4">
         <v>10</v>
       </c>
       <c r="H369" s="4">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I369" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="370" spans="1:9" x14ac:dyDescent="0.25">
@@ -15668,16 +15668,16 @@
         <v>31</v>
       </c>
       <c r="F370" s="4">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G370" s="4">
         <v>7</v>
       </c>
       <c r="H370" s="4">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I370" s="4">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="371" spans="1:9" x14ac:dyDescent="0.25">
@@ -16016,16 +16016,16 @@
         <v>32</v>
       </c>
       <c r="F382" s="4">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="G382" s="4">
         <v>61</v>
       </c>
       <c r="H382" s="4">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I382" s="4">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="383" spans="1:9" x14ac:dyDescent="0.25">
@@ -16074,16 +16074,16 @@
         <v>32</v>
       </c>
       <c r="F384" s="4">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G384" s="4">
         <v>5</v>
       </c>
       <c r="H384" s="4">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I384" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="385" spans="1:9" x14ac:dyDescent="0.25">
@@ -16277,16 +16277,16 @@
         <v>33</v>
       </c>
       <c r="F391" s="4">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G391" s="4">
         <v>4</v>
       </c>
       <c r="H391" s="4">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="I391" s="4">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="392" spans="1:9" x14ac:dyDescent="0.25">
@@ -16596,16 +16596,16 @@
         <v>33</v>
       </c>
       <c r="F402" s="4">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="G402" s="4">
         <v>10</v>
       </c>
       <c r="H402" s="4">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="I402" s="4">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="403" spans="1:9" x14ac:dyDescent="0.25">
@@ -16625,16 +16625,16 @@
         <v>33</v>
       </c>
       <c r="F403" s="4">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="G403" s="4">
         <v>58</v>
       </c>
       <c r="H403" s="4">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I403" s="4">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="404" spans="1:9" x14ac:dyDescent="0.25">
@@ -16886,16 +16886,16 @@
         <v>34</v>
       </c>
       <c r="F412" s="4">
+        <v>8</v>
+      </c>
+      <c r="G412" s="4">
+        <v>1</v>
+      </c>
+      <c r="H412" s="4">
+        <v>2</v>
+      </c>
+      <c r="I412" s="4">
         <v>7</v>
-      </c>
-      <c r="G412" s="4">
-        <v>1</v>
-      </c>
-      <c r="H412" s="4">
-        <v>1</v>
-      </c>
-      <c r="I412" s="4">
-        <v>6</v>
       </c>
     </row>
     <row r="413" spans="1:9" x14ac:dyDescent="0.25">
@@ -16973,16 +16973,16 @@
         <v>34</v>
       </c>
       <c r="F415" s="4">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G415" s="4">
         <v>7</v>
       </c>
       <c r="H415" s="4">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I415" s="4">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="416" spans="1:9" x14ac:dyDescent="0.25">
@@ -17031,16 +17031,16 @@
         <v>34</v>
       </c>
       <c r="F417" s="4">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G417" s="4">
         <v>6</v>
       </c>
       <c r="H417" s="4">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I417" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="418" spans="1:9" x14ac:dyDescent="0.25">
@@ -17292,16 +17292,16 @@
         <v>35</v>
       </c>
       <c r="F426" s="4">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="G426" s="4">
         <v>44</v>
       </c>
       <c r="H426" s="4">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I426" s="4">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="427" spans="1:9" x14ac:dyDescent="0.25">
@@ -17321,16 +17321,16 @@
         <v>35</v>
       </c>
       <c r="F427" s="4">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G427" s="4">
         <v>10</v>
       </c>
       <c r="H427" s="4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I427" s="4">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="428" spans="1:9" x14ac:dyDescent="0.25">
@@ -17350,16 +17350,16 @@
         <v>35</v>
       </c>
       <c r="F428" s="4">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G428" s="4">
         <v>7</v>
       </c>
       <c r="H428" s="4">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I428" s="4">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="429" spans="1:9" x14ac:dyDescent="0.25">
@@ -17437,16 +17437,16 @@
         <v>35</v>
       </c>
       <c r="F431" s="4">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G431" s="4">
         <v>25</v>
       </c>
       <c r="H431" s="4">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I431" s="4">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="432" spans="1:9" x14ac:dyDescent="0.25">
@@ -17553,16 +17553,16 @@
         <v>35</v>
       </c>
       <c r="F435" s="4">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G435" s="4">
         <v>8</v>
       </c>
       <c r="H435" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I435" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="436" spans="1:9" x14ac:dyDescent="0.25">
@@ -17698,16 +17698,16 @@
         <v>36</v>
       </c>
       <c r="F440" s="4">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G440" s="4">
         <v>20</v>
       </c>
       <c r="H440" s="4">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I440" s="4">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="441" spans="1:9" x14ac:dyDescent="0.25">
@@ -17727,16 +17727,16 @@
         <v>36</v>
       </c>
       <c r="F441" s="4">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="G441" s="4">
         <v>34</v>
       </c>
       <c r="H441" s="4">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="I441" s="4">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="442" spans="1:9" x14ac:dyDescent="0.25">
@@ -17814,16 +17814,16 @@
         <v>36</v>
       </c>
       <c r="F444" s="4">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G444" s="4">
         <v>7</v>
       </c>
       <c r="H444" s="4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I444" s="4">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="445" spans="1:9" x14ac:dyDescent="0.25">
@@ -17901,16 +17901,16 @@
         <v>36</v>
       </c>
       <c r="F447" s="4">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G447" s="4">
         <v>7</v>
       </c>
       <c r="H447" s="4">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="I447" s="4">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="448" spans="1:9" x14ac:dyDescent="0.25">
@@ -18191,16 +18191,16 @@
         <v>37</v>
       </c>
       <c r="F457" s="4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G457" s="4">
         <v>2</v>
       </c>
       <c r="H457" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I457" s="4">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="458" spans="1:9" x14ac:dyDescent="0.25">
@@ -18220,16 +18220,16 @@
         <v>37</v>
       </c>
       <c r="F458" s="4">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G458" s="4">
         <v>12</v>
       </c>
       <c r="H458" s="4">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I458" s="4">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="459" spans="1:9" x14ac:dyDescent="0.25">
@@ -18249,16 +18249,16 @@
         <v>37</v>
       </c>
       <c r="F459" s="4">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G459" s="4">
         <v>7</v>
       </c>
       <c r="H459" s="4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I459" s="4">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="460" spans="1:9" x14ac:dyDescent="0.25">
@@ -18394,16 +18394,16 @@
         <v>38</v>
       </c>
       <c r="F464" s="4">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G464" s="4">
         <v>14</v>
       </c>
       <c r="H464" s="4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I464" s="4">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="465" spans="1:9" x14ac:dyDescent="0.25">
@@ -18452,16 +18452,16 @@
         <v>38</v>
       </c>
       <c r="F466" s="4">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G466" s="4">
         <v>21</v>
       </c>
       <c r="H466" s="4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I466" s="4">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="467" spans="1:9" x14ac:dyDescent="0.25">
@@ -18539,16 +18539,16 @@
         <v>38</v>
       </c>
       <c r="F469" s="4">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G469" s="4">
         <v>8</v>
       </c>
       <c r="H469" s="4">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I469" s="4">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="470" spans="1:9" x14ac:dyDescent="0.25">
@@ -18597,16 +18597,16 @@
         <v>39</v>
       </c>
       <c r="F471" s="4">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="G471" s="4">
         <v>68</v>
       </c>
       <c r="H471" s="4">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I471" s="4">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="472" spans="1:9" x14ac:dyDescent="0.25">
@@ -18626,16 +18626,16 @@
         <v>39</v>
       </c>
       <c r="F472" s="4">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G472" s="4">
         <v>7</v>
       </c>
       <c r="H472" s="4">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I472" s="4">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="473" spans="1:9" x14ac:dyDescent="0.25">
@@ -18742,16 +18742,16 @@
         <v>39</v>
       </c>
       <c r="F476" s="4">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G476" s="4">
         <v>5</v>
       </c>
       <c r="H476" s="4">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I476" s="4">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="477" spans="1:9" x14ac:dyDescent="0.25">
@@ -19090,16 +19090,16 @@
         <v>40</v>
       </c>
       <c r="F488" s="4">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G488" s="4">
         <v>5</v>
       </c>
       <c r="H488" s="4">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="I488" s="4">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="489" spans="1:9" x14ac:dyDescent="0.25">
@@ -19235,16 +19235,16 @@
         <v>41</v>
       </c>
       <c r="F493" s="4">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G493" s="4">
         <v>35</v>
       </c>
       <c r="H493" s="4">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I493" s="4">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="494" spans="1:9" x14ac:dyDescent="0.25">
@@ -19409,16 +19409,16 @@
         <v>41</v>
       </c>
       <c r="F499" s="4">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G499" s="4">
         <v>12</v>
       </c>
       <c r="H499" s="4">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I499" s="4">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="500" spans="1:9" x14ac:dyDescent="0.25">
@@ -19496,16 +19496,16 @@
         <v>41</v>
       </c>
       <c r="F502" s="4">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G502" s="4">
         <v>14</v>
       </c>
       <c r="H502" s="4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I502" s="4">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="503" spans="1:9" x14ac:dyDescent="0.25">
@@ -19757,16 +19757,16 @@
         <v>42</v>
       </c>
       <c r="F511" s="4">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="G511" s="4">
         <v>64</v>
       </c>
       <c r="H511" s="4">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I511" s="4">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="512" spans="1:9" x14ac:dyDescent="0.25">
@@ -20047,16 +20047,16 @@
         <v>43</v>
       </c>
       <c r="F521" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G521" s="4">
         <v>6</v>
       </c>
       <c r="H521" s="4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I521" s="4">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="522" spans="1:9" x14ac:dyDescent="0.25">
@@ -20076,16 +20076,16 @@
         <v>43</v>
       </c>
       <c r="F522" s="4">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="G522" s="4">
         <v>47</v>
       </c>
       <c r="H522" s="4">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I522" s="4">
-        <v>115</v>
+        <v>119</v>
       </c>
     </row>
     <row r="523" spans="1:9" x14ac:dyDescent="0.25">
@@ -20134,16 +20134,16 @@
         <v>43</v>
       </c>
       <c r="F524" s="4">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G524" s="4">
         <v>10</v>
       </c>
       <c r="H524" s="4">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I524" s="4">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="525" spans="1:9" x14ac:dyDescent="0.25">
@@ -20279,16 +20279,16 @@
         <v>44</v>
       </c>
       <c r="F529" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G529" s="4">
         <v>0</v>
       </c>
       <c r="H529" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I529" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="530" spans="1:9" x14ac:dyDescent="0.25">
@@ -20337,16 +20337,16 @@
         <v>44</v>
       </c>
       <c r="F531" s="4">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="G531" s="4">
         <v>39</v>
       </c>
       <c r="H531" s="4">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I531" s="4">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="532" spans="1:9" x14ac:dyDescent="0.25">
@@ -20453,16 +20453,16 @@
         <v>44</v>
       </c>
       <c r="F535" s="4">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G535" s="4">
         <v>2</v>
       </c>
       <c r="H535" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I535" s="4">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="536" spans="1:9" x14ac:dyDescent="0.25">
@@ -20482,16 +20482,16 @@
         <v>44</v>
       </c>
       <c r="F536" s="4">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G536" s="4">
         <v>16</v>
       </c>
       <c r="H536" s="4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I536" s="4">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="537" spans="1:9" x14ac:dyDescent="0.25">
@@ -20685,16 +20685,16 @@
         <v>45</v>
       </c>
       <c r="F543" s="4">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="G543" s="4">
         <v>12</v>
       </c>
       <c r="H543" s="4">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I543" s="4">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="544" spans="1:9" x14ac:dyDescent="0.25">
@@ -20801,16 +20801,16 @@
         <v>45</v>
       </c>
       <c r="F547" s="4">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G547" s="4">
         <v>27</v>
       </c>
       <c r="H547" s="4">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I547" s="4">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="548" spans="1:9" x14ac:dyDescent="0.25">
@@ -20859,16 +20859,16 @@
         <v>45</v>
       </c>
       <c r="F549" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G549" s="4">
         <v>2</v>
       </c>
       <c r="H549" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I549" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="550" spans="1:9" x14ac:dyDescent="0.25">
@@ -21033,16 +21033,16 @@
         <v>46</v>
       </c>
       <c r="F555" s="4">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="G555" s="4">
         <v>77</v>
       </c>
       <c r="H555" s="4">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="I555" s="4">
-        <v>184</v>
+        <v>188</v>
       </c>
     </row>
     <row r="556" spans="1:9" x14ac:dyDescent="0.25">
@@ -21439,16 +21439,16 @@
         <v>47</v>
       </c>
       <c r="F569" s="4">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G569" s="4">
         <v>25</v>
       </c>
       <c r="H569" s="4">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I569" s="4">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="570" spans="1:9" x14ac:dyDescent="0.25">
@@ -21758,16 +21758,16 @@
         <v>48</v>
       </c>
       <c r="F580" s="4">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G580" s="4">
         <v>15</v>
       </c>
       <c r="H580" s="4">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I580" s="4">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="581" spans="1:9" x14ac:dyDescent="0.25">
@@ -21874,16 +21874,16 @@
         <v>48</v>
       </c>
       <c r="F584" s="4">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G584" s="4">
         <v>18</v>
       </c>
       <c r="H584" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I584" s="4">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="585" spans="1:9" x14ac:dyDescent="0.25">
@@ -21932,16 +21932,16 @@
         <v>48</v>
       </c>
       <c r="F586" s="4">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G586" s="4">
         <v>14</v>
       </c>
       <c r="H586" s="4">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I586" s="4">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="587" spans="1:9" x14ac:dyDescent="0.25">
@@ -22425,16 +22425,16 @@
         <v>50</v>
       </c>
       <c r="F603" s="4">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G603" s="4">
         <v>9</v>
       </c>
       <c r="H603" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I603" s="4">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="604" spans="1:9" x14ac:dyDescent="0.25">
@@ -22483,16 +22483,16 @@
         <v>50</v>
       </c>
       <c r="F605" s="4">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="G605" s="4">
         <v>55</v>
       </c>
       <c r="H605" s="4">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I605" s="4">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="606" spans="1:9" x14ac:dyDescent="0.25">
@@ -22541,16 +22541,16 @@
         <v>50</v>
       </c>
       <c r="F607" s="4">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G607" s="4">
         <v>10</v>
       </c>
       <c r="H607" s="4">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I607" s="4">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="608" spans="1:9" x14ac:dyDescent="0.25">
@@ -22744,16 +22744,16 @@
         <v>51</v>
       </c>
       <c r="F614" s="4">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G614" s="4">
         <v>34</v>
       </c>
       <c r="H614" s="4">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I614" s="4">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="615" spans="1:9" x14ac:dyDescent="0.25">
@@ -22860,16 +22860,16 @@
         <v>51</v>
       </c>
       <c r="F618" s="4">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G618" s="4">
         <v>10</v>
       </c>
       <c r="H618" s="4">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I618" s="4">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="619" spans="1:9" x14ac:dyDescent="0.25">
@@ -22976,16 +22976,16 @@
         <v>51</v>
       </c>
       <c r="F622" s="4">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G622" s="4">
         <v>15</v>
       </c>
       <c r="H622" s="4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I622" s="4">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="623" spans="1:9" x14ac:dyDescent="0.25">
@@ -23179,16 +23179,16 @@
         <v>52</v>
       </c>
       <c r="F629" s="4">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G629" s="4">
         <v>8</v>
       </c>
       <c r="H629" s="4">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I629" s="4">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="630" spans="1:9" x14ac:dyDescent="0.25">
@@ -23295,16 +23295,16 @@
         <v>52</v>
       </c>
       <c r="F633" s="4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G633" s="4">
         <v>4</v>
       </c>
       <c r="H633" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I633" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="634" spans="1:9" x14ac:dyDescent="0.25">
@@ -23353,16 +23353,16 @@
         <v>52</v>
       </c>
       <c r="F635" s="4">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G635" s="4">
         <v>6</v>
       </c>
       <c r="H635" s="4">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I635" s="4">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="636" spans="1:9" x14ac:dyDescent="0.25">
@@ -23701,16 +23701,16 @@
         <v>53</v>
       </c>
       <c r="F647" s="4">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G647" s="4">
         <v>13</v>
       </c>
       <c r="H647" s="4">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I647" s="4">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="648" spans="1:9" x14ac:dyDescent="0.25">
@@ -23730,16 +23730,16 @@
         <v>53</v>
       </c>
       <c r="F648" s="4">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="G648" s="4">
         <v>43</v>
       </c>
       <c r="H648" s="4">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I648" s="4">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="649" spans="1:9" x14ac:dyDescent="0.25">
@@ -23846,16 +23846,16 @@
         <v>53</v>
       </c>
       <c r="F652" s="4">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G652" s="4">
         <v>2</v>
       </c>
       <c r="H652" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I652" s="4">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="653" spans="1:9" x14ac:dyDescent="0.25">
@@ -23933,16 +23933,16 @@
         <v>54</v>
       </c>
       <c r="F655" s="4">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="G655" s="4">
         <v>42</v>
       </c>
       <c r="H655" s="4">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I655" s="4">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="656" spans="1:9" x14ac:dyDescent="0.25">
@@ -24020,16 +24020,16 @@
         <v>54</v>
       </c>
       <c r="F658" s="4">
+        <v>14</v>
+      </c>
+      <c r="G658" s="4">
+        <v>1</v>
+      </c>
+      <c r="H658" s="4">
+        <v>4</v>
+      </c>
+      <c r="I658" s="4">
         <v>13</v>
-      </c>
-      <c r="G658" s="4">
-        <v>1</v>
-      </c>
-      <c r="H658" s="4">
-        <v>3</v>
-      </c>
-      <c r="I658" s="4">
-        <v>12</v>
       </c>
     </row>
     <row r="659" spans="1:9" x14ac:dyDescent="0.25">
@@ -24049,16 +24049,16 @@
         <v>54</v>
       </c>
       <c r="F659" s="4">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G659" s="4">
         <v>9</v>
       </c>
       <c r="H659" s="4">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I659" s="4">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="660" spans="1:9" x14ac:dyDescent="0.25">
@@ -24107,16 +24107,16 @@
         <v>54</v>
       </c>
       <c r="F661" s="4">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G661" s="4">
         <v>12</v>
       </c>
       <c r="H661" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I661" s="4">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="662" spans="1:9" x14ac:dyDescent="0.25">
@@ -24194,16 +24194,16 @@
         <v>55</v>
       </c>
       <c r="F664" s="4">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G664" s="4">
         <v>7</v>
       </c>
       <c r="H664" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I664" s="4">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="665" spans="1:9" x14ac:dyDescent="0.25">
@@ -24397,16 +24397,16 @@
         <v>55</v>
       </c>
       <c r="F671" s="4">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G671" s="4">
         <v>28</v>
       </c>
       <c r="H671" s="4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I671" s="4">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="672" spans="1:9" x14ac:dyDescent="0.25">
@@ -24571,16 +24571,16 @@
         <v>56</v>
       </c>
       <c r="F677" s="4">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="G677" s="4">
         <v>53</v>
       </c>
       <c r="H677" s="4">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I677" s="4">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="678" spans="1:9" x14ac:dyDescent="0.25">
@@ -24658,16 +24658,16 @@
         <v>56</v>
       </c>
       <c r="F680" s="4">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="G680" s="4">
         <v>6</v>
       </c>
       <c r="H680" s="4">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="I680" s="4">
-        <v>27</v>
+        <v>32</v>
       </c>
     </row>
     <row r="681" spans="1:9" x14ac:dyDescent="0.25">
@@ -24861,16 +24861,16 @@
         <v>57</v>
       </c>
       <c r="F687" s="4">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="G687" s="4">
         <v>34</v>
       </c>
       <c r="H687" s="4">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I687" s="4">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="688" spans="1:9" x14ac:dyDescent="0.25">
@@ -24890,16 +24890,16 @@
         <v>57</v>
       </c>
       <c r="F688" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G688" s="4">
         <v>0</v>
       </c>
       <c r="H688" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I688" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="689" spans="1:9" x14ac:dyDescent="0.25">
@@ -24948,16 +24948,16 @@
         <v>57</v>
       </c>
       <c r="F690" s="4">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G690" s="4">
         <v>1</v>
       </c>
       <c r="H690" s="4">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I690" s="4">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="691" spans="1:9" x14ac:dyDescent="0.25">
@@ -25064,16 +25064,16 @@
         <v>57</v>
       </c>
       <c r="F694" s="4">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="G694" s="4">
         <v>51</v>
       </c>
       <c r="H694" s="4">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="I694" s="4">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="695" spans="1:9" x14ac:dyDescent="0.25">
@@ -25209,16 +25209,16 @@
         <v>58</v>
       </c>
       <c r="F699" s="4">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G699" s="4">
         <v>23</v>
       </c>
       <c r="H699" s="4">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I699" s="4">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="700" spans="1:9" x14ac:dyDescent="0.25">
@@ -25238,16 +25238,16 @@
         <v>58</v>
       </c>
       <c r="F700" s="4">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G700" s="4">
         <v>7</v>
       </c>
       <c r="H700" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I700" s="4">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="701" spans="1:9" x14ac:dyDescent="0.25">
@@ -25325,16 +25325,16 @@
         <v>58</v>
       </c>
       <c r="F703" s="4">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G703" s="4">
         <v>8</v>
       </c>
       <c r="H703" s="4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I703" s="4">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="704" spans="1:9" x14ac:dyDescent="0.25">
@@ -25354,16 +25354,16 @@
         <v>58</v>
       </c>
       <c r="F704" s="4">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G704" s="4">
         <v>13</v>
       </c>
       <c r="H704" s="4">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I704" s="4">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="705" spans="1:9" x14ac:dyDescent="0.25">
@@ -25615,16 +25615,16 @@
         <v>59</v>
       </c>
       <c r="F713" s="4">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G713" s="4">
         <v>14</v>
       </c>
       <c r="H713" s="4">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I713" s="4">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="714" spans="1:9" x14ac:dyDescent="0.25">
@@ -25673,16 +25673,16 @@
         <v>59</v>
       </c>
       <c r="F715" s="4">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="G715" s="4">
         <v>41</v>
       </c>
       <c r="H715" s="4">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="I715" s="4">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="716" spans="1:9" x14ac:dyDescent="0.25">
@@ -25760,16 +25760,16 @@
         <v>59</v>
       </c>
       <c r="F718" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G718" s="4">
         <v>4</v>
       </c>
       <c r="H718" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I718" s="4">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="719" spans="1:9" x14ac:dyDescent="0.25">
@@ -25963,16 +25963,16 @@
         <v>60</v>
       </c>
       <c r="F725" s="4">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G725" s="4">
         <v>43</v>
       </c>
       <c r="H725" s="4">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I725" s="4">
-        <v>81</v>
+        <v>85</v>
       </c>
     </row>
     <row r="726" spans="1:9" x14ac:dyDescent="0.25">
@@ -26021,16 +26021,16 @@
         <v>60</v>
       </c>
       <c r="F727" s="4">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G727" s="4">
         <v>17</v>
       </c>
       <c r="H727" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I727" s="4">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="728" spans="1:9" x14ac:dyDescent="0.25">
@@ -26050,16 +26050,16 @@
         <v>60</v>
       </c>
       <c r="F728" s="4">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G728" s="4">
         <v>8</v>
       </c>
       <c r="H728" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I728" s="4">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="729" spans="1:9" x14ac:dyDescent="0.25">
@@ -26108,16 +26108,16 @@
         <v>60</v>
       </c>
       <c r="F730" s="4">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G730" s="4">
         <v>6</v>
       </c>
       <c r="H730" s="4">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I730" s="4">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="731" spans="1:9" x14ac:dyDescent="0.25">
@@ -26224,16 +26224,16 @@
         <v>60</v>
       </c>
       <c r="F734" s="4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G734" s="4">
         <v>5</v>
       </c>
       <c r="H734" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I734" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="735" spans="1:9" x14ac:dyDescent="0.25">
@@ -26282,16 +26282,16 @@
         <v>61</v>
       </c>
       <c r="F736" s="4">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G736" s="4">
         <v>15</v>
       </c>
       <c r="H736" s="4">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I736" s="4">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="737" spans="1:9" x14ac:dyDescent="0.25">
@@ -26369,16 +26369,16 @@
         <v>61</v>
       </c>
       <c r="F739" s="4">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="G739" s="4">
         <v>33</v>
       </c>
       <c r="H739" s="4">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I739" s="4">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="740" spans="1:9" x14ac:dyDescent="0.25">
@@ -26398,16 +26398,16 @@
         <v>61</v>
       </c>
       <c r="F740" s="4">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="G740" s="4">
         <v>31</v>
       </c>
       <c r="H740" s="4">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I740" s="4">
-        <v>106</v>
+        <v>111</v>
       </c>
     </row>
     <row r="741" spans="1:9" x14ac:dyDescent="0.25">
@@ -26456,16 +26456,16 @@
         <v>61</v>
       </c>
       <c r="F742" s="4">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G742" s="4">
         <v>2</v>
       </c>
       <c r="H742" s="4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I742" s="4">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="743" spans="1:9" x14ac:dyDescent="0.25">
@@ -26572,16 +26572,16 @@
         <v>62</v>
       </c>
       <c r="F746" s="4">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="G746" s="4">
         <v>9</v>
       </c>
       <c r="H746" s="4">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="I746" s="4">
-        <v>27</v>
+        <v>32</v>
       </c>
     </row>
     <row r="747" spans="1:9" x14ac:dyDescent="0.25">
@@ -26630,16 +26630,16 @@
         <v>62</v>
       </c>
       <c r="F748" s="4">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="G748" s="4">
         <v>68</v>
       </c>
       <c r="H748" s="4">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="I748" s="4">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="749" spans="1:9" x14ac:dyDescent="0.25">
@@ -26775,16 +26775,16 @@
         <v>62</v>
       </c>
       <c r="F753" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G753" s="4">
         <v>0</v>
       </c>
       <c r="H753" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I753" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="754" spans="1:9" x14ac:dyDescent="0.25">
@@ -26862,16 +26862,16 @@
         <v>63</v>
       </c>
       <c r="F756" s="4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G756" s="4">
         <v>3</v>
       </c>
       <c r="H756" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I756" s="4">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="757" spans="1:9" x14ac:dyDescent="0.25">
@@ -26949,16 +26949,16 @@
         <v>63</v>
       </c>
       <c r="F759" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G759" s="4">
         <v>1</v>
       </c>
       <c r="H759" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I759" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="760" spans="1:9" x14ac:dyDescent="0.25">
@@ -27065,16 +27065,16 @@
         <v>63</v>
       </c>
       <c r="F763" s="4">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="G763" s="4">
         <v>6</v>
       </c>
       <c r="H763" s="4">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="I763" s="4">
-        <v>25</v>
+        <v>34</v>
       </c>
     </row>
     <row r="764" spans="1:9" x14ac:dyDescent="0.25">
@@ -27094,16 +27094,16 @@
         <v>63</v>
       </c>
       <c r="F764" s="4">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="G764" s="4">
         <v>29</v>
       </c>
       <c r="H764" s="4">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I764" s="4">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="765" spans="1:9" x14ac:dyDescent="0.25">
@@ -27210,16 +27210,16 @@
         <v>64</v>
       </c>
       <c r="F768" s="4">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G768" s="4">
         <v>5</v>
       </c>
       <c r="H768" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I768" s="4">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="769" spans="1:9" x14ac:dyDescent="0.25">
@@ -27239,16 +27239,16 @@
         <v>64</v>
       </c>
       <c r="F769" s="4">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G769" s="4">
         <v>15</v>
       </c>
       <c r="H769" s="4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I769" s="4">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="770" spans="1:9" x14ac:dyDescent="0.25">
@@ -27268,16 +27268,16 @@
         <v>64</v>
       </c>
       <c r="F770" s="4">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G770" s="4">
         <v>9</v>
       </c>
       <c r="H770" s="4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I770" s="4">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="771" spans="1:9" x14ac:dyDescent="0.25">
@@ -27384,16 +27384,16 @@
         <v>64</v>
       </c>
       <c r="F774" s="4">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G774" s="4">
         <v>26</v>
       </c>
       <c r="H774" s="4">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I774" s="4">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="775" spans="1:9" x14ac:dyDescent="0.25">
@@ -27413,16 +27413,16 @@
         <v>64</v>
       </c>
       <c r="F775" s="4">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G775" s="4">
         <v>16</v>
       </c>
       <c r="H775" s="4">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I775" s="4">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="776" spans="1:9" x14ac:dyDescent="0.25">
@@ -27645,16 +27645,16 @@
         <v>65</v>
       </c>
       <c r="F783" s="4">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G783" s="4">
         <v>7</v>
       </c>
       <c r="H783" s="4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I783" s="4">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="784" spans="1:9" x14ac:dyDescent="0.25">
@@ -27674,16 +27674,16 @@
         <v>65</v>
       </c>
       <c r="F784" s="4">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="G784" s="4">
         <v>71</v>
       </c>
       <c r="H784" s="4">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="I784" s="4">
-        <v>193</v>
+        <v>201</v>
       </c>
     </row>
     <row r="785" spans="1:9" x14ac:dyDescent="0.25">
@@ -27848,16 +27848,16 @@
         <v>66</v>
       </c>
       <c r="F790" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G790" s="4">
         <v>0</v>
       </c>
       <c r="H790" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I790" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="791" spans="1:9" x14ac:dyDescent="0.25">
@@ -27906,16 +27906,16 @@
         <v>66</v>
       </c>
       <c r="F792" s="4">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="G792" s="4">
         <v>29</v>
       </c>
       <c r="H792" s="4">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I792" s="4">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="793" spans="1:9" x14ac:dyDescent="0.25">
@@ -27964,16 +27964,16 @@
         <v>66</v>
       </c>
       <c r="F794" s="4">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G794" s="4">
         <v>14</v>
       </c>
       <c r="H794" s="4">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I794" s="4">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="795" spans="1:9" x14ac:dyDescent="0.25">
@@ -28022,16 +28022,16 @@
         <v>66</v>
       </c>
       <c r="F796" s="4">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G796" s="4">
         <v>52</v>
       </c>
       <c r="H796" s="4">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I796" s="4">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="797" spans="1:9" x14ac:dyDescent="0.25">
@@ -28109,16 +28109,16 @@
         <v>67</v>
       </c>
       <c r="F799" s="4">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G799" s="4">
         <v>21</v>
       </c>
       <c r="H799" s="4">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I799" s="4">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="800" spans="1:9" x14ac:dyDescent="0.25">
@@ -28283,16 +28283,16 @@
         <v>67</v>
       </c>
       <c r="F805" s="4">
+        <v>4</v>
+      </c>
+      <c r="G805" s="4">
+        <v>1</v>
+      </c>
+      <c r="H805" s="4">
         <v>3</v>
       </c>
-      <c r="G805" s="4">
-        <v>1</v>
-      </c>
-      <c r="H805" s="4">
-        <v>2</v>
-      </c>
       <c r="I805" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="806" spans="1:9" x14ac:dyDescent="0.25">
@@ -28312,16 +28312,16 @@
         <v>67</v>
       </c>
       <c r="F806" s="4">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G806" s="4">
         <v>31</v>
       </c>
       <c r="H806" s="4">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I806" s="4">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="807" spans="1:9" x14ac:dyDescent="0.25">
@@ -28370,16 +28370,16 @@
         <v>67</v>
       </c>
       <c r="F808" s="4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G808" s="4">
         <v>0</v>
       </c>
       <c r="H808" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I808" s="4">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="809" spans="1:9" x14ac:dyDescent="0.25">
@@ -28515,16 +28515,16 @@
         <v>67</v>
       </c>
       <c r="F813" s="4">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G813" s="4">
         <v>10</v>
       </c>
       <c r="H813" s="4">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I813" s="4">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="814" spans="1:9" x14ac:dyDescent="0.25">
@@ -28573,16 +28573,16 @@
         <v>68</v>
       </c>
       <c r="F815" s="4">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="G815" s="4">
         <v>42</v>
       </c>
       <c r="H815" s="4">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I815" s="4">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
     <row r="816" spans="1:9" x14ac:dyDescent="0.25">
@@ -28689,16 +28689,16 @@
         <v>68</v>
       </c>
       <c r="F819" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G819" s="4">
         <v>1</v>
       </c>
       <c r="H819" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I819" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="820" spans="1:9" x14ac:dyDescent="0.25">
@@ -28834,16 +28834,16 @@
         <v>68</v>
       </c>
       <c r="F824" s="4">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="G824" s="4">
         <v>8</v>
       </c>
       <c r="H824" s="4">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="I824" s="4">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="825" spans="1:9" x14ac:dyDescent="0.25">
@@ -28950,16 +28950,16 @@
         <v>69</v>
       </c>
       <c r="F828" s="4">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="G828" s="4">
         <v>35</v>
       </c>
       <c r="H828" s="4">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I828" s="4">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="829" spans="1:9" x14ac:dyDescent="0.25">
@@ -29008,16 +29008,16 @@
         <v>69</v>
       </c>
       <c r="F830" s="4">
+        <v>5</v>
+      </c>
+      <c r="G830" s="4">
+        <v>1</v>
+      </c>
+      <c r="H830" s="4">
+        <v>1</v>
+      </c>
+      <c r="I830" s="4">
         <v>4</v>
-      </c>
-      <c r="G830" s="4">
-        <v>1</v>
-      </c>
-      <c r="H830" s="4">
-        <v>0</v>
-      </c>
-      <c r="I830" s="4">
-        <v>3</v>
       </c>
     </row>
     <row r="831" spans="1:9" x14ac:dyDescent="0.25">
@@ -29182,16 +29182,16 @@
         <v>69</v>
       </c>
       <c r="F836" s="4">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G836" s="4">
         <v>11</v>
       </c>
       <c r="H836" s="4">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I836" s="4">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="837" spans="1:9" x14ac:dyDescent="0.25">
@@ -29240,16 +29240,16 @@
         <v>70</v>
       </c>
       <c r="F838" s="4">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="G838" s="4">
         <v>11</v>
       </c>
       <c r="H838" s="4">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="I838" s="4">
-        <v>47</v>
+        <v>54</v>
       </c>
     </row>
     <row r="839" spans="1:9" x14ac:dyDescent="0.25">
@@ -29269,16 +29269,16 @@
         <v>70</v>
       </c>
       <c r="F839" s="4">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="G839" s="4">
         <v>37</v>
       </c>
       <c r="H839" s="4">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I839" s="4">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="840" spans="1:9" x14ac:dyDescent="0.25">
@@ -29298,16 +29298,16 @@
         <v>70</v>
       </c>
       <c r="F840" s="4">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G840" s="4">
         <v>39</v>
       </c>
       <c r="H840" s="4">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I840" s="4">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="841" spans="1:9" x14ac:dyDescent="0.25">
@@ -29385,16 +29385,16 @@
         <v>71</v>
       </c>
       <c r="F843" s="4">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="G843" s="4">
         <v>23</v>
       </c>
       <c r="H843" s="4">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="I843" s="4">
-        <v>61</v>
+        <v>67</v>
       </c>
     </row>
     <row r="844" spans="1:9" x14ac:dyDescent="0.25">
@@ -29414,16 +29414,16 @@
         <v>71</v>
       </c>
       <c r="F844" s="4">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G844" s="4">
         <v>4</v>
       </c>
       <c r="H844" s="4">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I844" s="4">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="845" spans="1:9" x14ac:dyDescent="0.25">
@@ -29472,16 +29472,16 @@
         <v>71</v>
       </c>
       <c r="F846" s="4">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="G846" s="4">
         <v>48</v>
       </c>
       <c r="H846" s="4">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="I846" s="4">
-        <v>98</v>
+        <v>104</v>
       </c>
     </row>
     <row r="847" spans="1:9" x14ac:dyDescent="0.25">
@@ -29559,16 +29559,16 @@
         <v>72</v>
       </c>
       <c r="F849" s="4">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G849" s="4">
         <v>11</v>
       </c>
       <c r="H849" s="4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I849" s="4">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="850" spans="1:9" x14ac:dyDescent="0.25">
@@ -29588,16 +29588,16 @@
         <v>72</v>
       </c>
       <c r="F850" s="4">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G850" s="4">
         <v>23</v>
       </c>
       <c r="H850" s="4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I850" s="4">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="851" spans="1:9" x14ac:dyDescent="0.25">
@@ -29617,16 +29617,16 @@
         <v>72</v>
       </c>
       <c r="F851" s="4">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G851" s="4">
         <v>11</v>
       </c>
       <c r="H851" s="4">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I851" s="4">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="852" spans="1:9" x14ac:dyDescent="0.25">
@@ -29646,16 +29646,16 @@
         <v>72</v>
       </c>
       <c r="F852" s="4">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G852" s="4">
         <v>21</v>
       </c>
       <c r="H852" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I852" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="853" spans="1:9" x14ac:dyDescent="0.25">
@@ -29675,16 +29675,16 @@
         <v>72</v>
       </c>
       <c r="F853" s="4">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G853" s="4">
         <v>16</v>
       </c>
       <c r="H853" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I853" s="4">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="854" spans="1:9" x14ac:dyDescent="0.25">
@@ -29849,16 +29849,16 @@
         <v>73</v>
       </c>
       <c r="F859" s="4">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="G859" s="4">
         <v>10</v>
       </c>
       <c r="H859" s="4">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="I859" s="4">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="860" spans="1:9" x14ac:dyDescent="0.25">
@@ -29907,16 +29907,16 @@
         <v>73</v>
       </c>
       <c r="F861" s="4">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="G861" s="4">
         <v>15</v>
       </c>
       <c r="H861" s="4">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="I861" s="4">
-        <v>18</v>
+        <v>33</v>
       </c>
     </row>
     <row r="862" spans="1:9" x14ac:dyDescent="0.25">
@@ -29994,16 +29994,16 @@
         <v>74</v>
       </c>
       <c r="F864" s="4">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G864" s="4">
         <v>9</v>
       </c>
       <c r="H864" s="4">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I864" s="4">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="865" spans="1:9" x14ac:dyDescent="0.25">
@@ -30052,16 +30052,16 @@
         <v>74</v>
       </c>
       <c r="F866" s="4">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G866" s="4">
         <v>7</v>
       </c>
       <c r="H866" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I866" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="867" spans="1:9" x14ac:dyDescent="0.25">
@@ -30110,16 +30110,16 @@
         <v>74</v>
       </c>
       <c r="F868" s="4">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="G868" s="4">
         <v>51</v>
       </c>
       <c r="H868" s="4">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I868" s="4">
-        <v>95</v>
+        <v>99</v>
       </c>
     </row>
     <row r="869" spans="1:9" x14ac:dyDescent="0.25">
@@ -30139,16 +30139,16 @@
         <v>74</v>
       </c>
       <c r="F869" s="4">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G869" s="4">
         <v>5</v>
       </c>
       <c r="H869" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I869" s="4">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="870" spans="1:9" x14ac:dyDescent="0.25">
@@ -30400,16 +30400,16 @@
         <v>75</v>
       </c>
       <c r="F878" s="4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G878" s="4">
         <v>3</v>
       </c>
       <c r="H878" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I878" s="4">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="879" spans="1:9" x14ac:dyDescent="0.25">
@@ -30748,16 +30748,16 @@
         <v>77</v>
       </c>
       <c r="F890" s="4">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G890" s="4">
         <v>28</v>
       </c>
       <c r="H890" s="4">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I890" s="4">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="891" spans="1:9" x14ac:dyDescent="0.25">
@@ -30980,16 +30980,16 @@
         <v>77</v>
       </c>
       <c r="F898" s="4">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="G898" s="4">
         <v>13</v>
       </c>
       <c r="H898" s="4">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I898" s="4">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="899" spans="1:9" x14ac:dyDescent="0.25">
@@ -31067,16 +31067,16 @@
         <v>77</v>
       </c>
       <c r="F901" s="4">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G901" s="4">
         <v>14</v>
       </c>
       <c r="H901" s="4">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I901" s="4">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="902" spans="1:9" x14ac:dyDescent="0.25">
@@ -31154,16 +31154,16 @@
         <v>78</v>
       </c>
       <c r="F904" s="4">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G904" s="4">
         <v>7</v>
       </c>
       <c r="H904" s="4">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I904" s="4">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="905" spans="1:9" x14ac:dyDescent="0.25">
@@ -31183,16 +31183,16 @@
         <v>78</v>
       </c>
       <c r="F905" s="4">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G905" s="4">
         <v>12</v>
       </c>
       <c r="H905" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I905" s="4">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="906" spans="1:9" x14ac:dyDescent="0.25">
@@ -31241,16 +31241,16 @@
         <v>78</v>
       </c>
       <c r="F907" s="4">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="G907" s="4">
         <v>12</v>
       </c>
       <c r="H907" s="4">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="I907" s="4">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="908" spans="1:9" x14ac:dyDescent="0.25">
@@ -31473,16 +31473,16 @@
         <v>78</v>
       </c>
       <c r="F915" s="4">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G915" s="4">
         <v>23</v>
       </c>
       <c r="H915" s="4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I915" s="4">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="916" spans="1:9" x14ac:dyDescent="0.25">
@@ -31647,16 +31647,16 @@
         <v>79</v>
       </c>
       <c r="F921" s="4">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="G921" s="4">
         <v>18</v>
       </c>
       <c r="H921" s="4">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I921" s="4">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="922" spans="1:9" x14ac:dyDescent="0.25">
@@ -31705,16 +31705,16 @@
         <v>79</v>
       </c>
       <c r="F923" s="4">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G923" s="4">
         <v>5</v>
       </c>
       <c r="H923" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I923" s="4">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="924" spans="1:9" x14ac:dyDescent="0.25">
@@ -31734,16 +31734,16 @@
         <v>79</v>
       </c>
       <c r="F924" s="4">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G924" s="4">
         <v>4</v>
       </c>
       <c r="H924" s="4">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="I924" s="4">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="925" spans="1:9" x14ac:dyDescent="0.25">
@@ -31792,16 +31792,16 @@
         <v>79</v>
       </c>
       <c r="F926" s="4">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G926" s="4">
         <v>34</v>
       </c>
       <c r="H926" s="4">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I926" s="4">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="927" spans="1:9" x14ac:dyDescent="0.25">
@@ -32024,16 +32024,16 @@
         <v>80</v>
       </c>
       <c r="F934" s="4">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G934" s="4">
         <v>18</v>
       </c>
       <c r="H934" s="4">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I934" s="4">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="935" spans="1:9" x14ac:dyDescent="0.25">
@@ -32082,16 +32082,16 @@
         <v>80</v>
       </c>
       <c r="F936" s="4">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G936" s="4">
         <v>10</v>
       </c>
       <c r="H936" s="4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I936" s="4">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="937" spans="1:9" x14ac:dyDescent="0.25">
@@ -32198,16 +32198,16 @@
         <v>80</v>
       </c>
       <c r="F940" s="4">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G940" s="4">
         <v>19</v>
       </c>
       <c r="H940" s="4">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I940" s="4">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="941" spans="1:9" x14ac:dyDescent="0.25">
@@ -32256,16 +32256,16 @@
         <v>80</v>
       </c>
       <c r="F942" s="4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G942" s="4">
         <v>4</v>
       </c>
       <c r="H942" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I942" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="943" spans="1:9" x14ac:dyDescent="0.25">
@@ -32546,16 +32546,16 @@
         <v>81</v>
       </c>
       <c r="F952" s="4">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G952" s="4">
         <v>37</v>
       </c>
       <c r="H952" s="4">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I952" s="4">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="953" spans="1:9" x14ac:dyDescent="0.25">
@@ -32604,16 +32604,16 @@
         <v>81</v>
       </c>
       <c r="F954" s="4">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="G954" s="4">
         <v>44</v>
       </c>
       <c r="H954" s="4">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I954" s="4">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="955" spans="1:9" x14ac:dyDescent="0.25">
@@ -32662,16 +32662,16 @@
         <v>81</v>
       </c>
       <c r="F956" s="4">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G956" s="4">
         <v>10</v>
       </c>
       <c r="H956" s="4">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I956" s="4">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="957" spans="1:9" x14ac:dyDescent="0.25">
@@ -32778,16 +32778,16 @@
         <v>82</v>
       </c>
       <c r="F960" s="4">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G960" s="4">
         <v>15</v>
       </c>
       <c r="H960" s="4">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I960" s="4">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="961" spans="1:9" x14ac:dyDescent="0.25">
@@ -32952,16 +32952,16 @@
         <v>82</v>
       </c>
       <c r="F966" s="4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G966" s="4">
         <v>2</v>
       </c>
       <c r="H966" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I966" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="967" spans="1:9" x14ac:dyDescent="0.25">
@@ -33010,16 +33010,16 @@
         <v>82</v>
       </c>
       <c r="F968" s="4">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G968" s="4">
         <v>13</v>
       </c>
       <c r="H968" s="4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I968" s="4">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="969" spans="1:9" x14ac:dyDescent="0.25">
@@ -33126,16 +33126,16 @@
         <v>82</v>
       </c>
       <c r="F972" s="4">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G972" s="4">
         <v>11</v>
       </c>
       <c r="H972" s="4">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I972" s="4">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="973" spans="1:9" x14ac:dyDescent="0.25">
@@ -33271,16 +33271,16 @@
         <v>82</v>
       </c>
       <c r="F977" s="4">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G977" s="4">
         <v>9</v>
       </c>
       <c r="H977" s="4">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I977" s="4">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="978" spans="1:9" x14ac:dyDescent="0.25">
@@ -33416,16 +33416,16 @@
         <v>83</v>
       </c>
       <c r="F982" s="4">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G982" s="4">
         <v>9</v>
       </c>
       <c r="H982" s="4">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I982" s="4">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="983" spans="1:9" x14ac:dyDescent="0.25">
@@ -33590,16 +33590,16 @@
         <v>83</v>
       </c>
       <c r="F988" s="4">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G988" s="4">
         <v>8</v>
       </c>
       <c r="H988" s="4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I988" s="4">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="989" spans="1:9" x14ac:dyDescent="0.25">
@@ -33619,16 +33619,16 @@
         <v>83</v>
       </c>
       <c r="F989" s="4">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G989" s="4">
         <v>21</v>
       </c>
       <c r="H989" s="4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I989" s="4">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="990" spans="1:9" x14ac:dyDescent="0.25">
@@ -33735,16 +33735,16 @@
         <v>84</v>
       </c>
       <c r="F993" s="4">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G993" s="4">
         <v>4</v>
       </c>
       <c r="H993" s="4">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I993" s="4">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="994" spans="1:9" x14ac:dyDescent="0.25">
@@ -33764,16 +33764,16 @@
         <v>84</v>
       </c>
       <c r="F994" s="4">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G994" s="4">
         <v>27</v>
       </c>
       <c r="H994" s="4">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I994" s="4">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="995" spans="1:9" x14ac:dyDescent="0.25">
@@ -33793,16 +33793,16 @@
         <v>84</v>
       </c>
       <c r="F995" s="4">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G995" s="4">
         <v>22</v>
       </c>
       <c r="H995" s="4">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="I995" s="4">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="996" spans="1:9" x14ac:dyDescent="0.25">
@@ -33822,16 +33822,16 @@
         <v>84</v>
       </c>
       <c r="F996" s="4">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G996" s="4">
         <v>8</v>
       </c>
       <c r="H996" s="4">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I996" s="4">
-        <v>23</v>
+        <v>26</v>
       </c>
     </row>
     <row r="997" spans="1:9" x14ac:dyDescent="0.25">
@@ -34025,16 +34025,16 @@
         <v>84</v>
       </c>
       <c r="F1003" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1003" s="4">
         <v>0</v>
       </c>
       <c r="H1003" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I1003" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1004" spans="1:9" x14ac:dyDescent="0.25">
@@ -34199,16 +34199,16 @@
         <v>85</v>
       </c>
       <c r="F1009" s="4">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G1009" s="4">
         <v>5</v>
       </c>
       <c r="H1009" s="4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I1009" s="4">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1010" spans="1:9" x14ac:dyDescent="0.25">
@@ -34257,16 +34257,16 @@
         <v>85</v>
       </c>
       <c r="F1011" s="4">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G1011" s="4">
         <v>15</v>
       </c>
       <c r="H1011" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I1011" s="4">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1012" spans="1:9" x14ac:dyDescent="0.25">
@@ -34373,16 +34373,16 @@
         <v>85</v>
       </c>
       <c r="F1015" s="4">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G1015" s="4">
         <v>9</v>
       </c>
       <c r="H1015" s="4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I1015" s="4">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1016" spans="1:9" x14ac:dyDescent="0.25">
@@ -34431,16 +34431,16 @@
         <v>85</v>
       </c>
       <c r="F1017" s="4">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G1017" s="4">
         <v>7</v>
       </c>
       <c r="H1017" s="4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I1017" s="4">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1018" spans="1:9" x14ac:dyDescent="0.25">
@@ -34576,16 +34576,16 @@
         <v>85</v>
       </c>
       <c r="F1022" s="4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G1022" s="4">
         <v>3</v>
       </c>
       <c r="H1022" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I1022" s="4">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1023" spans="1:9" x14ac:dyDescent="0.25">
@@ -34808,16 +34808,16 @@
         <v>86</v>
       </c>
       <c r="F1030" s="4">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="G1030" s="4">
         <v>23</v>
       </c>
       <c r="H1030" s="4">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="I1030" s="4">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="1031" spans="1:9" x14ac:dyDescent="0.25">
@@ -34924,16 +34924,16 @@
         <v>86</v>
       </c>
       <c r="F1034" s="4">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G1034" s="4">
         <v>14</v>
       </c>
       <c r="H1034" s="4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I1034" s="4">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="1035" spans="1:9" x14ac:dyDescent="0.25">
@@ -35040,16 +35040,16 @@
         <v>86</v>
       </c>
       <c r="F1038" s="4">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G1038" s="4">
         <v>9</v>
       </c>
       <c r="H1038" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I1038" s="4">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1039" spans="1:9" x14ac:dyDescent="0.25">
@@ -35214,16 +35214,16 @@
         <v>87</v>
       </c>
       <c r="F1044" s="4">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G1044" s="4">
         <v>2</v>
       </c>
       <c r="H1044" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I1044" s="4">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1045" spans="1:9" x14ac:dyDescent="0.25">
@@ -35446,16 +35446,16 @@
         <v>87</v>
       </c>
       <c r="F1052" s="4">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G1052" s="4">
         <v>13</v>
       </c>
       <c r="H1052" s="4">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I1052" s="4">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="1053" spans="1:9" x14ac:dyDescent="0.25">
@@ -35475,16 +35475,16 @@
         <v>87</v>
       </c>
       <c r="F1053" s="4">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="G1053" s="4">
         <v>62</v>
       </c>
       <c r="H1053" s="4">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I1053" s="4">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="1054" spans="1:9" x14ac:dyDescent="0.25">
@@ -35562,16 +35562,16 @@
         <v>88</v>
       </c>
       <c r="F1056" s="4">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G1056" s="4">
         <v>45</v>
       </c>
       <c r="H1056" s="4">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I1056" s="4">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="1057" spans="1:9" x14ac:dyDescent="0.25">
@@ -35620,16 +35620,16 @@
         <v>88</v>
       </c>
       <c r="F1058" s="4">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G1058" s="4">
         <v>4</v>
       </c>
       <c r="H1058" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I1058" s="4">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1059" spans="1:9" x14ac:dyDescent="0.25">
@@ -35678,16 +35678,16 @@
         <v>88</v>
       </c>
       <c r="F1060" s="4">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="G1060" s="4">
         <v>11</v>
       </c>
       <c r="H1060" s="4">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I1060" s="4">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1061" spans="1:9" x14ac:dyDescent="0.25">
@@ -35736,16 +35736,16 @@
         <v>88</v>
       </c>
       <c r="F1062" s="4">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G1062" s="4">
         <v>30</v>
       </c>
       <c r="H1062" s="4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I1062" s="4">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="1063" spans="1:9" x14ac:dyDescent="0.25">
@@ -35852,16 +35852,16 @@
         <v>89</v>
       </c>
       <c r="F1066" s="4">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G1066" s="4">
         <v>5</v>
       </c>
       <c r="H1066" s="4">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I1066" s="4">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1067" spans="1:9" x14ac:dyDescent="0.25">
@@ -35968,16 +35968,16 @@
         <v>89</v>
       </c>
       <c r="F1070" s="4">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G1070" s="4">
         <v>4</v>
       </c>
       <c r="H1070" s="4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I1070" s="4">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="1071" spans="1:9" x14ac:dyDescent="0.25">
@@ -36055,16 +36055,16 @@
         <v>89</v>
       </c>
       <c r="F1073" s="4">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="G1073" s="4">
         <v>73</v>
       </c>
       <c r="H1073" s="4">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I1073" s="4">
-        <v>110</v>
+        <v>114</v>
       </c>
     </row>
     <row r="1074" spans="1:9" x14ac:dyDescent="0.25">
@@ -36200,16 +36200,16 @@
         <v>90</v>
       </c>
       <c r="F1078" s="4">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="G1078" s="4">
         <v>56</v>
       </c>
       <c r="H1078" s="4">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I1078" s="4">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="1079" spans="1:9" x14ac:dyDescent="0.25">
@@ -36229,16 +36229,16 @@
         <v>90</v>
       </c>
       <c r="F1079" s="4">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G1079" s="4">
         <v>16</v>
       </c>
       <c r="H1079" s="4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I1079" s="4">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="1080" spans="1:9" x14ac:dyDescent="0.25">
@@ -36287,16 +36287,16 @@
         <v>90</v>
       </c>
       <c r="F1081" s="4">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G1081" s="4">
         <v>18</v>
       </c>
       <c r="H1081" s="4">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I1081" s="4">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="1082" spans="1:9" x14ac:dyDescent="0.25">
@@ -36345,16 +36345,16 @@
         <v>91</v>
       </c>
       <c r="F1083" s="4">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G1083" s="4">
         <v>6</v>
       </c>
       <c r="H1083" s="4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I1083" s="4">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1084" spans="1:9" x14ac:dyDescent="0.25">
@@ -36461,16 +36461,16 @@
         <v>91</v>
       </c>
       <c r="F1087" s="4">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="G1087" s="4">
         <v>15</v>
       </c>
       <c r="H1087" s="4">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="I1087" s="4">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1088" spans="1:9" x14ac:dyDescent="0.25">
@@ -36577,16 +36577,16 @@
         <v>91</v>
       </c>
       <c r="F1091" s="4">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G1091" s="4">
         <v>38</v>
       </c>
       <c r="H1091" s="4">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I1091" s="4">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="1092" spans="1:9" x14ac:dyDescent="0.25">
@@ -37273,16 +37273,16 @@
         <v>93</v>
       </c>
       <c r="F1115" s="4">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G1115" s="4">
         <v>22</v>
       </c>
       <c r="H1115" s="4">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I1115" s="4">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="1116" spans="1:9" x14ac:dyDescent="0.25">
@@ -37476,16 +37476,16 @@
         <v>93</v>
       </c>
       <c r="F1122" s="4">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G1122" s="4">
         <v>3</v>
       </c>
       <c r="H1122" s="4">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I1122" s="4">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1123" spans="1:9" x14ac:dyDescent="0.25">
@@ -37505,16 +37505,16 @@
         <v>93</v>
       </c>
       <c r="F1123" s="4">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="G1123" s="4">
         <v>16</v>
       </c>
       <c r="H1123" s="4">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="I1123" s="4">
-        <v>29</v>
+        <v>34</v>
       </c>
     </row>
     <row r="1124" spans="1:9" x14ac:dyDescent="0.25">
@@ -37650,16 +37650,16 @@
         <v>94</v>
       </c>
       <c r="F1128" s="4">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="G1128" s="4">
         <v>36</v>
       </c>
       <c r="H1128" s="4">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I1128" s="4">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="1129" spans="1:9" x14ac:dyDescent="0.25">
@@ -37679,16 +37679,16 @@
         <v>94</v>
       </c>
       <c r="F1129" s="4">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G1129" s="4">
         <v>22</v>
       </c>
       <c r="H1129" s="4">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I1129" s="4">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="1130" spans="1:9" x14ac:dyDescent="0.25">
@@ -37766,16 +37766,16 @@
         <v>94</v>
       </c>
       <c r="F1132" s="4">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G1132" s="4">
         <v>10</v>
       </c>
       <c r="H1132" s="4">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I1132" s="4">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="1133" spans="1:9" x14ac:dyDescent="0.25">
@@ -38085,16 +38085,16 @@
         <v>95</v>
       </c>
       <c r="F1143" s="4">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G1143" s="4">
         <v>10</v>
       </c>
       <c r="H1143" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I1143" s="4">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="1144" spans="1:9" x14ac:dyDescent="0.25">
@@ -38172,16 +38172,16 @@
         <v>95</v>
       </c>
       <c r="F1146" s="4">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G1146" s="4">
         <v>8</v>
       </c>
       <c r="H1146" s="4">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I1146" s="4">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1147" spans="1:9" x14ac:dyDescent="0.25">
@@ -38433,16 +38433,16 @@
         <v>96</v>
       </c>
       <c r="F1155" s="4">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G1155" s="4">
         <v>18</v>
       </c>
       <c r="H1155" s="4">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I1155" s="4">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="1156" spans="1:9" x14ac:dyDescent="0.25">
@@ -38694,16 +38694,16 @@
         <v>96</v>
       </c>
       <c r="F1164" s="4">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G1164" s="4">
         <v>14</v>
       </c>
       <c r="H1164" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I1164" s="4">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="1165" spans="1:9" x14ac:dyDescent="0.25">
@@ -38781,16 +38781,16 @@
         <v>97</v>
       </c>
       <c r="F1167" s="4">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G1167" s="4">
         <v>7</v>
       </c>
       <c r="H1167" s="4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I1167" s="4">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="1168" spans="1:9" x14ac:dyDescent="0.25">
@@ -38897,16 +38897,16 @@
         <v>97</v>
       </c>
       <c r="F1171" s="4">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="G1171" s="4">
         <v>47</v>
       </c>
       <c r="H1171" s="4">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I1171" s="4">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="1172" spans="1:9" x14ac:dyDescent="0.25">
@@ -39042,16 +39042,16 @@
         <v>97</v>
       </c>
       <c r="F1176" s="4">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G1176" s="4">
         <v>6</v>
       </c>
       <c r="H1176" s="4">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="I1176" s="4">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="1177" spans="1:9" x14ac:dyDescent="0.25">
@@ -39419,16 +39419,16 @@
         <v>98</v>
       </c>
       <c r="F1189" s="4">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G1189" s="4">
         <v>7</v>
       </c>
       <c r="H1189" s="4">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I1189" s="4">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="1190" spans="1:9" x14ac:dyDescent="0.25">
@@ -39506,16 +39506,16 @@
         <v>99</v>
       </c>
       <c r="F1192" s="4">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G1192" s="4">
         <v>27</v>
       </c>
       <c r="H1192" s="4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I1192" s="4">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="1193" spans="1:9" x14ac:dyDescent="0.25">
@@ -39564,16 +39564,16 @@
         <v>99</v>
       </c>
       <c r="F1194" s="4">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G1194" s="4">
         <v>8</v>
       </c>
       <c r="H1194" s="4">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I1194" s="4">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="1195" spans="1:9" x14ac:dyDescent="0.25">
@@ -39651,16 +39651,16 @@
         <v>99</v>
       </c>
       <c r="F1197" s="4">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G1197" s="4">
         <v>8</v>
       </c>
       <c r="H1197" s="4">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I1197" s="4">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="1198" spans="1:9" x14ac:dyDescent="0.25">
@@ -39738,16 +39738,16 @@
         <v>99</v>
       </c>
       <c r="F1200" s="4">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G1200" s="4">
         <v>5</v>
       </c>
       <c r="H1200" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I1200" s="4">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="1201" spans="1:9" x14ac:dyDescent="0.25">
@@ -39883,16 +39883,16 @@
         <v>100</v>
       </c>
       <c r="F1205" s="4">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="G1205" s="4">
         <v>27</v>
       </c>
       <c r="H1205" s="4">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I1205" s="4">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="1206" spans="1:9" x14ac:dyDescent="0.25">
@@ -39941,16 +39941,16 @@
         <v>100</v>
       </c>
       <c r="F1207" s="4">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G1207" s="4">
         <v>6</v>
       </c>
       <c r="H1207" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I1207" s="4">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="1208" spans="1:9" x14ac:dyDescent="0.25">
@@ -40028,16 +40028,16 @@
         <v>100</v>
       </c>
       <c r="F1210" s="4">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G1210" s="4">
         <v>4</v>
       </c>
       <c r="H1210" s="4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I1210" s="4">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1211" spans="1:9" x14ac:dyDescent="0.25">
@@ -40086,16 +40086,16 @@
         <v>101</v>
       </c>
       <c r="F1212" s="4">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G1212" s="4">
         <v>30</v>
       </c>
       <c r="H1212" s="4">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I1212" s="4">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="1213" spans="1:9" x14ac:dyDescent="0.25">
@@ -40115,16 +40115,16 @@
         <v>101</v>
       </c>
       <c r="F1213" s="4">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G1213" s="4">
         <v>0</v>
       </c>
       <c r="H1213" s="4">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I1213" s="4">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="1214" spans="1:9" x14ac:dyDescent="0.25">
@@ -40318,16 +40318,16 @@
         <v>102</v>
       </c>
       <c r="F1220" s="4">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="G1220" s="4">
         <v>14</v>
       </c>
       <c r="H1220" s="4">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="I1220" s="4">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="1221" spans="1:9" x14ac:dyDescent="0.25">
@@ -40376,16 +40376,16 @@
         <v>102</v>
       </c>
       <c r="F1222" s="4">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G1222" s="4">
         <v>21</v>
       </c>
       <c r="H1222" s="4">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I1222" s="4">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="1223" spans="1:9" x14ac:dyDescent="0.25">
@@ -40521,16 +40521,16 @@
         <v>103</v>
       </c>
       <c r="F1227" s="4">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="G1227" s="4">
         <v>65</v>
       </c>
       <c r="H1227" s="4">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I1227" s="4">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="1228" spans="1:9" x14ac:dyDescent="0.25">
@@ -40608,16 +40608,16 @@
         <v>104</v>
       </c>
       <c r="F1230" s="4">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G1230" s="4">
         <v>31</v>
       </c>
       <c r="H1230" s="4">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I1230" s="4">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="1231" spans="1:9" x14ac:dyDescent="0.25">
@@ -40811,16 +40811,16 @@
         <v>105</v>
       </c>
       <c r="F1237" s="4">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G1237" s="4">
         <v>34</v>
       </c>
       <c r="H1237" s="4">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I1237" s="4">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="1238" spans="1:9" x14ac:dyDescent="0.25">
@@ -41130,16 +41130,16 @@
         <v>106</v>
       </c>
       <c r="F1248" s="4">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G1248" s="4">
         <v>6</v>
       </c>
       <c r="H1248" s="4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I1248" s="4">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1249" spans="1:9" x14ac:dyDescent="0.25">
@@ -41333,16 +41333,16 @@
         <v>106</v>
       </c>
       <c r="F1255" s="4">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G1255" s="4">
         <v>5</v>
       </c>
       <c r="H1255" s="4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I1255" s="4">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="1256" spans="1:9" x14ac:dyDescent="0.25">
@@ -41768,16 +41768,16 @@
         <v>107</v>
       </c>
       <c r="F1270" s="4">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G1270" s="4">
         <v>10</v>
       </c>
       <c r="H1270" s="4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I1270" s="4">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="1271" spans="1:9" x14ac:dyDescent="0.25">
@@ -41913,16 +41913,16 @@
         <v>107</v>
       </c>
       <c r="F1275" s="4">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G1275" s="4">
         <v>3</v>
       </c>
       <c r="H1275" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I1275" s="4">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1276" spans="1:9" x14ac:dyDescent="0.25">
@@ -41942,16 +41942,16 @@
         <v>107</v>
       </c>
       <c r="F1276" s="4">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G1276" s="4">
         <v>8</v>
       </c>
       <c r="H1276" s="4">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I1276" s="4">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="1277" spans="1:9" x14ac:dyDescent="0.25">
@@ -42000,16 +42000,16 @@
         <v>107</v>
       </c>
       <c r="F1278" s="4">
+        <v>9</v>
+      </c>
+      <c r="G1278" s="4">
+        <v>1</v>
+      </c>
+      <c r="H1278" s="4">
+        <v>2</v>
+      </c>
+      <c r="I1278" s="4">
         <v>8</v>
-      </c>
-      <c r="G1278" s="4">
-        <v>1</v>
-      </c>
-      <c r="H1278" s="4">
-        <v>1</v>
-      </c>
-      <c r="I1278" s="4">
-        <v>7</v>
       </c>
     </row>
     <row r="1279" spans="1:9" x14ac:dyDescent="0.25">
@@ -42493,16 +42493,16 @@
         <v>109</v>
       </c>
       <c r="F1295" s="4">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G1295" s="4">
         <v>17</v>
       </c>
       <c r="H1295" s="4">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I1295" s="4">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="1296" spans="1:9" x14ac:dyDescent="0.25">
@@ -43015,16 +43015,16 @@
         <v>110</v>
       </c>
       <c r="F1313" s="4">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G1313" s="4">
         <v>13</v>
       </c>
       <c r="H1313" s="4">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I1313" s="4">
-        <v>23</v>
+        <v>26</v>
       </c>
     </row>
     <row r="1314" spans="1:9" x14ac:dyDescent="0.25">
@@ -43131,16 +43131,16 @@
         <v>111</v>
       </c>
       <c r="F1317" s="4">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G1317" s="4">
         <v>12</v>
       </c>
       <c r="H1317" s="4">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I1317" s="4">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1318" spans="1:9" x14ac:dyDescent="0.25">
@@ -43305,16 +43305,16 @@
         <v>112</v>
       </c>
       <c r="F1323" s="4">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G1323" s="4">
         <v>8</v>
       </c>
       <c r="H1323" s="4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I1323" s="4">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="1324" spans="1:9" x14ac:dyDescent="0.25">
@@ -43566,16 +43566,16 @@
         <v>113</v>
       </c>
       <c r="F1332" s="4">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="G1332" s="4">
         <v>10</v>
       </c>
       <c r="H1332" s="4">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="I1332" s="4">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="1333" spans="1:9" x14ac:dyDescent="0.25">
@@ -43943,16 +43943,16 @@
         <v>115</v>
       </c>
       <c r="F1345" s="4">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G1345" s="4">
         <v>12</v>
       </c>
       <c r="H1345" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1345" s="4">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="1346" spans="1:9" x14ac:dyDescent="0.25">
@@ -44001,16 +44001,16 @@
         <v>115</v>
       </c>
       <c r="F1347" s="4">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G1347" s="4">
         <v>13</v>
       </c>
       <c r="H1347" s="4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I1347" s="4">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="1348" spans="1:9" x14ac:dyDescent="0.25">
@@ -44755,16 +44755,16 @@
         <v>117</v>
       </c>
       <c r="F1373" s="4">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G1373" s="4">
         <v>14</v>
       </c>
       <c r="H1373" s="4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I1373" s="4">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="1374" spans="1:9" x14ac:dyDescent="0.25">
@@ -45277,16 +45277,16 @@
         <v>118</v>
       </c>
       <c r="F1391" s="4">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G1391" s="4">
         <v>8</v>
       </c>
       <c r="H1391" s="4">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="I1391" s="4">
-        <v>27</v>
+        <v>32</v>
       </c>
     </row>
     <row r="1392" spans="1:9" x14ac:dyDescent="0.25">
@@ -45451,16 +45451,16 @@
         <v>119</v>
       </c>
       <c r="F1397" s="4">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G1397" s="4">
         <v>17</v>
       </c>
       <c r="H1397" s="4">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I1397" s="4">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1398" spans="1:9" x14ac:dyDescent="0.25">
@@ -45973,16 +45973,16 @@
         <v>120</v>
       </c>
       <c r="F1415" s="4">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G1415" s="4">
         <v>3</v>
       </c>
       <c r="H1415" s="4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I1415" s="4">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="1416" spans="1:9" x14ac:dyDescent="0.25">
@@ -46060,16 +46060,16 @@
         <v>121</v>
       </c>
       <c r="F1418" s="4">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G1418" s="4">
         <v>13</v>
       </c>
       <c r="H1418" s="4">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I1418" s="4">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1419" spans="1:9" x14ac:dyDescent="0.25">
@@ -46147,16 +46147,16 @@
         <v>121</v>
       </c>
       <c r="F1421" s="4">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G1421" s="4">
         <v>6</v>
       </c>
       <c r="H1421" s="4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I1421" s="4">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1422" spans="1:9" x14ac:dyDescent="0.25">
@@ -46611,16 +46611,16 @@
         <v>122</v>
       </c>
       <c r="F1437" s="4">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G1437" s="4">
         <v>7</v>
       </c>
       <c r="H1437" s="4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I1437" s="4">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="1438" spans="1:9" x14ac:dyDescent="0.25">
@@ -48119,16 +48119,16 @@
         <v>126</v>
       </c>
       <c r="F1489" s="4">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G1489" s="4">
         <v>6</v>
       </c>
       <c r="H1489" s="4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I1489" s="4">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="1490" spans="1:9" x14ac:dyDescent="0.25">
@@ -48496,16 +48496,16 @@
         <v>127</v>
       </c>
       <c r="F1502" s="4">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G1502" s="4">
         <v>9</v>
       </c>
       <c r="H1502" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I1502" s="4">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="1503" spans="1:9" x14ac:dyDescent="0.25">
@@ -48583,16 +48583,16 @@
         <v>128</v>
       </c>
       <c r="F1505" s="4">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G1505" s="4">
         <v>3</v>
       </c>
       <c r="H1505" s="4">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I1505" s="4">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="1506" spans="1:9" x14ac:dyDescent="0.25">
@@ -48931,16 +48931,16 @@
         <v>129</v>
       </c>
       <c r="F1517" s="4">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G1517" s="4">
         <v>17</v>
       </c>
       <c r="H1517" s="4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I1517" s="4">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="1518" spans="1:9" x14ac:dyDescent="0.25">
@@ -49018,16 +49018,16 @@
         <v>129</v>
       </c>
       <c r="F1520" s="4">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G1520" s="4">
         <v>8</v>
       </c>
       <c r="H1520" s="4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I1520" s="4">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="1521" spans="1:9" x14ac:dyDescent="0.25">
@@ -50265,16 +50265,16 @@
         <v>133</v>
       </c>
       <c r="F1563" s="4">
+        <v>9</v>
+      </c>
+      <c r="G1563" s="4">
+        <v>2</v>
+      </c>
+      <c r="H1563" s="4">
+        <v>3</v>
+      </c>
+      <c r="I1563" s="4">
         <v>7</v>
-      </c>
-      <c r="G1563" s="4">
-        <v>2</v>
-      </c>
-      <c r="H1563" s="4">
-        <v>1</v>
-      </c>
-      <c r="I1563" s="4">
-        <v>5</v>
       </c>
     </row>
     <row r="1564" spans="1:9" x14ac:dyDescent="0.25">
@@ -50352,16 +50352,16 @@
         <v>134</v>
       </c>
       <c r="F1566" s="4">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G1566" s="4">
         <v>15</v>
       </c>
       <c r="H1566" s="4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I1566" s="4">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="1567" spans="1:9" x14ac:dyDescent="0.25">
@@ -50903,16 +50903,16 @@
         <v>135</v>
       </c>
       <c r="F1585" s="4">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G1585" s="4">
         <v>16</v>
       </c>
       <c r="H1585" s="4">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I1585" s="4">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="1586" spans="1:9" x14ac:dyDescent="0.25">
@@ -51744,16 +51744,16 @@
         <v>137</v>
       </c>
       <c r="F1614" s="4">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G1614" s="4">
         <v>9</v>
       </c>
       <c r="H1614" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I1614" s="4">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1615" spans="1:9" x14ac:dyDescent="0.25">
@@ -52005,16 +52005,16 @@
         <v>138</v>
       </c>
       <c r="F1623" s="4">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G1623" s="4">
         <v>7</v>
       </c>
       <c r="H1623" s="4">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I1623" s="4">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="1624" spans="1:9" x14ac:dyDescent="0.25">
@@ -52295,16 +52295,16 @@
         <v>139</v>
       </c>
       <c r="F1633" s="4">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G1633" s="4">
         <v>33</v>
       </c>
       <c r="H1633" s="4">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I1633" s="4">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="1634" spans="1:9" x14ac:dyDescent="0.25">
@@ -52382,16 +52382,16 @@
         <v>139</v>
       </c>
       <c r="F1636" s="4">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G1636" s="4">
         <v>9</v>
       </c>
       <c r="H1636" s="4">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I1636" s="4">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="1637" spans="1:9" x14ac:dyDescent="0.25">
@@ -52788,16 +52788,16 @@
         <v>141</v>
       </c>
       <c r="F1650" s="4">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G1650" s="4">
         <v>33</v>
       </c>
       <c r="H1650" s="4">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I1650" s="4">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="1651" spans="1:9" x14ac:dyDescent="0.25">
@@ -52817,16 +52817,16 @@
         <v>141</v>
       </c>
       <c r="F1651" s="4">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G1651" s="4">
         <v>3</v>
       </c>
       <c r="H1651" s="4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I1651" s="4">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="1652" spans="1:9" x14ac:dyDescent="0.25">
@@ -54383,16 +54383,16 @@
         <v>146</v>
       </c>
       <c r="F1705" s="4">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="G1705" s="4">
         <v>48</v>
       </c>
       <c r="H1705" s="4">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I1705" s="4">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="1706" spans="1:9" x14ac:dyDescent="0.25">
@@ -54412,16 +54412,16 @@
         <v>146</v>
       </c>
       <c r="F1706" s="4">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G1706" s="4">
         <v>32</v>
       </c>
       <c r="H1706" s="4">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I1706" s="4">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="1707" spans="1:9" x14ac:dyDescent="0.25">
@@ -54673,16 +54673,16 @@
         <v>147</v>
       </c>
       <c r="F1715" s="4">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G1715" s="4">
         <v>13</v>
       </c>
       <c r="H1715" s="4">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I1715" s="4">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="1716" spans="1:9" x14ac:dyDescent="0.25">
@@ -54789,16 +54789,16 @@
         <v>148</v>
       </c>
       <c r="F1719" s="4">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G1719" s="4">
         <v>4</v>
       </c>
       <c r="H1719" s="4">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I1719" s="4">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="1720" spans="1:9" x14ac:dyDescent="0.25">
@@ -54934,16 +54934,16 @@
         <v>149</v>
       </c>
       <c r="F1724" s="4">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G1724" s="4">
         <v>26</v>
       </c>
       <c r="H1724" s="4">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I1724" s="4">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="1725" spans="1:9" x14ac:dyDescent="0.25">
@@ -54992,16 +54992,16 @@
         <v>150</v>
       </c>
       <c r="F1726" s="4">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G1726" s="4">
         <v>11</v>
       </c>
       <c r="H1726" s="4">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I1726" s="4">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="1727" spans="1:9" x14ac:dyDescent="0.25">
@@ -55050,16 +55050,16 @@
         <v>150</v>
       </c>
       <c r="F1728" s="4">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G1728" s="4">
         <v>21</v>
       </c>
       <c r="H1728" s="4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I1728" s="4">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="1729" spans="1:9" x14ac:dyDescent="0.25">
@@ -55195,16 +55195,16 @@
         <v>151</v>
       </c>
       <c r="F1733" s="4">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="G1733" s="4">
         <v>60</v>
       </c>
       <c r="H1733" s="4">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I1733" s="4">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="1734" spans="1:9" x14ac:dyDescent="0.25">
@@ -55224,16 +55224,16 @@
         <v>151</v>
       </c>
       <c r="F1734" s="4">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G1734" s="4">
         <v>22</v>
       </c>
       <c r="H1734" s="4">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I1734" s="4">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="1735" spans="1:9" x14ac:dyDescent="0.25">
@@ -55253,16 +55253,16 @@
         <v>151</v>
       </c>
       <c r="F1735" s="4">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G1735" s="4">
         <v>11</v>
       </c>
       <c r="H1735" s="4">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I1735" s="4">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="1736" spans="1:9" x14ac:dyDescent="0.25">

--- a/0. capaian omnibus 2026.xlsx
+++ b/0. capaian omnibus 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\0. codex\0. Omnibus\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76D6C95E-4E9C-4AA1-8637-5B0A1FB6603A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AF45B14-85E2-49CD-87B5-B7E47DB3681F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-109" yWindow="-109" windowWidth="26301" windowHeight="15800" xr2:uid="{ABC9ECFA-347A-408B-B0D0-6F1CCFF80879}"/>
   </bookViews>
@@ -5112,16 +5112,16 @@
         <v>1</v>
       </c>
       <c r="F6" s="4">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G6" s="4">
         <v>22</v>
       </c>
       <c r="H6" s="4">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I6" s="4">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
@@ -5228,16 +5228,16 @@
         <v>1</v>
       </c>
       <c r="F10" s="4">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G10" s="4">
         <v>8</v>
       </c>
       <c r="H10" s="4">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I10" s="4">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
@@ -5373,16 +5373,16 @@
         <v>2</v>
       </c>
       <c r="F15" s="4">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="G15" s="4">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H15" s="4">
         <v>23</v>
       </c>
       <c r="I15" s="4">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
@@ -5518,7 +5518,7 @@
         <v>2</v>
       </c>
       <c r="F20" s="4">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="G20" s="4">
         <v>31</v>
@@ -5527,7 +5527,7 @@
         <v>18</v>
       </c>
       <c r="I20" s="4">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
@@ -5872,7 +5872,7 @@
         <v>9</v>
       </c>
       <c r="H32" s="4">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I32" s="4">
         <v>33</v>
@@ -6278,7 +6278,7 @@
         <v>2</v>
       </c>
       <c r="H46" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I46" s="4">
         <v>21</v>
@@ -6336,7 +6336,7 @@
         <v>33</v>
       </c>
       <c r="H48" s="4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I48" s="4">
         <v>42</v>
@@ -6481,7 +6481,7 @@
         <v>32</v>
       </c>
       <c r="H53" s="4">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I53" s="4">
         <v>84</v>
@@ -6771,7 +6771,7 @@
         <v>31</v>
       </c>
       <c r="H63" s="4">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I63" s="4">
         <v>77</v>
@@ -6887,7 +6887,7 @@
         <v>8</v>
       </c>
       <c r="H67" s="4">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="I67" s="4">
         <v>46</v>
@@ -6939,16 +6939,16 @@
         <v>6</v>
       </c>
       <c r="F69" s="4">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G69" s="4">
         <v>39</v>
       </c>
       <c r="H69" s="4">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I69" s="4">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.25">
@@ -7206,7 +7206,7 @@
         <v>0</v>
       </c>
       <c r="H78" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I78" s="4">
         <v>9</v>
@@ -7496,7 +7496,7 @@
         <v>11</v>
       </c>
       <c r="H88" s="4">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I88" s="4">
         <v>29</v>
@@ -7728,7 +7728,7 @@
         <v>6</v>
       </c>
       <c r="H96" s="4">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I96" s="4">
         <v>32</v>
@@ -8134,7 +8134,7 @@
         <v>6</v>
       </c>
       <c r="H110" s="4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I110" s="4">
         <v>33</v>
@@ -8250,7 +8250,7 @@
         <v>14</v>
       </c>
       <c r="H114" s="4">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I114" s="4">
         <v>42</v>
@@ -8337,7 +8337,7 @@
         <v>24</v>
       </c>
       <c r="H117" s="4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I117" s="4">
         <v>22</v>
@@ -8366,7 +8366,7 @@
         <v>5</v>
       </c>
       <c r="H118" s="4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I118" s="4">
         <v>38</v>
@@ -8598,7 +8598,7 @@
         <v>8</v>
       </c>
       <c r="H126" s="4">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I126" s="4">
         <v>36</v>
@@ -8679,7 +8679,7 @@
         <v>11</v>
       </c>
       <c r="F129" s="4">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G129" s="4">
         <v>14</v>
@@ -8688,7 +8688,7 @@
         <v>15</v>
       </c>
       <c r="I129" s="4">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.25">
@@ -8911,7 +8911,7 @@
         <v>12</v>
       </c>
       <c r="F137" s="4">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="G137" s="4">
         <v>39</v>
@@ -8920,7 +8920,7 @@
         <v>12</v>
       </c>
       <c r="I137" s="4">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.25">
@@ -8940,16 +8940,16 @@
         <v>12</v>
       </c>
       <c r="F138" s="4">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G138" s="4">
         <v>5</v>
       </c>
       <c r="H138" s="4">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I138" s="4">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.25">
@@ -9120,7 +9120,7 @@
         <v>12</v>
       </c>
       <c r="H144" s="4">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I144" s="4">
         <v>34</v>
@@ -9404,16 +9404,16 @@
         <v>13</v>
       </c>
       <c r="F154" s="4">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="G154" s="4">
         <v>32</v>
       </c>
       <c r="H154" s="4">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I154" s="4">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="155" spans="1:9" x14ac:dyDescent="0.25">
@@ -9433,16 +9433,16 @@
         <v>13</v>
       </c>
       <c r="F155" s="4">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G155" s="4">
         <v>37</v>
       </c>
       <c r="H155" s="4">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I155" s="4">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="156" spans="1:9" x14ac:dyDescent="0.25">
@@ -9555,7 +9555,7 @@
         <v>11</v>
       </c>
       <c r="H159" s="4">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="I159" s="4">
         <v>51</v>
@@ -9665,16 +9665,16 @@
         <v>13</v>
       </c>
       <c r="F163" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G163" s="4">
         <v>1</v>
       </c>
       <c r="H163" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I163" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="164" spans="1:9" x14ac:dyDescent="0.25">
@@ -9781,16 +9781,16 @@
         <v>14</v>
       </c>
       <c r="F167" s="4">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G167" s="4">
         <v>43</v>
       </c>
       <c r="H167" s="4">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I167" s="4">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="168" spans="1:9" x14ac:dyDescent="0.25">
@@ -9839,7 +9839,7 @@
         <v>14</v>
       </c>
       <c r="F169" s="4">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G169" s="4">
         <v>18</v>
@@ -9848,7 +9848,7 @@
         <v>9</v>
       </c>
       <c r="I169" s="4">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="170" spans="1:9" x14ac:dyDescent="0.25">
@@ -9903,7 +9903,7 @@
         <v>2</v>
       </c>
       <c r="H171" s="4">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="I171" s="4">
         <v>40</v>
@@ -10071,16 +10071,16 @@
         <v>15</v>
       </c>
       <c r="F177" s="4">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G177" s="4">
         <v>10</v>
       </c>
       <c r="H177" s="4">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="I177" s="4">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="178" spans="1:9" x14ac:dyDescent="0.25">
@@ -10106,7 +10106,7 @@
         <v>2</v>
       </c>
       <c r="H178" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I178" s="4">
         <v>15</v>
@@ -10274,16 +10274,16 @@
         <v>15</v>
       </c>
       <c r="F184" s="4">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G184" s="4">
         <v>26</v>
       </c>
       <c r="H184" s="4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I184" s="4">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="185" spans="1:9" x14ac:dyDescent="0.25">
@@ -10303,16 +10303,16 @@
         <v>15</v>
       </c>
       <c r="F185" s="4">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G185" s="4">
         <v>22</v>
       </c>
       <c r="H185" s="4">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I185" s="4">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="186" spans="1:9" x14ac:dyDescent="0.25">
@@ -10425,7 +10425,7 @@
         <v>10</v>
       </c>
       <c r="H189" s="4">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I189" s="4">
         <v>38</v>
@@ -10448,16 +10448,16 @@
         <v>16</v>
       </c>
       <c r="F190" s="4">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="G190" s="4">
         <v>72</v>
       </c>
       <c r="H190" s="4">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I190" s="4">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="191" spans="1:9" x14ac:dyDescent="0.25">
@@ -10483,7 +10483,7 @@
         <v>5</v>
       </c>
       <c r="H191" s="4">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="I191" s="4">
         <v>33</v>
@@ -10628,7 +10628,7 @@
         <v>1</v>
       </c>
       <c r="H196" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I196" s="4">
         <v>3</v>
@@ -10709,16 +10709,16 @@
         <v>17</v>
       </c>
       <c r="F199" s="4">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="G199" s="4">
         <v>33</v>
       </c>
       <c r="H199" s="4">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I199" s="4">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="200" spans="1:9" x14ac:dyDescent="0.25">
@@ -10773,7 +10773,7 @@
         <v>15</v>
       </c>
       <c r="H201" s="4">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I201" s="4">
         <v>43</v>
@@ -10802,7 +10802,7 @@
         <v>5</v>
       </c>
       <c r="H202" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I202" s="4">
         <v>16</v>
@@ -10825,16 +10825,16 @@
         <v>17</v>
       </c>
       <c r="F203" s="4">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G203" s="4">
         <v>17</v>
       </c>
       <c r="H203" s="4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I203" s="4">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="204" spans="1:9" x14ac:dyDescent="0.25">
@@ -11057,16 +11057,16 @@
         <v>18</v>
       </c>
       <c r="F211" s="4">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G211" s="4">
         <v>11</v>
       </c>
       <c r="H211" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I211" s="4">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="212" spans="1:9" x14ac:dyDescent="0.25">
@@ -11144,16 +11144,16 @@
         <v>18</v>
       </c>
       <c r="F214" s="4">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G214" s="4">
         <v>8</v>
       </c>
       <c r="H214" s="4">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="I214" s="4">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="215" spans="1:9" x14ac:dyDescent="0.25">
@@ -11173,7 +11173,7 @@
         <v>18</v>
       </c>
       <c r="F215" s="4">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G215" s="4">
         <v>27</v>
@@ -11182,7 +11182,7 @@
         <v>17</v>
       </c>
       <c r="I215" s="4">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="216" spans="1:9" x14ac:dyDescent="0.25">
@@ -11347,16 +11347,16 @@
         <v>19</v>
       </c>
       <c r="F221" s="4">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="G221" s="4">
         <v>49</v>
       </c>
       <c r="H221" s="4">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I221" s="4">
-        <v>124</v>
+        <v>127</v>
       </c>
     </row>
     <row r="222" spans="1:9" x14ac:dyDescent="0.25">
@@ -11469,7 +11469,7 @@
         <v>17</v>
       </c>
       <c r="H225" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I225" s="4">
         <v>40</v>
@@ -11695,16 +11695,16 @@
         <v>19</v>
       </c>
       <c r="F233" s="4">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="G233" s="4">
         <v>2</v>
       </c>
       <c r="H233" s="4">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I233" s="4">
-        <v>33</v>
+        <v>42</v>
       </c>
     </row>
     <row r="234" spans="1:9" x14ac:dyDescent="0.25">
@@ -11788,7 +11788,7 @@
         <v>20</v>
       </c>
       <c r="H236" s="4">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I236" s="4">
         <v>48</v>
@@ -11869,16 +11869,16 @@
         <v>20</v>
       </c>
       <c r="F239" s="4">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G239" s="4">
         <v>21</v>
       </c>
       <c r="H239" s="4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I239" s="4">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="240" spans="1:9" x14ac:dyDescent="0.25">
@@ -12014,16 +12014,16 @@
         <v>20</v>
       </c>
       <c r="F244" s="4">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="G244" s="4">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H244" s="4">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I244" s="4">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
     <row r="245" spans="1:9" x14ac:dyDescent="0.25">
@@ -12107,7 +12107,7 @@
         <v>22</v>
       </c>
       <c r="H247" s="4">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I247" s="4">
         <v>57</v>
@@ -12165,7 +12165,7 @@
         <v>9</v>
       </c>
       <c r="H249" s="4">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="I249" s="4">
         <v>45</v>
@@ -12275,7 +12275,7 @@
         <v>21</v>
       </c>
       <c r="F253" s="4">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G253" s="4">
         <v>23</v>
@@ -12284,7 +12284,7 @@
         <v>13</v>
       </c>
       <c r="I253" s="4">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="254" spans="1:9" x14ac:dyDescent="0.25">
@@ -12397,7 +12397,7 @@
         <v>9</v>
       </c>
       <c r="H257" s="4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I257" s="4">
         <v>37</v>
@@ -12449,16 +12449,16 @@
         <v>22</v>
       </c>
       <c r="F259" s="4">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G259" s="4">
         <v>18</v>
       </c>
       <c r="H259" s="4">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I259" s="4">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="260" spans="1:9" x14ac:dyDescent="0.25">
@@ -12745,7 +12745,7 @@
         <v>9</v>
       </c>
       <c r="H269" s="4">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="I269" s="4">
         <v>32</v>
@@ -12832,7 +12832,7 @@
         <v>33</v>
       </c>
       <c r="H272" s="4">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I272" s="4">
         <v>79</v>
@@ -12977,7 +12977,7 @@
         <v>40</v>
       </c>
       <c r="H277" s="4">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="I277" s="4">
         <v>97</v>
@@ -13087,10 +13087,10 @@
         <v>24</v>
       </c>
       <c r="F281" s="4">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G281" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H281" s="4">
         <v>1</v>
@@ -13203,7 +13203,7 @@
         <v>24</v>
       </c>
       <c r="F285" s="4">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G285" s="4">
         <v>4</v>
@@ -13212,7 +13212,7 @@
         <v>10</v>
       </c>
       <c r="I285" s="4">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="286" spans="1:9" x14ac:dyDescent="0.25">
@@ -13464,7 +13464,7 @@
         <v>25</v>
       </c>
       <c r="F294" s="4">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G294" s="4">
         <v>0</v>
@@ -13473,7 +13473,7 @@
         <v>13</v>
       </c>
       <c r="I294" s="4">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="295" spans="1:9" x14ac:dyDescent="0.25">
@@ -13528,7 +13528,7 @@
         <v>7</v>
       </c>
       <c r="H296" s="4">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I296" s="4">
         <v>35</v>
@@ -13644,7 +13644,7 @@
         <v>3</v>
       </c>
       <c r="H300" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I300" s="4">
         <v>11</v>
@@ -13783,16 +13783,16 @@
         <v>26</v>
       </c>
       <c r="F305" s="4">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G305" s="4">
         <v>62</v>
       </c>
       <c r="H305" s="4">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I305" s="4">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="306" spans="1:9" x14ac:dyDescent="0.25">
@@ -13812,16 +13812,16 @@
         <v>26</v>
       </c>
       <c r="F306" s="4">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G306" s="4">
         <v>4</v>
       </c>
       <c r="H306" s="4">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I306" s="4">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="307" spans="1:9" x14ac:dyDescent="0.25">
@@ -13992,7 +13992,7 @@
         <v>1</v>
       </c>
       <c r="H312" s="4">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I312" s="4">
         <v>17</v>
@@ -14015,7 +14015,7 @@
         <v>27</v>
       </c>
       <c r="F313" s="4">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="G313" s="4">
         <v>29</v>
@@ -14024,7 +14024,7 @@
         <v>21</v>
       </c>
       <c r="I313" s="4">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="314" spans="1:9" x14ac:dyDescent="0.25">
@@ -14050,7 +14050,7 @@
         <v>44</v>
       </c>
       <c r="H314" s="4">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I314" s="4">
         <v>96</v>
@@ -14166,7 +14166,7 @@
         <v>4</v>
       </c>
       <c r="H318" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I318" s="4">
         <v>6</v>
@@ -14311,7 +14311,7 @@
         <v>4</v>
       </c>
       <c r="H323" s="4">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I323" s="4">
         <v>37</v>
@@ -14514,7 +14514,7 @@
         <v>4</v>
       </c>
       <c r="H330" s="4">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I330" s="4">
         <v>14</v>
@@ -14775,7 +14775,7 @@
         <v>12</v>
       </c>
       <c r="H339" s="4">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I339" s="4">
         <v>58</v>
@@ -14798,16 +14798,16 @@
         <v>29</v>
       </c>
       <c r="F340" s="4">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="G340" s="4">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H340" s="4">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I340" s="4">
-        <v>139</v>
+        <v>144</v>
       </c>
     </row>
     <row r="341" spans="1:9" x14ac:dyDescent="0.25">
@@ -14914,7 +14914,7 @@
         <v>29</v>
       </c>
       <c r="F344" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G344" s="4">
         <v>0</v>
@@ -14923,7 +14923,7 @@
         <v>0</v>
       </c>
       <c r="I344" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="345" spans="1:9" x14ac:dyDescent="0.25">
@@ -15065,7 +15065,7 @@
         <v>2</v>
       </c>
       <c r="H349" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I349" s="4">
         <v>7</v>
@@ -15210,7 +15210,7 @@
         <v>3</v>
       </c>
       <c r="H354" s="4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I354" s="4">
         <v>10</v>
@@ -15291,16 +15291,16 @@
         <v>30</v>
       </c>
       <c r="F357" s="4">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="G357" s="4">
         <v>44</v>
       </c>
       <c r="H357" s="4">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I357" s="4">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="358" spans="1:9" x14ac:dyDescent="0.25">
@@ -15407,7 +15407,7 @@
         <v>30</v>
       </c>
       <c r="F361" s="4">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G361" s="4">
         <v>20</v>
@@ -15416,7 +15416,7 @@
         <v>11</v>
       </c>
       <c r="I361" s="4">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="362" spans="1:9" x14ac:dyDescent="0.25">
@@ -15436,7 +15436,7 @@
         <v>30</v>
       </c>
       <c r="F362" s="4">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G362" s="4">
         <v>20</v>
@@ -15445,7 +15445,7 @@
         <v>11</v>
       </c>
       <c r="I362" s="4">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="363" spans="1:9" x14ac:dyDescent="0.25">
@@ -15529,7 +15529,7 @@
         <v>46</v>
       </c>
       <c r="H365" s="4">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="I365" s="4">
         <v>108</v>
@@ -15552,7 +15552,7 @@
         <v>31</v>
       </c>
       <c r="F366" s="4">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G366" s="4">
         <v>3</v>
@@ -15561,7 +15561,7 @@
         <v>1</v>
       </c>
       <c r="I366" s="4">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="367" spans="1:9" x14ac:dyDescent="0.25">
@@ -15616,7 +15616,7 @@
         <v>3</v>
       </c>
       <c r="H368" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I368" s="4">
         <v>6</v>
@@ -15645,7 +15645,7 @@
         <v>10</v>
       </c>
       <c r="H369" s="4">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="I369" s="4">
         <v>39</v>
@@ -15674,7 +15674,7 @@
         <v>7</v>
       </c>
       <c r="H370" s="4">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="I370" s="4">
         <v>41</v>
@@ -15813,10 +15813,10 @@
         <v>31</v>
       </c>
       <c r="F375" s="4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G375" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H375" s="4">
         <v>3</v>
@@ -15906,7 +15906,7 @@
         <v>9</v>
       </c>
       <c r="H378" s="4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I378" s="4">
         <v>34</v>
@@ -16016,16 +16016,16 @@
         <v>32</v>
       </c>
       <c r="F382" s="4">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="G382" s="4">
         <v>61</v>
       </c>
       <c r="H382" s="4">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="I382" s="4">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="383" spans="1:9" x14ac:dyDescent="0.25">
@@ -16080,7 +16080,7 @@
         <v>5</v>
       </c>
       <c r="H384" s="4">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="I384" s="4">
         <v>39</v>
@@ -16283,7 +16283,7 @@
         <v>4</v>
       </c>
       <c r="H391" s="4">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="I391" s="4">
         <v>31</v>
@@ -16422,16 +16422,16 @@
         <v>33</v>
       </c>
       <c r="F396" s="4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G396" s="4">
         <v>5</v>
       </c>
       <c r="H396" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I396" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="397" spans="1:9" x14ac:dyDescent="0.25">
@@ -16602,7 +16602,7 @@
         <v>10</v>
       </c>
       <c r="H402" s="4">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="I402" s="4">
         <v>42</v>
@@ -16625,16 +16625,16 @@
         <v>33</v>
       </c>
       <c r="F403" s="4">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="G403" s="4">
         <v>58</v>
       </c>
       <c r="H403" s="4">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I403" s="4">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="404" spans="1:9" x14ac:dyDescent="0.25">
@@ -16863,7 +16863,7 @@
         <v>8</v>
       </c>
       <c r="H411" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I411" s="4">
         <v>9</v>
@@ -16892,7 +16892,7 @@
         <v>1</v>
       </c>
       <c r="H412" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I412" s="4">
         <v>7</v>
@@ -16979,7 +16979,7 @@
         <v>7</v>
       </c>
       <c r="H415" s="4">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="I415" s="4">
         <v>40</v>
@@ -17037,7 +17037,7 @@
         <v>6</v>
       </c>
       <c r="H417" s="4">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="I417" s="4">
         <v>39</v>
@@ -17095,7 +17095,7 @@
         <v>6</v>
       </c>
       <c r="H419" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I419" s="4">
         <v>11</v>
@@ -17292,16 +17292,16 @@
         <v>35</v>
       </c>
       <c r="F426" s="4">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G426" s="4">
         <v>44</v>
       </c>
       <c r="H426" s="4">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="I426" s="4">
-        <v>80</v>
+        <v>83</v>
       </c>
     </row>
     <row r="427" spans="1:9" x14ac:dyDescent="0.25">
@@ -17321,16 +17321,16 @@
         <v>35</v>
       </c>
       <c r="F427" s="4">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G427" s="4">
         <v>10</v>
       </c>
       <c r="H427" s="4">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I427" s="4">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="428" spans="1:9" x14ac:dyDescent="0.25">
@@ -17350,16 +17350,16 @@
         <v>35</v>
       </c>
       <c r="F428" s="4">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G428" s="4">
         <v>7</v>
       </c>
       <c r="H428" s="4">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="I428" s="4">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="429" spans="1:9" x14ac:dyDescent="0.25">
@@ -17437,7 +17437,7 @@
         <v>35</v>
       </c>
       <c r="F431" s="4">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G431" s="4">
         <v>25</v>
@@ -17446,7 +17446,7 @@
         <v>15</v>
       </c>
       <c r="I431" s="4">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="432" spans="1:9" x14ac:dyDescent="0.25">
@@ -17559,7 +17559,7 @@
         <v>8</v>
       </c>
       <c r="H435" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I435" s="4">
         <v>17</v>
@@ -17640,7 +17640,7 @@
         <v>36</v>
       </c>
       <c r="F438" s="4">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G438" s="4">
         <v>20</v>
@@ -17649,7 +17649,7 @@
         <v>10</v>
       </c>
       <c r="I438" s="4">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="439" spans="1:9" x14ac:dyDescent="0.25">
@@ -17704,7 +17704,7 @@
         <v>20</v>
       </c>
       <c r="H440" s="4">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I440" s="4">
         <v>52</v>
@@ -17733,7 +17733,7 @@
         <v>34</v>
       </c>
       <c r="H441" s="4">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I441" s="4">
         <v>55</v>
@@ -17820,7 +17820,7 @@
         <v>7</v>
       </c>
       <c r="H444" s="4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I444" s="4">
         <v>18</v>
@@ -17907,7 +17907,7 @@
         <v>7</v>
       </c>
       <c r="H447" s="4">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="I447" s="4">
         <v>29</v>
@@ -18162,16 +18162,16 @@
         <v>37</v>
       </c>
       <c r="F456" s="4">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G456" s="4">
         <v>24</v>
       </c>
       <c r="H456" s="4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I456" s="4">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="457" spans="1:9" x14ac:dyDescent="0.25">
@@ -18197,7 +18197,7 @@
         <v>2</v>
       </c>
       <c r="H457" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I457" s="4">
         <v>10</v>
@@ -18220,16 +18220,16 @@
         <v>37</v>
       </c>
       <c r="F458" s="4">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G458" s="4">
         <v>12</v>
       </c>
       <c r="H458" s="4">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I458" s="4">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="459" spans="1:9" x14ac:dyDescent="0.25">
@@ -18249,16 +18249,16 @@
         <v>37</v>
       </c>
       <c r="F459" s="4">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G459" s="4">
         <v>7</v>
       </c>
       <c r="H459" s="4">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I459" s="4">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="460" spans="1:9" x14ac:dyDescent="0.25">
@@ -18400,7 +18400,7 @@
         <v>14</v>
       </c>
       <c r="H464" s="4">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I464" s="4">
         <v>39</v>
@@ -18458,7 +18458,7 @@
         <v>21</v>
       </c>
       <c r="H466" s="4">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I466" s="4">
         <v>29</v>
@@ -18487,7 +18487,7 @@
         <v>6</v>
       </c>
       <c r="H467" s="4">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="I467" s="4">
         <v>40</v>
@@ -18545,7 +18545,7 @@
         <v>8</v>
       </c>
       <c r="H469" s="4">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="I469" s="4">
         <v>41</v>
@@ -18603,7 +18603,7 @@
         <v>68</v>
       </c>
       <c r="H471" s="4">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="I471" s="4">
         <v>133</v>
@@ -18632,7 +18632,7 @@
         <v>7</v>
       </c>
       <c r="H472" s="4">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I472" s="4">
         <v>32</v>
@@ -18742,16 +18742,16 @@
         <v>39</v>
       </c>
       <c r="F476" s="4">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G476" s="4">
         <v>5</v>
       </c>
       <c r="H476" s="4">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="I476" s="4">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="477" spans="1:9" x14ac:dyDescent="0.25">
@@ -19067,7 +19067,7 @@
         <v>0</v>
       </c>
       <c r="H487" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I487" s="4">
         <v>12</v>
@@ -19096,7 +19096,7 @@
         <v>5</v>
       </c>
       <c r="H488" s="4">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="I488" s="4">
         <v>55</v>
@@ -19241,7 +19241,7 @@
         <v>35</v>
       </c>
       <c r="H493" s="4">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I493" s="4">
         <v>53</v>
@@ -19322,7 +19322,7 @@
         <v>41</v>
       </c>
       <c r="F496" s="4">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G496" s="4">
         <v>27</v>
@@ -19331,7 +19331,7 @@
         <v>19</v>
       </c>
       <c r="I496" s="4">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="497" spans="1:9" x14ac:dyDescent="0.25">
@@ -19415,7 +19415,7 @@
         <v>12</v>
       </c>
       <c r="H499" s="4">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="I499" s="4">
         <v>30</v>
@@ -19502,7 +19502,7 @@
         <v>14</v>
       </c>
       <c r="H502" s="4">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I502" s="4">
         <v>34</v>
@@ -19670,7 +19670,7 @@
         <v>42</v>
       </c>
       <c r="F508" s="4">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G508" s="4">
         <v>10</v>
@@ -19679,7 +19679,7 @@
         <v>20</v>
       </c>
       <c r="I508" s="4">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="509" spans="1:9" x14ac:dyDescent="0.25">
@@ -19757,16 +19757,16 @@
         <v>42</v>
       </c>
       <c r="F511" s="4">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="G511" s="4">
         <v>64</v>
       </c>
       <c r="H511" s="4">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I511" s="4">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="512" spans="1:9" x14ac:dyDescent="0.25">
@@ -19786,7 +19786,7 @@
         <v>42</v>
       </c>
       <c r="F512" s="4">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G512" s="4">
         <v>6</v>
@@ -19795,7 +19795,7 @@
         <v>1</v>
       </c>
       <c r="I512" s="4">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="513" spans="1:9" x14ac:dyDescent="0.25">
@@ -19821,7 +19821,7 @@
         <v>14</v>
       </c>
       <c r="H513" s="4">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I513" s="4">
         <v>38</v>
@@ -19844,7 +19844,7 @@
         <v>42</v>
       </c>
       <c r="F514" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G514" s="4">
         <v>0</v>
@@ -19853,7 +19853,7 @@
         <v>1</v>
       </c>
       <c r="I514" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="515" spans="1:9" x14ac:dyDescent="0.25">
@@ -19966,7 +19966,7 @@
         <v>7</v>
       </c>
       <c r="H518" s="4">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="I518" s="4">
         <v>35</v>
@@ -20053,7 +20053,7 @@
         <v>6</v>
       </c>
       <c r="H521" s="4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I521" s="4">
         <v>11</v>
@@ -20082,7 +20082,7 @@
         <v>47</v>
       </c>
       <c r="H522" s="4">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="I522" s="4">
         <v>119</v>
@@ -20140,7 +20140,7 @@
         <v>10</v>
       </c>
       <c r="H524" s="4">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="I524" s="4">
         <v>37</v>
@@ -20256,7 +20256,7 @@
         <v>0</v>
       </c>
       <c r="H528" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I528" s="4">
         <v>2</v>
@@ -20285,7 +20285,7 @@
         <v>0</v>
       </c>
       <c r="H529" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I529" s="4">
         <v>5</v>
@@ -20314,7 +20314,7 @@
         <v>17</v>
       </c>
       <c r="H530" s="4">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I530" s="4">
         <v>37</v>
@@ -20343,7 +20343,7 @@
         <v>39</v>
       </c>
       <c r="H531" s="4">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="I531" s="4">
         <v>80</v>
@@ -20401,7 +20401,7 @@
         <v>0</v>
       </c>
       <c r="H533" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I533" s="4">
         <v>2</v>
@@ -20459,7 +20459,7 @@
         <v>2</v>
       </c>
       <c r="H535" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I535" s="4">
         <v>18</v>
@@ -20488,7 +20488,7 @@
         <v>16</v>
       </c>
       <c r="H536" s="4">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I536" s="4">
         <v>49</v>
@@ -20598,7 +20598,7 @@
         <v>45</v>
       </c>
       <c r="F540" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G540" s="4">
         <v>0</v>
@@ -20607,7 +20607,7 @@
         <v>1</v>
       </c>
       <c r="I540" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="541" spans="1:9" x14ac:dyDescent="0.25">
@@ -20691,7 +20691,7 @@
         <v>12</v>
       </c>
       <c r="H543" s="4">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="I543" s="4">
         <v>39</v>
@@ -20743,13 +20743,13 @@
         <v>45</v>
       </c>
       <c r="F545" s="4">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G545" s="4">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H545" s="4">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I545" s="4">
         <v>86</v>
@@ -20807,7 +20807,7 @@
         <v>27</v>
       </c>
       <c r="H547" s="4">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I547" s="4">
         <v>73</v>
@@ -20865,7 +20865,7 @@
         <v>2</v>
       </c>
       <c r="H549" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I549" s="4">
         <v>1</v>
@@ -21010,7 +21010,7 @@
         <v>3</v>
       </c>
       <c r="H554" s="4">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="I554" s="4">
         <v>31</v>
@@ -21033,16 +21033,16 @@
         <v>46</v>
       </c>
       <c r="F555" s="4">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="G555" s="4">
         <v>77</v>
       </c>
       <c r="H555" s="4">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="I555" s="4">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="556" spans="1:9" x14ac:dyDescent="0.25">
@@ -21097,7 +21097,7 @@
         <v>1</v>
       </c>
       <c r="H557" s="4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I557" s="4">
         <v>8</v>
@@ -21358,7 +21358,7 @@
         <v>2</v>
       </c>
       <c r="H566" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I566" s="4">
         <v>7</v>
@@ -21445,7 +21445,7 @@
         <v>25</v>
       </c>
       <c r="H569" s="4">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I569" s="4">
         <v>46</v>
@@ -21561,7 +21561,7 @@
         <v>6</v>
       </c>
       <c r="H573" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I573" s="4">
         <v>27</v>
@@ -21590,7 +21590,7 @@
         <v>12</v>
       </c>
       <c r="H574" s="4">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I574" s="4">
         <v>48</v>
@@ -21648,7 +21648,7 @@
         <v>17</v>
       </c>
       <c r="H576" s="4">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I576" s="4">
         <v>37</v>
@@ -21735,7 +21735,7 @@
         <v>2</v>
       </c>
       <c r="H579" s="4">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I579" s="4">
         <v>19</v>
@@ -21764,7 +21764,7 @@
         <v>15</v>
       </c>
       <c r="H580" s="4">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I580" s="4">
         <v>41</v>
@@ -21851,7 +21851,7 @@
         <v>12</v>
       </c>
       <c r="H583" s="4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I583" s="4">
         <v>14</v>
@@ -21880,7 +21880,7 @@
         <v>18</v>
       </c>
       <c r="H584" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I584" s="4">
         <v>35</v>
@@ -21938,7 +21938,7 @@
         <v>14</v>
       </c>
       <c r="H586" s="4">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I586" s="4">
         <v>37</v>
@@ -22141,7 +22141,7 @@
         <v>81</v>
       </c>
       <c r="H593" s="4">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I593" s="4">
         <v>177</v>
@@ -22170,7 +22170,7 @@
         <v>0</v>
       </c>
       <c r="H594" s="4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I594" s="4">
         <v>15</v>
@@ -22199,7 +22199,7 @@
         <v>0</v>
       </c>
       <c r="H595" s="4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I595" s="4">
         <v>11</v>
@@ -22431,7 +22431,7 @@
         <v>9</v>
       </c>
       <c r="H603" s="4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I603" s="4">
         <v>18</v>
@@ -22483,7 +22483,7 @@
         <v>50</v>
       </c>
       <c r="F605" s="4">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G605" s="4">
         <v>55</v>
@@ -22492,7 +22492,7 @@
         <v>34</v>
       </c>
       <c r="I605" s="4">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="606" spans="1:9" x14ac:dyDescent="0.25">
@@ -22547,7 +22547,7 @@
         <v>10</v>
       </c>
       <c r="H607" s="4">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="I607" s="4">
         <v>32</v>
@@ -22570,7 +22570,7 @@
         <v>50</v>
       </c>
       <c r="F608" s="4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G608" s="4">
         <v>2</v>
@@ -22579,7 +22579,7 @@
         <v>2</v>
       </c>
       <c r="I608" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="609" spans="1:9" x14ac:dyDescent="0.25">
@@ -22750,7 +22750,7 @@
         <v>34</v>
       </c>
       <c r="H614" s="4">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I614" s="4">
         <v>71</v>
@@ -22866,7 +22866,7 @@
         <v>10</v>
       </c>
       <c r="H618" s="4">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="I618" s="4">
         <v>38</v>
@@ -22982,7 +22982,7 @@
         <v>15</v>
       </c>
       <c r="H622" s="4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I622" s="4">
         <v>17</v>
@@ -23185,7 +23185,7 @@
         <v>8</v>
       </c>
       <c r="H629" s="4">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I629" s="4">
         <v>22</v>
@@ -23301,7 +23301,7 @@
         <v>4</v>
       </c>
       <c r="H633" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I633" s="4">
         <v>5</v>
@@ -23359,7 +23359,7 @@
         <v>6</v>
       </c>
       <c r="H635" s="4">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I635" s="4">
         <v>23</v>
@@ -23446,7 +23446,7 @@
         <v>11</v>
       </c>
       <c r="H638" s="4">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I638" s="4">
         <v>44</v>
@@ -23475,7 +23475,7 @@
         <v>3</v>
       </c>
       <c r="H639" s="4">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I639" s="4">
         <v>39</v>
@@ -23701,13 +23701,13 @@
         <v>53</v>
       </c>
       <c r="F647" s="4">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G647" s="4">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H647" s="4">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="I647" s="4">
         <v>48</v>
@@ -23730,16 +23730,16 @@
         <v>53</v>
       </c>
       <c r="F648" s="4">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G648" s="4">
         <v>43</v>
       </c>
       <c r="H648" s="4">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I648" s="4">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="649" spans="1:9" x14ac:dyDescent="0.25">
@@ -23765,7 +23765,7 @@
         <v>11</v>
       </c>
       <c r="H649" s="4">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I649" s="4">
         <v>40</v>
@@ -23852,7 +23852,7 @@
         <v>2</v>
       </c>
       <c r="H652" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I652" s="4">
         <v>11</v>
@@ -23939,7 +23939,7 @@
         <v>42</v>
       </c>
       <c r="H655" s="4">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="I655" s="4">
         <v>56</v>
@@ -24026,7 +24026,7 @@
         <v>1</v>
       </c>
       <c r="H658" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I658" s="4">
         <v>13</v>
@@ -24055,7 +24055,7 @@
         <v>9</v>
       </c>
       <c r="H659" s="4">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="I659" s="4">
         <v>42</v>
@@ -24113,7 +24113,7 @@
         <v>12</v>
       </c>
       <c r="H661" s="4">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="I661" s="4">
         <v>35</v>
@@ -24200,7 +24200,7 @@
         <v>7</v>
       </c>
       <c r="H664" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I664" s="4">
         <v>13</v>
@@ -24281,7 +24281,7 @@
         <v>55</v>
       </c>
       <c r="F667" s="4">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G667" s="4">
         <v>18</v>
@@ -24290,7 +24290,7 @@
         <v>12</v>
       </c>
       <c r="I667" s="4">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="668" spans="1:9" x14ac:dyDescent="0.25">
@@ -24403,7 +24403,7 @@
         <v>28</v>
       </c>
       <c r="H671" s="4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I671" s="4">
         <v>39</v>
@@ -24426,7 +24426,7 @@
         <v>55</v>
       </c>
       <c r="F672" s="4">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G672" s="4">
         <v>3</v>
@@ -24435,7 +24435,7 @@
         <v>5</v>
       </c>
       <c r="I672" s="4">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="673" spans="1:9" x14ac:dyDescent="0.25">
@@ -24577,7 +24577,7 @@
         <v>53</v>
       </c>
       <c r="H677" s="4">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I677" s="4">
         <v>138</v>
@@ -24658,16 +24658,16 @@
         <v>56</v>
       </c>
       <c r="F680" s="4">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G680" s="4">
         <v>6</v>
       </c>
       <c r="H680" s="4">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I680" s="4">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="681" spans="1:9" x14ac:dyDescent="0.25">
@@ -24722,7 +24722,7 @@
         <v>15</v>
       </c>
       <c r="H682" s="4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I682" s="4">
         <v>34</v>
@@ -24861,16 +24861,16 @@
         <v>57</v>
       </c>
       <c r="F687" s="4">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G687" s="4">
         <v>34</v>
       </c>
       <c r="H687" s="4">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I687" s="4">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="688" spans="1:9" x14ac:dyDescent="0.25">
@@ -24896,7 +24896,7 @@
         <v>0</v>
       </c>
       <c r="H688" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I688" s="4">
         <v>3</v>
@@ -24954,7 +24954,7 @@
         <v>1</v>
       </c>
       <c r="H690" s="4">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I690" s="4">
         <v>17</v>
@@ -25041,7 +25041,7 @@
         <v>5</v>
       </c>
       <c r="H693" s="4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I693" s="4">
         <v>14</v>
@@ -25064,16 +25064,16 @@
         <v>57</v>
       </c>
       <c r="F694" s="4">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="G694" s="4">
         <v>51</v>
       </c>
       <c r="H694" s="4">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="I694" s="4">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="695" spans="1:9" x14ac:dyDescent="0.25">
@@ -25215,7 +25215,7 @@
         <v>23</v>
       </c>
       <c r="H699" s="4">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I699" s="4">
         <v>62</v>
@@ -25244,7 +25244,7 @@
         <v>7</v>
       </c>
       <c r="H700" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I700" s="4">
         <v>11</v>
@@ -25267,16 +25267,16 @@
         <v>58</v>
       </c>
       <c r="F701" s="4">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G701" s="4">
         <v>8</v>
       </c>
       <c r="H701" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I701" s="4">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="702" spans="1:9" x14ac:dyDescent="0.25">
@@ -25331,7 +25331,7 @@
         <v>8</v>
       </c>
       <c r="H703" s="4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I703" s="4">
         <v>25</v>
@@ -25360,7 +25360,7 @@
         <v>13</v>
       </c>
       <c r="H704" s="4">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I704" s="4">
         <v>45</v>
@@ -25383,16 +25383,16 @@
         <v>58</v>
       </c>
       <c r="F705" s="4">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G705" s="4">
         <v>28</v>
       </c>
       <c r="H705" s="4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I705" s="4">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="706" spans="1:9" x14ac:dyDescent="0.25">
@@ -25505,7 +25505,7 @@
         <v>4</v>
       </c>
       <c r="H709" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I709" s="4">
         <v>8</v>
@@ -25621,7 +25621,7 @@
         <v>14</v>
       </c>
       <c r="H713" s="4">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I713" s="4">
         <v>40</v>
@@ -25673,16 +25673,16 @@
         <v>59</v>
       </c>
       <c r="F715" s="4">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="G715" s="4">
         <v>41</v>
       </c>
       <c r="H715" s="4">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="I715" s="4">
-        <v>90</v>
+        <v>93</v>
       </c>
     </row>
     <row r="716" spans="1:9" x14ac:dyDescent="0.25">
@@ -25766,7 +25766,7 @@
         <v>4</v>
       </c>
       <c r="H718" s="4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I718" s="4">
         <v>13</v>
@@ -25969,7 +25969,7 @@
         <v>43</v>
       </c>
       <c r="H725" s="4">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="I725" s="4">
         <v>85</v>
@@ -26027,7 +26027,7 @@
         <v>17</v>
       </c>
       <c r="H727" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I727" s="4">
         <v>49</v>
@@ -26056,7 +26056,7 @@
         <v>8</v>
       </c>
       <c r="H728" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I728" s="4">
         <v>15</v>
@@ -26114,7 +26114,7 @@
         <v>6</v>
       </c>
       <c r="H730" s="4">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="I730" s="4">
         <v>37</v>
@@ -26230,7 +26230,7 @@
         <v>5</v>
       </c>
       <c r="H734" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I734" s="4">
         <v>4</v>
@@ -26288,7 +26288,7 @@
         <v>15</v>
       </c>
       <c r="H736" s="4">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="I736" s="4">
         <v>47</v>
@@ -26346,7 +26346,7 @@
         <v>0</v>
       </c>
       <c r="H738" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I738" s="4">
         <v>4</v>
@@ -26375,7 +26375,7 @@
         <v>33</v>
       </c>
       <c r="H739" s="4">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="I739" s="4">
         <v>53</v>
@@ -26404,7 +26404,7 @@
         <v>31</v>
       </c>
       <c r="H740" s="4">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="I740" s="4">
         <v>111</v>
@@ -26462,7 +26462,7 @@
         <v>2</v>
       </c>
       <c r="H742" s="4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I742" s="4">
         <v>23</v>
@@ -26572,16 +26572,16 @@
         <v>62</v>
       </c>
       <c r="F746" s="4">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G746" s="4">
         <v>9</v>
       </c>
       <c r="H746" s="4">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I746" s="4">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="747" spans="1:9" x14ac:dyDescent="0.25">
@@ -26630,16 +26630,16 @@
         <v>62</v>
       </c>
       <c r="F748" s="4">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G748" s="4">
         <v>68</v>
       </c>
       <c r="H748" s="4">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="I748" s="4">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="749" spans="1:9" x14ac:dyDescent="0.25">
@@ -26781,7 +26781,7 @@
         <v>0</v>
       </c>
       <c r="H753" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I753" s="4">
         <v>2</v>
@@ -26868,7 +26868,7 @@
         <v>3</v>
       </c>
       <c r="H756" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I756" s="4">
         <v>8</v>
@@ -26955,7 +26955,7 @@
         <v>1</v>
       </c>
       <c r="H759" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I759" s="4">
         <v>2</v>
@@ -26978,7 +26978,7 @@
         <v>63</v>
       </c>
       <c r="F760" s="4">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G760" s="4">
         <v>22</v>
@@ -26987,7 +26987,7 @@
         <v>21</v>
       </c>
       <c r="I760" s="4">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="761" spans="1:9" x14ac:dyDescent="0.25">
@@ -27007,16 +27007,16 @@
         <v>63</v>
       </c>
       <c r="F761" s="4">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="G761" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H761" s="4">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I761" s="4">
-        <v>25</v>
+        <v>31</v>
       </c>
     </row>
     <row r="762" spans="1:9" x14ac:dyDescent="0.25">
@@ -27065,16 +27065,16 @@
         <v>63</v>
       </c>
       <c r="F763" s="4">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="G763" s="4">
         <v>6</v>
       </c>
       <c r="H763" s="4">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I763" s="4">
-        <v>34</v>
+        <v>41</v>
       </c>
     </row>
     <row r="764" spans="1:9" x14ac:dyDescent="0.25">
@@ -27100,7 +27100,7 @@
         <v>29</v>
       </c>
       <c r="H764" s="4">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="I764" s="4">
         <v>79</v>
@@ -27216,7 +27216,7 @@
         <v>5</v>
       </c>
       <c r="H768" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I768" s="4">
         <v>18</v>
@@ -27239,7 +27239,7 @@
         <v>64</v>
       </c>
       <c r="F769" s="4">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G769" s="4">
         <v>15</v>
@@ -27248,7 +27248,7 @@
         <v>9</v>
       </c>
       <c r="I769" s="4">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="770" spans="1:9" x14ac:dyDescent="0.25">
@@ -27274,7 +27274,7 @@
         <v>9</v>
       </c>
       <c r="H770" s="4">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I770" s="4">
         <v>39</v>
@@ -27390,7 +27390,7 @@
         <v>26</v>
       </c>
       <c r="H774" s="4">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="I774" s="4">
         <v>42</v>
@@ -27419,7 +27419,7 @@
         <v>16</v>
       </c>
       <c r="H775" s="4">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="I775" s="4">
         <v>44</v>
@@ -27651,7 +27651,7 @@
         <v>7</v>
       </c>
       <c r="H783" s="4">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I783" s="4">
         <v>13</v>
@@ -27680,7 +27680,7 @@
         <v>71</v>
       </c>
       <c r="H784" s="4">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="I784" s="4">
         <v>201</v>
@@ -27738,7 +27738,7 @@
         <v>1</v>
       </c>
       <c r="H786" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I786" s="4">
         <v>2</v>
@@ -27854,7 +27854,7 @@
         <v>0</v>
       </c>
       <c r="H790" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I790" s="4">
         <v>6</v>
@@ -27912,7 +27912,7 @@
         <v>29</v>
       </c>
       <c r="H792" s="4">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I792" s="4">
         <v>54</v>
@@ -27970,7 +27970,7 @@
         <v>14</v>
       </c>
       <c r="H794" s="4">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I794" s="4">
         <v>95</v>
@@ -28022,16 +28022,16 @@
         <v>66</v>
       </c>
       <c r="F796" s="4">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="G796" s="4">
         <v>52</v>
       </c>
       <c r="H796" s="4">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="I796" s="4">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="797" spans="1:9" x14ac:dyDescent="0.25">
@@ -28115,7 +28115,7 @@
         <v>21</v>
       </c>
       <c r="H799" s="4">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="I799" s="4">
         <v>70</v>
@@ -28144,7 +28144,7 @@
         <v>0</v>
       </c>
       <c r="H800" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I800" s="4">
         <v>2</v>
@@ -28231,7 +28231,7 @@
         <v>11</v>
       </c>
       <c r="H803" s="4">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I803" s="4">
         <v>35</v>
@@ -28289,7 +28289,7 @@
         <v>1</v>
       </c>
       <c r="H805" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I805" s="4">
         <v>3</v>
@@ -28318,7 +28318,7 @@
         <v>31</v>
       </c>
       <c r="H806" s="4">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="I806" s="4">
         <v>59</v>
@@ -28376,7 +28376,7 @@
         <v>0</v>
       </c>
       <c r="H808" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I808" s="4">
         <v>7</v>
@@ -28521,7 +28521,7 @@
         <v>10</v>
       </c>
       <c r="H813" s="4">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I813" s="4">
         <v>40</v>
@@ -28573,16 +28573,16 @@
         <v>68</v>
       </c>
       <c r="F815" s="4">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="G815" s="4">
         <v>42</v>
       </c>
       <c r="H815" s="4">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I815" s="4">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="816" spans="1:9" x14ac:dyDescent="0.25">
@@ -28608,7 +28608,7 @@
         <v>33</v>
       </c>
       <c r="H816" s="4">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="I816" s="4">
         <v>58</v>
@@ -28695,7 +28695,7 @@
         <v>1</v>
       </c>
       <c r="H819" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I819" s="4">
         <v>2</v>
@@ -28834,16 +28834,16 @@
         <v>68</v>
       </c>
       <c r="F824" s="4">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="G824" s="4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H824" s="4">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I824" s="4">
-        <v>33</v>
+        <v>39</v>
       </c>
     </row>
     <row r="825" spans="1:9" x14ac:dyDescent="0.25">
@@ -28956,7 +28956,7 @@
         <v>35</v>
       </c>
       <c r="H828" s="4">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="I828" s="4">
         <v>92</v>
@@ -29014,7 +29014,7 @@
         <v>1</v>
       </c>
       <c r="H830" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I830" s="4">
         <v>4</v>
@@ -29188,7 +29188,7 @@
         <v>11</v>
       </c>
       <c r="H836" s="4">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I836" s="4">
         <v>58</v>
@@ -29246,7 +29246,7 @@
         <v>11</v>
       </c>
       <c r="H838" s="4">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I838" s="4">
         <v>54</v>
@@ -29275,7 +29275,7 @@
         <v>37</v>
       </c>
       <c r="H839" s="4">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="I839" s="4">
         <v>68</v>
@@ -29304,7 +29304,7 @@
         <v>39</v>
       </c>
       <c r="H840" s="4">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="I840" s="4">
         <v>80</v>
@@ -29391,7 +29391,7 @@
         <v>23</v>
       </c>
       <c r="H843" s="4">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="I843" s="4">
         <v>67</v>
@@ -29420,7 +29420,7 @@
         <v>4</v>
       </c>
       <c r="H844" s="4">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I844" s="4">
         <v>21</v>
@@ -29478,7 +29478,7 @@
         <v>48</v>
       </c>
       <c r="H846" s="4">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="I846" s="4">
         <v>104</v>
@@ -29565,7 +29565,7 @@
         <v>11</v>
       </c>
       <c r="H849" s="4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I849" s="4">
         <v>31</v>
@@ -29594,7 +29594,7 @@
         <v>23</v>
       </c>
       <c r="H850" s="4">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I850" s="4">
         <v>43</v>
@@ -29623,7 +29623,7 @@
         <v>11</v>
       </c>
       <c r="H851" s="4">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I851" s="4">
         <v>37</v>
@@ -29652,7 +29652,7 @@
         <v>21</v>
       </c>
       <c r="H852" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I852" s="4">
         <v>17</v>
@@ -29681,7 +29681,7 @@
         <v>16</v>
       </c>
       <c r="H853" s="4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I853" s="4">
         <v>37</v>
@@ -29849,7 +29849,7 @@
         <v>73</v>
       </c>
       <c r="F859" s="4">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="G859" s="4">
         <v>10</v>
@@ -29858,7 +29858,7 @@
         <v>20</v>
       </c>
       <c r="I859" s="4">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="860" spans="1:9" x14ac:dyDescent="0.25">
@@ -29907,16 +29907,16 @@
         <v>73</v>
       </c>
       <c r="F861" s="4">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="G861" s="4">
         <v>15</v>
       </c>
       <c r="H861" s="4">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I861" s="4">
-        <v>33</v>
+        <v>42</v>
       </c>
     </row>
     <row r="862" spans="1:9" x14ac:dyDescent="0.25">
@@ -30000,7 +30000,7 @@
         <v>9</v>
       </c>
       <c r="H864" s="4">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="I864" s="4">
         <v>29</v>
@@ -30023,16 +30023,16 @@
         <v>74</v>
       </c>
       <c r="F865" s="4">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="G865" s="4">
         <v>3</v>
       </c>
       <c r="H865" s="4">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I865" s="4">
-        <v>11</v>
+        <v>20</v>
       </c>
     </row>
     <row r="866" spans="1:9" x14ac:dyDescent="0.25">
@@ -30058,7 +30058,7 @@
         <v>7</v>
       </c>
       <c r="H866" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I866" s="4">
         <v>6</v>
@@ -30081,16 +30081,16 @@
         <v>74</v>
       </c>
       <c r="F867" s="4">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="G867" s="4">
         <v>9</v>
       </c>
       <c r="H867" s="4">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I867" s="4">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="868" spans="1:9" x14ac:dyDescent="0.25">
@@ -30116,7 +30116,7 @@
         <v>51</v>
       </c>
       <c r="H868" s="4">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="I868" s="4">
         <v>99</v>
@@ -30145,7 +30145,7 @@
         <v>5</v>
       </c>
       <c r="H869" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I869" s="4">
         <v>9</v>
@@ -30197,16 +30197,16 @@
         <v>75</v>
       </c>
       <c r="F871" s="4">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G871" s="4">
         <v>5</v>
       </c>
       <c r="H871" s="4">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I871" s="4">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="872" spans="1:9" x14ac:dyDescent="0.25">
@@ -30284,16 +30284,16 @@
         <v>75</v>
       </c>
       <c r="F874" s="4">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G874" s="4">
         <v>4</v>
       </c>
       <c r="H874" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I874" s="4">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="875" spans="1:9" x14ac:dyDescent="0.25">
@@ -30406,7 +30406,7 @@
         <v>3</v>
       </c>
       <c r="H878" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I878" s="4">
         <v>8</v>
@@ -30458,16 +30458,16 @@
         <v>76</v>
       </c>
       <c r="F880" s="4">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G880" s="4">
         <v>4</v>
       </c>
       <c r="H880" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I880" s="4">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="881" spans="1:9" x14ac:dyDescent="0.25">
@@ -30661,16 +30661,16 @@
         <v>76</v>
       </c>
       <c r="F887" s="4">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G887" s="4">
         <v>4</v>
       </c>
       <c r="H887" s="4">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I887" s="4">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="888" spans="1:9" x14ac:dyDescent="0.25">
@@ -30754,7 +30754,7 @@
         <v>28</v>
       </c>
       <c r="H890" s="4">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="I890" s="4">
         <v>62</v>
@@ -30986,7 +30986,7 @@
         <v>13</v>
       </c>
       <c r="H898" s="4">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="I898" s="4">
         <v>33</v>
@@ -31073,7 +31073,7 @@
         <v>14</v>
       </c>
       <c r="H901" s="4">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I901" s="4">
         <v>37</v>
@@ -31160,7 +31160,7 @@
         <v>7</v>
       </c>
       <c r="H904" s="4">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I904" s="4">
         <v>41</v>
@@ -31189,7 +31189,7 @@
         <v>12</v>
       </c>
       <c r="H905" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I905" s="4">
         <v>13</v>
@@ -31241,16 +31241,16 @@
         <v>78</v>
       </c>
       <c r="F907" s="4">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G907" s="4">
         <v>12</v>
       </c>
       <c r="H907" s="4">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I907" s="4">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="908" spans="1:9" x14ac:dyDescent="0.25">
@@ -31334,7 +31334,7 @@
         <v>6</v>
       </c>
       <c r="H910" s="4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I910" s="4">
         <v>33</v>
@@ -31479,7 +31479,7 @@
         <v>23</v>
       </c>
       <c r="H915" s="4">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I915" s="4">
         <v>44</v>
@@ -31653,7 +31653,7 @@
         <v>18</v>
       </c>
       <c r="H921" s="4">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I921" s="4">
         <v>50</v>
@@ -31711,7 +31711,7 @@
         <v>5</v>
       </c>
       <c r="H923" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I923" s="4">
         <v>11</v>
@@ -31740,7 +31740,7 @@
         <v>4</v>
       </c>
       <c r="H924" s="4">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="I924" s="4">
         <v>23</v>
@@ -31798,7 +31798,7 @@
         <v>34</v>
       </c>
       <c r="H926" s="4">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="I926" s="4">
         <v>83</v>
@@ -32024,16 +32024,16 @@
         <v>80</v>
       </c>
       <c r="F934" s="4">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G934" s="4">
         <v>18</v>
       </c>
       <c r="H934" s="4">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I934" s="4">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="935" spans="1:9" x14ac:dyDescent="0.25">
@@ -32082,16 +32082,16 @@
         <v>80</v>
       </c>
       <c r="F936" s="4">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G936" s="4">
         <v>10</v>
       </c>
       <c r="H936" s="4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I936" s="4">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="937" spans="1:9" x14ac:dyDescent="0.25">
@@ -32140,7 +32140,7 @@
         <v>80</v>
       </c>
       <c r="F938" s="4">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G938" s="4">
         <v>15</v>
@@ -32149,7 +32149,7 @@
         <v>11</v>
       </c>
       <c r="I938" s="4">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="939" spans="1:9" x14ac:dyDescent="0.25">
@@ -32204,7 +32204,7 @@
         <v>19</v>
       </c>
       <c r="H940" s="4">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I940" s="4">
         <v>45</v>
@@ -32262,7 +32262,7 @@
         <v>4</v>
       </c>
       <c r="H942" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I942" s="4">
         <v>3</v>
@@ -32546,16 +32546,16 @@
         <v>81</v>
       </c>
       <c r="F952" s="4">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G952" s="4">
         <v>37</v>
       </c>
       <c r="H952" s="4">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="I952" s="4">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="953" spans="1:9" x14ac:dyDescent="0.25">
@@ -32604,16 +32604,16 @@
         <v>81</v>
       </c>
       <c r="F954" s="4">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="G954" s="4">
         <v>44</v>
       </c>
       <c r="H954" s="4">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I954" s="4">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="955" spans="1:9" x14ac:dyDescent="0.25">
@@ -32668,7 +32668,7 @@
         <v>10</v>
       </c>
       <c r="H956" s="4">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I956" s="4">
         <v>35</v>
@@ -32784,7 +32784,7 @@
         <v>15</v>
       </c>
       <c r="H960" s="4">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I960" s="4">
         <v>33</v>
@@ -32958,7 +32958,7 @@
         <v>2</v>
       </c>
       <c r="H966" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I966" s="4">
         <v>5</v>
@@ -33016,7 +33016,7 @@
         <v>13</v>
       </c>
       <c r="H968" s="4">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I968" s="4">
         <v>39</v>
@@ -33126,16 +33126,16 @@
         <v>82</v>
       </c>
       <c r="F972" s="4">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G972" s="4">
         <v>11</v>
       </c>
       <c r="H972" s="4">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="I972" s="4">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="973" spans="1:9" x14ac:dyDescent="0.25">
@@ -33277,7 +33277,7 @@
         <v>9</v>
       </c>
       <c r="H977" s="4">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I977" s="4">
         <v>25</v>
@@ -33422,7 +33422,7 @@
         <v>9</v>
       </c>
       <c r="H982" s="4">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I982" s="4">
         <v>36</v>
@@ -33503,7 +33503,7 @@
         <v>83</v>
       </c>
       <c r="F985" s="4">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G985" s="4">
         <v>19</v>
@@ -33512,7 +33512,7 @@
         <v>4</v>
       </c>
       <c r="I985" s="4">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="986" spans="1:9" x14ac:dyDescent="0.25">
@@ -33596,7 +33596,7 @@
         <v>8</v>
       </c>
       <c r="H988" s="4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I988" s="4">
         <v>24</v>
@@ -33619,7 +33619,7 @@
         <v>83</v>
       </c>
       <c r="F989" s="4">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G989" s="4">
         <v>21</v>
@@ -33628,7 +33628,7 @@
         <v>8</v>
       </c>
       <c r="I989" s="4">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="990" spans="1:9" x14ac:dyDescent="0.25">
@@ -33706,16 +33706,16 @@
         <v>84</v>
       </c>
       <c r="F992" s="4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G992" s="4">
         <v>2</v>
       </c>
       <c r="H992" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I992" s="4">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="993" spans="1:9" x14ac:dyDescent="0.25">
@@ -33741,7 +33741,7 @@
         <v>4</v>
       </c>
       <c r="H993" s="4">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I993" s="4">
         <v>21</v>
@@ -33770,7 +33770,7 @@
         <v>27</v>
       </c>
       <c r="H994" s="4">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I994" s="4">
         <v>58</v>
@@ -33799,7 +33799,7 @@
         <v>22</v>
       </c>
       <c r="H995" s="4">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="I995" s="4">
         <v>35</v>
@@ -33822,16 +33822,16 @@
         <v>84</v>
       </c>
       <c r="F996" s="4">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="G996" s="4">
         <v>8</v>
       </c>
       <c r="H996" s="4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I996" s="4">
-        <v>26</v>
+        <v>33</v>
       </c>
     </row>
     <row r="997" spans="1:9" x14ac:dyDescent="0.25">
@@ -33880,16 +33880,16 @@
         <v>84</v>
       </c>
       <c r="F998" s="4">
+        <v>8</v>
+      </c>
+      <c r="G998" s="4">
+        <v>1</v>
+      </c>
+      <c r="H998" s="4">
+        <v>2</v>
+      </c>
+      <c r="I998" s="4">
         <v>7</v>
-      </c>
-      <c r="G998" s="4">
-        <v>1</v>
-      </c>
-      <c r="H998" s="4">
-        <v>1</v>
-      </c>
-      <c r="I998" s="4">
-        <v>6</v>
       </c>
     </row>
     <row r="999" spans="1:9" x14ac:dyDescent="0.25">
@@ -34031,7 +34031,7 @@
         <v>0</v>
       </c>
       <c r="H1003" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I1003" s="4">
         <v>5</v>
@@ -34199,16 +34199,16 @@
         <v>85</v>
       </c>
       <c r="F1009" s="4">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="G1009" s="4">
         <v>5</v>
       </c>
       <c r="H1009" s="4">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I1009" s="4">
-        <v>22</v>
+        <v>31</v>
       </c>
     </row>
     <row r="1010" spans="1:9" x14ac:dyDescent="0.25">
@@ -34263,7 +34263,7 @@
         <v>15</v>
       </c>
       <c r="H1011" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I1011" s="4">
         <v>14</v>
@@ -34373,16 +34373,16 @@
         <v>85</v>
       </c>
       <c r="F1015" s="4">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="G1015" s="4">
         <v>9</v>
       </c>
       <c r="H1015" s="4">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="I1015" s="4">
-        <v>21</v>
+        <v>32</v>
       </c>
     </row>
     <row r="1016" spans="1:9" x14ac:dyDescent="0.25">
@@ -34437,7 +34437,7 @@
         <v>7</v>
       </c>
       <c r="H1017" s="4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I1017" s="4">
         <v>14</v>
@@ -34553,7 +34553,7 @@
         <v>1</v>
       </c>
       <c r="H1021" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I1021" s="4">
         <v>3</v>
@@ -34576,13 +34576,13 @@
         <v>85</v>
       </c>
       <c r="F1022" s="4">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G1022" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1022" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I1022" s="4">
         <v>9</v>
@@ -34669,7 +34669,7 @@
         <v>26</v>
       </c>
       <c r="H1025" s="4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I1025" s="4">
         <v>52</v>
@@ -34814,7 +34814,7 @@
         <v>23</v>
       </c>
       <c r="H1030" s="4">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="I1030" s="4">
         <v>61</v>
@@ -34930,7 +34930,7 @@
         <v>14</v>
       </c>
       <c r="H1034" s="4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I1034" s="4">
         <v>36</v>
@@ -35046,7 +35046,7 @@
         <v>9</v>
       </c>
       <c r="H1038" s="4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I1038" s="4">
         <v>28</v>
@@ -35220,7 +35220,7 @@
         <v>2</v>
       </c>
       <c r="H1044" s="4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I1044" s="4">
         <v>12</v>
@@ -35452,7 +35452,7 @@
         <v>13</v>
       </c>
       <c r="H1052" s="4">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="I1052" s="4">
         <v>27</v>
@@ -35475,16 +35475,16 @@
         <v>87</v>
       </c>
       <c r="F1053" s="4">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="G1053" s="4">
         <v>62</v>
       </c>
       <c r="H1053" s="4">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="I1053" s="4">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="1054" spans="1:9" x14ac:dyDescent="0.25">
@@ -35562,16 +35562,16 @@
         <v>88</v>
       </c>
       <c r="F1056" s="4">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G1056" s="4">
         <v>45</v>
       </c>
       <c r="H1056" s="4">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="I1056" s="4">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="1057" spans="1:9" x14ac:dyDescent="0.25">
@@ -35626,7 +35626,7 @@
         <v>4</v>
       </c>
       <c r="H1058" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I1058" s="4">
         <v>9</v>
@@ -35684,7 +35684,7 @@
         <v>11</v>
       </c>
       <c r="H1060" s="4">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I1060" s="4">
         <v>22</v>
@@ -35713,7 +35713,7 @@
         <v>1</v>
       </c>
       <c r="H1061" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I1061" s="4">
         <v>10</v>
@@ -35736,16 +35736,16 @@
         <v>88</v>
       </c>
       <c r="F1062" s="4">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G1062" s="4">
         <v>30</v>
       </c>
       <c r="H1062" s="4">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I1062" s="4">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="1063" spans="1:9" x14ac:dyDescent="0.25">
@@ -35771,7 +35771,7 @@
         <v>0</v>
       </c>
       <c r="H1063" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1063" s="4">
         <v>5</v>
@@ -35858,7 +35858,7 @@
         <v>5</v>
       </c>
       <c r="H1066" s="4">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I1066" s="4">
         <v>28</v>
@@ -36055,16 +36055,16 @@
         <v>89</v>
       </c>
       <c r="F1073" s="4">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="G1073" s="4">
         <v>73</v>
       </c>
       <c r="H1073" s="4">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="I1073" s="4">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="1074" spans="1:9" x14ac:dyDescent="0.25">
@@ -36113,16 +36113,16 @@
         <v>90</v>
       </c>
       <c r="F1075" s="4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G1075" s="4">
         <v>5</v>
       </c>
       <c r="H1075" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I1075" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1076" spans="1:9" x14ac:dyDescent="0.25">
@@ -36206,7 +36206,7 @@
         <v>56</v>
       </c>
       <c r="H1078" s="4">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I1078" s="4">
         <v>83</v>
@@ -36235,7 +36235,7 @@
         <v>16</v>
       </c>
       <c r="H1079" s="4">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I1079" s="4">
         <v>36</v>
@@ -36258,7 +36258,7 @@
         <v>90</v>
       </c>
       <c r="F1080" s="4">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G1080" s="4">
         <v>10</v>
@@ -36267,7 +36267,7 @@
         <v>2</v>
       </c>
       <c r="I1080" s="4">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1081" spans="1:9" x14ac:dyDescent="0.25">
@@ -36293,7 +36293,7 @@
         <v>18</v>
       </c>
       <c r="H1081" s="4">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I1081" s="4">
         <v>33</v>
@@ -36351,7 +36351,7 @@
         <v>6</v>
       </c>
       <c r="H1083" s="4">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I1083" s="4">
         <v>35</v>
@@ -36461,16 +36461,16 @@
         <v>91</v>
       </c>
       <c r="F1087" s="4">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G1087" s="4">
         <v>15</v>
       </c>
       <c r="H1087" s="4">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I1087" s="4">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="1088" spans="1:9" x14ac:dyDescent="0.25">
@@ -36519,16 +36519,16 @@
         <v>91</v>
       </c>
       <c r="F1089" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1089" s="4">
         <v>0</v>
       </c>
       <c r="H1089" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I1089" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1090" spans="1:9" x14ac:dyDescent="0.25">
@@ -36577,16 +36577,16 @@
         <v>91</v>
       </c>
       <c r="F1091" s="4">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G1091" s="4">
         <v>38</v>
       </c>
       <c r="H1091" s="4">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="I1091" s="4">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="1092" spans="1:9" x14ac:dyDescent="0.25">
@@ -36664,16 +36664,16 @@
         <v>92</v>
       </c>
       <c r="F1094" s="4">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="G1094" s="4">
         <v>7</v>
       </c>
       <c r="H1094" s="4">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I1094" s="4">
-        <v>16</v>
+        <v>26</v>
       </c>
     </row>
     <row r="1095" spans="1:9" x14ac:dyDescent="0.25">
@@ -36751,16 +36751,16 @@
         <v>92</v>
       </c>
       <c r="F1097" s="4">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="G1097" s="4">
         <v>0</v>
       </c>
       <c r="H1097" s="4">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="I1097" s="4">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="1098" spans="1:9" x14ac:dyDescent="0.25">
@@ -37250,7 +37250,7 @@
         <v>4</v>
       </c>
       <c r="H1114" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I1114" s="4">
         <v>12</v>
@@ -37279,7 +37279,7 @@
         <v>22</v>
       </c>
       <c r="H1115" s="4">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I1115" s="4">
         <v>38</v>
@@ -37476,16 +37476,16 @@
         <v>93</v>
       </c>
       <c r="F1122" s="4">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="G1122" s="4">
         <v>3</v>
       </c>
       <c r="H1122" s="4">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I1122" s="4">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1123" spans="1:9" x14ac:dyDescent="0.25">
@@ -37505,16 +37505,16 @@
         <v>93</v>
       </c>
       <c r="F1123" s="4">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="G1123" s="4">
         <v>16</v>
       </c>
       <c r="H1123" s="4">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I1123" s="4">
-        <v>34</v>
+        <v>44</v>
       </c>
     </row>
     <row r="1124" spans="1:9" x14ac:dyDescent="0.25">
@@ -37650,16 +37650,16 @@
         <v>94</v>
       </c>
       <c r="F1128" s="4">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="G1128" s="4">
         <v>36</v>
       </c>
       <c r="H1128" s="4">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I1128" s="4">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="1129" spans="1:9" x14ac:dyDescent="0.25">
@@ -37679,16 +37679,16 @@
         <v>94</v>
       </c>
       <c r="F1129" s="4">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G1129" s="4">
         <v>22</v>
       </c>
       <c r="H1129" s="4">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I1129" s="4">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="1130" spans="1:9" x14ac:dyDescent="0.25">
@@ -37708,16 +37708,16 @@
         <v>94</v>
       </c>
       <c r="F1130" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1130" s="4">
         <v>0</v>
       </c>
       <c r="H1130" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I1130" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1131" spans="1:9" x14ac:dyDescent="0.25">
@@ -37772,7 +37772,7 @@
         <v>10</v>
       </c>
       <c r="H1132" s="4">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I1132" s="4">
         <v>42</v>
@@ -37801,7 +37801,7 @@
         <v>2</v>
       </c>
       <c r="H1133" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I1133" s="4">
         <v>14</v>
@@ -37882,16 +37882,16 @@
         <v>95</v>
       </c>
       <c r="F1136" s="4">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G1136" s="4">
         <v>7</v>
       </c>
       <c r="H1136" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I1136" s="4">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1137" spans="1:9" x14ac:dyDescent="0.25">
@@ -37969,16 +37969,16 @@
         <v>95</v>
       </c>
       <c r="F1139" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1139" s="4">
         <v>0</v>
       </c>
       <c r="H1139" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I1139" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1140" spans="1:9" x14ac:dyDescent="0.25">
@@ -38091,7 +38091,7 @@
         <v>10</v>
       </c>
       <c r="H1143" s="4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I1143" s="4">
         <v>44</v>
@@ -38178,7 +38178,7 @@
         <v>8</v>
       </c>
       <c r="H1146" s="4">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I1146" s="4">
         <v>35</v>
@@ -38346,16 +38346,16 @@
         <v>96</v>
       </c>
       <c r="F1152" s="4">
+        <v>10</v>
+      </c>
+      <c r="G1152" s="4">
+        <v>2</v>
+      </c>
+      <c r="H1152" s="4">
+        <v>2</v>
+      </c>
+      <c r="I1152" s="4">
         <v>8</v>
-      </c>
-      <c r="G1152" s="4">
-        <v>2</v>
-      </c>
-      <c r="H1152" s="4">
-        <v>1</v>
-      </c>
-      <c r="I1152" s="4">
-        <v>6</v>
       </c>
     </row>
     <row r="1153" spans="1:9" x14ac:dyDescent="0.25">
@@ -38439,7 +38439,7 @@
         <v>18</v>
       </c>
       <c r="H1155" s="4">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I1155" s="4">
         <v>49</v>
@@ -38549,16 +38549,16 @@
         <v>96</v>
       </c>
       <c r="F1159" s="4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G1159" s="4">
         <v>4</v>
       </c>
       <c r="H1159" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1159" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1160" spans="1:9" x14ac:dyDescent="0.25">
@@ -38578,16 +38578,16 @@
         <v>96</v>
       </c>
       <c r="F1160" s="4">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G1160" s="4">
         <v>13</v>
       </c>
       <c r="H1160" s="4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I1160" s="4">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="1161" spans="1:9" x14ac:dyDescent="0.25">
@@ -38642,7 +38642,7 @@
         <v>7</v>
       </c>
       <c r="H1162" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I1162" s="4">
         <v>23</v>
@@ -38665,7 +38665,7 @@
         <v>96</v>
       </c>
       <c r="F1163" s="4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G1163" s="4">
         <v>3</v>
@@ -38674,7 +38674,7 @@
         <v>1</v>
       </c>
       <c r="I1163" s="4">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1164" spans="1:9" x14ac:dyDescent="0.25">
@@ -38700,7 +38700,7 @@
         <v>14</v>
       </c>
       <c r="H1164" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I1164" s="4">
         <v>41</v>
@@ -38758,7 +38758,7 @@
         <v>3</v>
       </c>
       <c r="H1166" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I1166" s="4">
         <v>11</v>
@@ -38781,16 +38781,16 @@
         <v>97</v>
       </c>
       <c r="F1167" s="4">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="G1167" s="4">
         <v>7</v>
       </c>
       <c r="H1167" s="4">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I1167" s="4">
-        <v>20</v>
+        <v>29</v>
       </c>
     </row>
     <row r="1168" spans="1:9" x14ac:dyDescent="0.25">
@@ -38897,16 +38897,16 @@
         <v>97</v>
       </c>
       <c r="F1171" s="4">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="G1171" s="4">
         <v>47</v>
       </c>
       <c r="H1171" s="4">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I1171" s="4">
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
     <row r="1172" spans="1:9" x14ac:dyDescent="0.25">
@@ -39048,7 +39048,7 @@
         <v>6</v>
       </c>
       <c r="H1176" s="4">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="I1176" s="4">
         <v>33</v>
@@ -39245,7 +39245,7 @@
         <v>98</v>
       </c>
       <c r="F1183" s="4">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G1183" s="4">
         <v>7</v>
@@ -39254,7 +39254,7 @@
         <v>1</v>
       </c>
       <c r="I1183" s="4">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1184" spans="1:9" x14ac:dyDescent="0.25">
@@ -39309,7 +39309,7 @@
         <v>7</v>
       </c>
       <c r="H1185" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I1185" s="4">
         <v>19</v>
@@ -39367,7 +39367,7 @@
         <v>6</v>
       </c>
       <c r="H1187" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I1187" s="4">
         <v>41</v>
@@ -39396,7 +39396,7 @@
         <v>22</v>
       </c>
       <c r="H1188" s="4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I1188" s="4">
         <v>39</v>
@@ -39425,7 +39425,7 @@
         <v>7</v>
       </c>
       <c r="H1189" s="4">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I1189" s="4">
         <v>30</v>
@@ -39506,16 +39506,16 @@
         <v>99</v>
       </c>
       <c r="F1192" s="4">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="G1192" s="4">
         <v>27</v>
       </c>
       <c r="H1192" s="4">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I1192" s="4">
-        <v>72</v>
+        <v>78</v>
       </c>
     </row>
     <row r="1193" spans="1:9" x14ac:dyDescent="0.25">
@@ -39570,7 +39570,7 @@
         <v>8</v>
       </c>
       <c r="H1194" s="4">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I1194" s="4">
         <v>36</v>
@@ -39628,7 +39628,7 @@
         <v>1</v>
       </c>
       <c r="H1196" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I1196" s="4">
         <v>9</v>
@@ -39651,16 +39651,16 @@
         <v>99</v>
       </c>
       <c r="F1197" s="4">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="G1197" s="4">
         <v>8</v>
       </c>
       <c r="H1197" s="4">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I1197" s="4">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="1198" spans="1:9" x14ac:dyDescent="0.25">
@@ -39680,16 +39680,16 @@
         <v>99</v>
       </c>
       <c r="F1198" s="4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G1198" s="4">
         <v>4</v>
       </c>
       <c r="H1198" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1198" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1199" spans="1:9" x14ac:dyDescent="0.25">
@@ -39715,7 +39715,7 @@
         <v>7</v>
       </c>
       <c r="H1199" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I1199" s="4">
         <v>11</v>
@@ -39744,7 +39744,7 @@
         <v>5</v>
       </c>
       <c r="H1200" s="4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I1200" s="4">
         <v>25</v>
@@ -39860,7 +39860,7 @@
         <v>0</v>
       </c>
       <c r="H1204" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I1204" s="4">
         <v>2</v>
@@ -39889,7 +39889,7 @@
         <v>27</v>
       </c>
       <c r="H1205" s="4">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="I1205" s="4">
         <v>44</v>
@@ -39947,7 +39947,7 @@
         <v>6</v>
       </c>
       <c r="H1207" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I1207" s="4">
         <v>18</v>
@@ -40028,7 +40028,7 @@
         <v>100</v>
       </c>
       <c r="F1210" s="4">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G1210" s="4">
         <v>4</v>
@@ -40037,7 +40037,7 @@
         <v>9</v>
       </c>
       <c r="I1210" s="4">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="1211" spans="1:9" x14ac:dyDescent="0.25">
@@ -40092,7 +40092,7 @@
         <v>30</v>
       </c>
       <c r="H1212" s="4">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="I1212" s="4">
         <v>78</v>
@@ -40121,7 +40121,7 @@
         <v>0</v>
       </c>
       <c r="H1213" s="4">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I1213" s="4">
         <v>15</v>
@@ -40208,7 +40208,7 @@
         <v>33</v>
       </c>
       <c r="H1216" s="4">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="I1216" s="4">
         <v>94</v>
@@ -40295,7 +40295,7 @@
         <v>0</v>
       </c>
       <c r="H1219" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1219" s="4">
         <v>5</v>
@@ -40324,7 +40324,7 @@
         <v>14</v>
       </c>
       <c r="H1220" s="4">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="I1220" s="4">
         <v>64</v>
@@ -40347,16 +40347,16 @@
         <v>102</v>
       </c>
       <c r="F1221" s="4">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G1221" s="4">
         <v>22</v>
       </c>
       <c r="H1221" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I1221" s="4">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="1222" spans="1:9" x14ac:dyDescent="0.25">
@@ -40382,7 +40382,7 @@
         <v>21</v>
       </c>
       <c r="H1222" s="4">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="I1222" s="4">
         <v>60</v>
@@ -40521,7 +40521,7 @@
         <v>103</v>
       </c>
       <c r="F1227" s="4">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="G1227" s="4">
         <v>65</v>
@@ -40530,7 +40530,7 @@
         <v>31</v>
       </c>
       <c r="I1227" s="4">
-        <v>158</v>
+        <v>161</v>
       </c>
     </row>
     <row r="1228" spans="1:9" x14ac:dyDescent="0.25">
@@ -40550,7 +40550,7 @@
         <v>103</v>
       </c>
       <c r="F1228" s="4">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G1228" s="4">
         <v>6</v>
@@ -40559,7 +40559,7 @@
         <v>10</v>
       </c>
       <c r="I1228" s="4">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="1229" spans="1:9" x14ac:dyDescent="0.25">
@@ -40608,16 +40608,16 @@
         <v>104</v>
       </c>
       <c r="F1230" s="4">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="G1230" s="4">
         <v>31</v>
       </c>
       <c r="H1230" s="4">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I1230" s="4">
-        <v>94</v>
+        <v>97</v>
       </c>
     </row>
     <row r="1231" spans="1:9" x14ac:dyDescent="0.25">
@@ -40637,16 +40637,16 @@
         <v>104</v>
       </c>
       <c r="F1231" s="4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G1231" s="4">
         <v>4</v>
       </c>
       <c r="H1231" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1231" s="4">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1232" spans="1:9" x14ac:dyDescent="0.25">
@@ -40666,16 +40666,16 @@
         <v>104</v>
       </c>
       <c r="F1232" s="4">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="G1232" s="4">
         <v>5</v>
       </c>
       <c r="H1232" s="4">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I1232" s="4">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1233" spans="1:9" x14ac:dyDescent="0.25">
@@ -40782,16 +40782,16 @@
         <v>105</v>
       </c>
       <c r="F1236" s="4">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="G1236" s="4">
         <v>9</v>
       </c>
       <c r="H1236" s="4">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I1236" s="4">
-        <v>18</v>
+        <v>29</v>
       </c>
     </row>
     <row r="1237" spans="1:9" x14ac:dyDescent="0.25">
@@ -40817,7 +40817,7 @@
         <v>34</v>
       </c>
       <c r="H1237" s="4">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I1237" s="4">
         <v>49</v>
@@ -41130,16 +41130,16 @@
         <v>106</v>
       </c>
       <c r="F1248" s="4">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G1248" s="4">
         <v>6</v>
       </c>
       <c r="H1248" s="4">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I1248" s="4">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="1249" spans="1:9" x14ac:dyDescent="0.25">
@@ -41165,7 +41165,7 @@
         <v>42</v>
       </c>
       <c r="H1249" s="4">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I1249" s="4">
         <v>62</v>
@@ -41194,7 +41194,7 @@
         <v>5</v>
       </c>
       <c r="H1250" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I1250" s="4">
         <v>9</v>
@@ -41333,16 +41333,16 @@
         <v>106</v>
       </c>
       <c r="F1255" s="4">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G1255" s="4">
         <v>5</v>
       </c>
       <c r="H1255" s="4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I1255" s="4">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="1256" spans="1:9" x14ac:dyDescent="0.25">
@@ -41507,7 +41507,7 @@
         <v>107</v>
       </c>
       <c r="F1261" s="4">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G1261" s="4">
         <v>9</v>
@@ -41516,7 +41516,7 @@
         <v>6</v>
       </c>
       <c r="I1261" s="4">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="1262" spans="1:9" x14ac:dyDescent="0.25">
@@ -41623,16 +41623,16 @@
         <v>107</v>
       </c>
       <c r="F1265" s="4">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G1265" s="4">
         <v>11</v>
       </c>
       <c r="H1265" s="4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I1265" s="4">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="1266" spans="1:9" x14ac:dyDescent="0.25">
@@ -41745,7 +41745,7 @@
         <v>4</v>
       </c>
       <c r="H1269" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I1269" s="4">
         <v>12</v>
@@ -41768,16 +41768,16 @@
         <v>107</v>
       </c>
       <c r="F1270" s="4">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G1270" s="4">
         <v>10</v>
       </c>
       <c r="H1270" s="4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I1270" s="4">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="1271" spans="1:9" x14ac:dyDescent="0.25">
@@ -41948,7 +41948,7 @@
         <v>8</v>
       </c>
       <c r="H1276" s="4">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I1276" s="4">
         <v>32</v>
@@ -42006,7 +42006,7 @@
         <v>1</v>
       </c>
       <c r="H1278" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1278" s="4">
         <v>8</v>
@@ -42116,16 +42116,16 @@
         <v>108</v>
       </c>
       <c r="F1282" s="4">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G1282" s="4">
         <v>9</v>
       </c>
       <c r="H1282" s="4">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I1282" s="4">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1283" spans="1:9" x14ac:dyDescent="0.25">
@@ -42493,16 +42493,16 @@
         <v>109</v>
       </c>
       <c r="F1295" s="4">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="G1295" s="4">
         <v>17</v>
       </c>
       <c r="H1295" s="4">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I1295" s="4">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="1296" spans="1:9" x14ac:dyDescent="0.25">
@@ -42638,16 +42638,16 @@
         <v>109</v>
       </c>
       <c r="F1300" s="4">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="G1300" s="4">
         <v>46</v>
       </c>
       <c r="H1300" s="4">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I1300" s="4">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="1301" spans="1:9" x14ac:dyDescent="0.25">
@@ -42957,16 +42957,16 @@
         <v>110</v>
       </c>
       <c r="F1311" s="4">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G1311" s="4">
         <v>10</v>
       </c>
       <c r="H1311" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I1311" s="4">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1312" spans="1:9" x14ac:dyDescent="0.25">
@@ -43015,7 +43015,7 @@
         <v>110</v>
       </c>
       <c r="F1313" s="4">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G1313" s="4">
         <v>13</v>
@@ -43024,7 +43024,7 @@
         <v>11</v>
       </c>
       <c r="I1313" s="4">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1314" spans="1:9" x14ac:dyDescent="0.25">
@@ -43131,16 +43131,16 @@
         <v>111</v>
       </c>
       <c r="F1317" s="4">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G1317" s="4">
         <v>12</v>
       </c>
       <c r="H1317" s="4">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I1317" s="4">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="1318" spans="1:9" x14ac:dyDescent="0.25">
@@ -43189,16 +43189,16 @@
         <v>111</v>
       </c>
       <c r="F1319" s="4">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G1319" s="4">
         <v>15</v>
       </c>
       <c r="H1319" s="4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I1319" s="4">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="1320" spans="1:9" x14ac:dyDescent="0.25">
@@ -43218,16 +43218,16 @@
         <v>111</v>
       </c>
       <c r="F1320" s="4">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G1320" s="4">
         <v>10</v>
       </c>
       <c r="H1320" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1320" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="1321" spans="1:9" x14ac:dyDescent="0.25">
@@ -43305,16 +43305,16 @@
         <v>112</v>
       </c>
       <c r="F1323" s="4">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G1323" s="4">
         <v>8</v>
       </c>
       <c r="H1323" s="4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I1323" s="4">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="1324" spans="1:9" x14ac:dyDescent="0.25">
@@ -43421,16 +43421,16 @@
         <v>112</v>
       </c>
       <c r="F1327" s="4">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G1327" s="4">
         <v>17</v>
       </c>
       <c r="H1327" s="4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I1327" s="4">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1328" spans="1:9" x14ac:dyDescent="0.25">
@@ -43566,16 +43566,16 @@
         <v>113</v>
       </c>
       <c r="F1332" s="4">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G1332" s="4">
         <v>10</v>
       </c>
       <c r="H1332" s="4">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I1332" s="4">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="1333" spans="1:9" x14ac:dyDescent="0.25">
@@ -43659,7 +43659,7 @@
         <v>50</v>
       </c>
       <c r="H1335" s="4">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I1335" s="4">
         <v>81</v>
@@ -43717,7 +43717,7 @@
         <v>10</v>
       </c>
       <c r="H1337" s="4">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I1337" s="4">
         <v>46</v>
@@ -43943,16 +43943,16 @@
         <v>115</v>
       </c>
       <c r="F1345" s="4">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G1345" s="4">
         <v>12</v>
       </c>
       <c r="H1345" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I1345" s="4">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1346" spans="1:9" x14ac:dyDescent="0.25">
@@ -44036,7 +44036,7 @@
         <v>17</v>
       </c>
       <c r="H1348" s="4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I1348" s="4">
         <v>33</v>
@@ -44181,7 +44181,7 @@
         <v>4</v>
       </c>
       <c r="H1353" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1353" s="4">
         <v>16</v>
@@ -44407,16 +44407,16 @@
         <v>116</v>
       </c>
       <c r="F1361" s="4">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G1361" s="4">
         <v>5</v>
       </c>
       <c r="H1361" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I1361" s="4">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1362" spans="1:9" x14ac:dyDescent="0.25">
@@ -44465,16 +44465,16 @@
         <v>116</v>
       </c>
       <c r="F1363" s="4">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G1363" s="4">
         <v>15</v>
       </c>
       <c r="H1363" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I1363" s="4">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1364" spans="1:9" x14ac:dyDescent="0.25">
@@ -44668,16 +44668,16 @@
         <v>117</v>
       </c>
       <c r="F1370" s="4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G1370" s="4">
         <v>5</v>
       </c>
       <c r="H1370" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I1370" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1371" spans="1:9" x14ac:dyDescent="0.25">
@@ -44755,16 +44755,16 @@
         <v>117</v>
       </c>
       <c r="F1373" s="4">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G1373" s="4">
         <v>14</v>
       </c>
       <c r="H1373" s="4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I1373" s="4">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1374" spans="1:9" x14ac:dyDescent="0.25">
@@ -44784,16 +44784,16 @@
         <v>117</v>
       </c>
       <c r="F1374" s="4">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="G1374" s="4">
         <v>11</v>
       </c>
       <c r="H1374" s="4">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I1374" s="4">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="1375" spans="1:9" x14ac:dyDescent="0.25">
@@ -45161,16 +45161,16 @@
         <v>118</v>
       </c>
       <c r="F1387" s="4">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G1387" s="4">
         <v>5</v>
       </c>
       <c r="H1387" s="4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I1387" s="4">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="1388" spans="1:9" x14ac:dyDescent="0.25">
@@ -45190,7 +45190,7 @@
         <v>118</v>
       </c>
       <c r="F1388" s="4">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G1388" s="4">
         <v>13</v>
@@ -45199,7 +45199,7 @@
         <v>7</v>
       </c>
       <c r="I1388" s="4">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="1389" spans="1:9" x14ac:dyDescent="0.25">
@@ -45254,7 +45254,7 @@
         <v>38</v>
       </c>
       <c r="H1390" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I1390" s="4">
         <v>52</v>
@@ -45277,7 +45277,7 @@
         <v>118</v>
       </c>
       <c r="F1391" s="4">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G1391" s="4">
         <v>8</v>
@@ -45286,7 +45286,7 @@
         <v>14</v>
       </c>
       <c r="I1391" s="4">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="1392" spans="1:9" x14ac:dyDescent="0.25">
@@ -45341,7 +45341,7 @@
         <v>16</v>
       </c>
       <c r="H1393" s="4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I1393" s="4">
         <v>59</v>
@@ -45689,7 +45689,7 @@
         <v>17</v>
       </c>
       <c r="H1405" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I1405" s="4">
         <v>41</v>
@@ -45828,16 +45828,16 @@
         <v>120</v>
       </c>
       <c r="F1410" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G1410" s="4">
         <v>8</v>
       </c>
       <c r="H1410" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1410" s="4">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1411" spans="1:9" x14ac:dyDescent="0.25">
@@ -45973,7 +45973,7 @@
         <v>120</v>
       </c>
       <c r="F1415" s="4">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G1415" s="4">
         <v>3</v>
@@ -45982,7 +45982,7 @@
         <v>8</v>
       </c>
       <c r="I1415" s="4">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="1416" spans="1:9" x14ac:dyDescent="0.25">
@@ -46089,7 +46089,7 @@
         <v>121</v>
       </c>
       <c r="F1419" s="4">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G1419" s="4">
         <v>41</v>
@@ -46098,7 +46098,7 @@
         <v>9</v>
       </c>
       <c r="I1419" s="4">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="1420" spans="1:9" x14ac:dyDescent="0.25">
@@ -46153,7 +46153,7 @@
         <v>6</v>
       </c>
       <c r="H1421" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I1421" s="4">
         <v>21</v>
@@ -46176,16 +46176,16 @@
         <v>121</v>
       </c>
       <c r="F1422" s="4">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G1422" s="4">
         <v>4</v>
       </c>
       <c r="H1422" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I1422" s="4">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="1423" spans="1:9" x14ac:dyDescent="0.25">
@@ -46959,16 +46959,16 @@
         <v>123</v>
       </c>
       <c r="F1449" s="4">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G1449" s="4">
         <v>21</v>
       </c>
       <c r="H1449" s="4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I1449" s="4">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="1450" spans="1:9" x14ac:dyDescent="0.25">
@@ -47104,7 +47104,7 @@
         <v>123</v>
       </c>
       <c r="F1454" s="4">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G1454" s="4">
         <v>24</v>
@@ -47113,7 +47113,7 @@
         <v>12</v>
       </c>
       <c r="I1454" s="4">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="1455" spans="1:9" x14ac:dyDescent="0.25">
@@ -47342,7 +47342,7 @@
         <v>11</v>
       </c>
       <c r="H1462" s="4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I1462" s="4">
         <v>34</v>
@@ -47545,7 +47545,7 @@
         <v>20</v>
       </c>
       <c r="H1469" s="4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I1469" s="4">
         <v>38</v>
@@ -48119,16 +48119,16 @@
         <v>126</v>
       </c>
       <c r="F1489" s="4">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="G1489" s="4">
         <v>6</v>
       </c>
       <c r="H1489" s="4">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I1489" s="4">
-        <v>18</v>
+        <v>23</v>
       </c>
     </row>
     <row r="1490" spans="1:9" x14ac:dyDescent="0.25">
@@ -48241,7 +48241,7 @@
         <v>11</v>
       </c>
       <c r="H1493" s="4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I1493" s="4">
         <v>33</v>
@@ -48583,7 +48583,7 @@
         <v>128</v>
       </c>
       <c r="F1505" s="4">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G1505" s="4">
         <v>3</v>
@@ -48592,7 +48592,7 @@
         <v>15</v>
       </c>
       <c r="I1505" s="4">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="1506" spans="1:9" x14ac:dyDescent="0.25">
@@ -48850,7 +48850,7 @@
         <v>0</v>
       </c>
       <c r="H1514" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1514" s="4">
         <v>4</v>
@@ -48879,7 +48879,7 @@
         <v>22</v>
       </c>
       <c r="H1515" s="4">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I1515" s="4">
         <v>61</v>
@@ -48937,7 +48937,7 @@
         <v>17</v>
       </c>
       <c r="H1517" s="4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I1517" s="4">
         <v>30</v>
@@ -49076,16 +49076,16 @@
         <v>129</v>
       </c>
       <c r="F1522" s="4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G1522" s="4">
         <v>4</v>
       </c>
       <c r="H1522" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I1522" s="4">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1523" spans="1:9" x14ac:dyDescent="0.25">
@@ -49198,7 +49198,7 @@
         <v>23</v>
       </c>
       <c r="H1526" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I1526" s="4">
         <v>55</v>
@@ -49256,7 +49256,7 @@
         <v>12</v>
       </c>
       <c r="H1528" s="4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I1528" s="4">
         <v>35</v>
@@ -49285,7 +49285,7 @@
         <v>7</v>
       </c>
       <c r="H1529" s="4">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I1529" s="4">
         <v>42</v>
@@ -49459,7 +49459,7 @@
         <v>23</v>
       </c>
       <c r="H1535" s="4">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I1535" s="4">
         <v>47</v>
@@ -49923,7 +49923,7 @@
         <v>17</v>
       </c>
       <c r="H1551" s="4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I1551" s="4">
         <v>39</v>
@@ -49952,7 +49952,7 @@
         <v>3</v>
       </c>
       <c r="H1552" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I1552" s="4">
         <v>5</v>
@@ -50097,7 +50097,7 @@
         <v>58</v>
       </c>
       <c r="H1557" s="4">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I1557" s="4">
         <v>132</v>
@@ -50236,16 +50236,16 @@
         <v>133</v>
       </c>
       <c r="F1562" s="4">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="G1562" s="4">
         <v>3</v>
       </c>
       <c r="H1562" s="4">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I1562" s="4">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="1563" spans="1:9" x14ac:dyDescent="0.25">
@@ -50561,7 +50561,7 @@
         <v>8</v>
       </c>
       <c r="H1573" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1573" s="4">
         <v>11</v>
@@ -50851,7 +50851,7 @@
         <v>9</v>
       </c>
       <c r="H1583" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1583" s="4">
         <v>8</v>
@@ -51077,16 +51077,16 @@
         <v>135</v>
       </c>
       <c r="F1591" s="4">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="G1591" s="4">
         <v>7</v>
       </c>
       <c r="H1591" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I1591" s="4">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1592" spans="1:9" x14ac:dyDescent="0.25">
@@ -51106,16 +51106,16 @@
         <v>135</v>
       </c>
       <c r="F1592" s="4">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="G1592" s="4">
         <v>7</v>
       </c>
       <c r="H1592" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I1592" s="4">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1593" spans="1:9" x14ac:dyDescent="0.25">
@@ -51257,7 +51257,7 @@
         <v>18</v>
       </c>
       <c r="H1597" s="4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I1597" s="4">
         <v>54</v>
@@ -51280,16 +51280,16 @@
         <v>136</v>
       </c>
       <c r="F1598" s="4">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G1598" s="4">
         <v>16</v>
       </c>
       <c r="H1598" s="4">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I1598" s="4">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="1599" spans="1:9" x14ac:dyDescent="0.25">
@@ -51309,16 +51309,16 @@
         <v>136</v>
       </c>
       <c r="F1599" s="4">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G1599" s="4">
         <v>12</v>
       </c>
       <c r="H1599" s="4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I1599" s="4">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="1600" spans="1:9" x14ac:dyDescent="0.25">
@@ -51576,7 +51576,7 @@
         <v>3</v>
       </c>
       <c r="H1608" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1608" s="4">
         <v>11</v>
@@ -51686,7 +51686,7 @@
         <v>137</v>
       </c>
       <c r="F1612" s="4">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G1612" s="4">
         <v>37</v>
@@ -51695,7 +51695,7 @@
         <v>15</v>
       </c>
       <c r="I1612" s="4">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="1613" spans="1:9" x14ac:dyDescent="0.25">
@@ -51750,7 +51750,7 @@
         <v>9</v>
       </c>
       <c r="H1614" s="4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I1614" s="4">
         <v>24</v>
@@ -51831,16 +51831,16 @@
         <v>137</v>
       </c>
       <c r="F1617" s="4">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G1617" s="4">
         <v>9</v>
       </c>
       <c r="H1617" s="4">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="I1617" s="4">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="1618" spans="1:9" x14ac:dyDescent="0.25">
@@ -51947,16 +51947,16 @@
         <v>138</v>
       </c>
       <c r="F1621" s="4">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G1621" s="4">
         <v>8</v>
       </c>
       <c r="H1621" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I1621" s="4">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1622" spans="1:9" x14ac:dyDescent="0.25">
@@ -52011,7 +52011,7 @@
         <v>7</v>
       </c>
       <c r="H1623" s="4">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="I1623" s="4">
         <v>31</v>
@@ -52034,7 +52034,7 @@
         <v>138</v>
       </c>
       <c r="F1624" s="4">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G1624" s="4">
         <v>26</v>
@@ -52043,7 +52043,7 @@
         <v>4</v>
       </c>
       <c r="I1624" s="4">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="1625" spans="1:9" x14ac:dyDescent="0.25">
@@ -52098,7 +52098,7 @@
         <v>3</v>
       </c>
       <c r="H1626" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I1626" s="4">
         <v>5</v>
@@ -52237,16 +52237,16 @@
         <v>139</v>
       </c>
       <c r="F1631" s="4">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="G1631" s="4">
         <v>31</v>
       </c>
       <c r="H1631" s="4">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I1631" s="4">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="1632" spans="1:9" x14ac:dyDescent="0.25">
@@ -52382,16 +52382,16 @@
         <v>139</v>
       </c>
       <c r="F1636" s="4">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G1636" s="4">
         <v>9</v>
       </c>
       <c r="H1636" s="4">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="I1636" s="4">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="1637" spans="1:9" x14ac:dyDescent="0.25">
@@ -52678,7 +52678,7 @@
         <v>3</v>
       </c>
       <c r="H1646" s="4">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="I1646" s="4">
         <v>30</v>
@@ -52794,7 +52794,7 @@
         <v>33</v>
       </c>
       <c r="H1650" s="4">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I1650" s="4">
         <v>50</v>
@@ -52823,7 +52823,7 @@
         <v>3</v>
       </c>
       <c r="H1651" s="4">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I1651" s="4">
         <v>26</v>
@@ -52852,7 +52852,7 @@
         <v>39</v>
       </c>
       <c r="H1652" s="4">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I1652" s="4">
         <v>106</v>
@@ -53107,16 +53107,16 @@
         <v>142</v>
       </c>
       <c r="F1661" s="4">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="G1661" s="4">
         <v>29</v>
       </c>
       <c r="H1661" s="4">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I1661" s="4">
-        <v>75</v>
+        <v>78</v>
       </c>
     </row>
     <row r="1662" spans="1:9" x14ac:dyDescent="0.25">
@@ -53200,7 +53200,7 @@
         <v>22</v>
       </c>
       <c r="H1664" s="4">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I1664" s="4">
         <v>43</v>
@@ -53548,7 +53548,7 @@
         <v>40</v>
       </c>
       <c r="H1676" s="4">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I1676" s="4">
         <v>56</v>
@@ -53606,7 +53606,7 @@
         <v>4</v>
       </c>
       <c r="H1678" s="4">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="I1678" s="4">
         <v>36</v>
@@ -53809,7 +53809,7 @@
         <v>15</v>
       </c>
       <c r="H1685" s="4">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I1685" s="4">
         <v>39</v>
@@ -53838,7 +53838,7 @@
         <v>7</v>
       </c>
       <c r="H1686" s="4">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I1686" s="4">
         <v>33</v>
@@ -53925,7 +53925,7 @@
         <v>44</v>
       </c>
       <c r="H1689" s="4">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="I1689" s="4">
         <v>83</v>
@@ -54064,16 +54064,16 @@
         <v>145</v>
       </c>
       <c r="F1694" s="4">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G1694" s="4">
         <v>50</v>
       </c>
       <c r="H1694" s="4">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I1694" s="4">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="1695" spans="1:9" x14ac:dyDescent="0.25">
@@ -54128,7 +54128,7 @@
         <v>13</v>
       </c>
       <c r="H1696" s="4">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="I1696" s="4">
         <v>36</v>
@@ -54383,7 +54383,7 @@
         <v>146</v>
       </c>
       <c r="F1705" s="4">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="G1705" s="4">
         <v>48</v>
@@ -54392,7 +54392,7 @@
         <v>34</v>
       </c>
       <c r="I1705" s="4">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="1706" spans="1:9" x14ac:dyDescent="0.25">
@@ -54418,7 +54418,7 @@
         <v>32</v>
       </c>
       <c r="H1706" s="4">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I1706" s="4">
         <v>44</v>
@@ -54476,7 +54476,7 @@
         <v>6</v>
       </c>
       <c r="H1708" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I1708" s="4">
         <v>12</v>
@@ -54505,7 +54505,7 @@
         <v>43</v>
       </c>
       <c r="H1709" s="4">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I1709" s="4">
         <v>55</v>
@@ -54592,7 +54592,7 @@
         <v>13</v>
       </c>
       <c r="H1712" s="4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I1712" s="4">
         <v>36</v>
@@ -54673,16 +54673,16 @@
         <v>147</v>
       </c>
       <c r="F1715" s="4">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G1715" s="4">
         <v>13</v>
       </c>
       <c r="H1715" s="4">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I1715" s="4">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="1716" spans="1:9" x14ac:dyDescent="0.25">
@@ -54731,16 +54731,16 @@
         <v>148</v>
       </c>
       <c r="F1717" s="4">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G1717" s="4">
         <v>45</v>
       </c>
       <c r="H1717" s="4">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I1717" s="4">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="1718" spans="1:9" x14ac:dyDescent="0.25">
@@ -54760,16 +54760,16 @@
         <v>148</v>
       </c>
       <c r="F1718" s="4">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="G1718" s="4">
         <v>38</v>
       </c>
       <c r="H1718" s="4">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I1718" s="4">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="1719" spans="1:9" x14ac:dyDescent="0.25">
@@ -54795,7 +54795,7 @@
         <v>4</v>
       </c>
       <c r="H1719" s="4">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="I1719" s="4">
         <v>34</v>
@@ -54853,7 +54853,7 @@
         <v>37</v>
       </c>
       <c r="H1721" s="4">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I1721" s="4">
         <v>81</v>
@@ -54940,7 +54940,7 @@
         <v>26</v>
       </c>
       <c r="H1724" s="4">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I1724" s="4">
         <v>41</v>
@@ -54992,16 +54992,16 @@
         <v>150</v>
       </c>
       <c r="F1726" s="4">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G1726" s="4">
         <v>11</v>
       </c>
       <c r="H1726" s="4">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="I1726" s="4">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="1727" spans="1:9" x14ac:dyDescent="0.25">
@@ -55114,7 +55114,7 @@
         <v>14</v>
       </c>
       <c r="H1730" s="4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I1730" s="4">
         <v>35</v>
@@ -55195,16 +55195,16 @@
         <v>151</v>
       </c>
       <c r="F1733" s="4">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="G1733" s="4">
         <v>60</v>
       </c>
       <c r="H1733" s="4">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I1733" s="4">
-        <v>146</v>
+        <v>153</v>
       </c>
     </row>
     <row r="1734" spans="1:9" x14ac:dyDescent="0.25">
@@ -55224,16 +55224,16 @@
         <v>151</v>
       </c>
       <c r="F1734" s="4">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G1734" s="4">
         <v>22</v>
       </c>
       <c r="H1734" s="4">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="I1734" s="4">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="1735" spans="1:9" x14ac:dyDescent="0.25">
@@ -55259,7 +55259,7 @@
         <v>11</v>
       </c>
       <c r="H1735" s="4">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I1735" s="4">
         <v>46</v>
